--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{AEE4955E-EFC3-438E-8D1F-3DACCBCB0136}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C28F1E2-5D9F-47A5-8BBC-DE131C2D9DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K12" s="2">
         <v>0</v>
@@ -3032,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K13" s="2">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
@@ -3206,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>1000</v>
+        <v>500</v>
       </c>
       <c r="K15" s="2">
         <v>0</v>
@@ -4546,16 +4546,16 @@
         <v>1</v>
       </c>
       <c r="U30" s="21">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="V30" s="21">
-        <v>16000</v>
+        <v>12000</v>
       </c>
       <c r="W30" s="21">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="X30" s="21">
-        <v>8000</v>
+        <v>7200</v>
       </c>
       <c r="Y30" s="21">
         <v>0</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C28F1E2-5D9F-47A5-8BBC-DE131C2D9DFA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D193E54-C71D-48A7-AEFB-007D38D85585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="J12" s="2">
-        <v>500</v>
+        <v>0</v>
       </c>
       <c r="K12" s="2">
         <v>0</v>
@@ -3032,7 +3032,7 @@
         <v>0</v>
       </c>
       <c r="J13" s="2">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="K13" s="2">
         <v>0</v>
@@ -3119,7 +3119,7 @@
         <v>0</v>
       </c>
       <c r="J14" s="2">
-        <v>500</v>
+        <v>250</v>
       </c>
       <c r="K14" s="2">
         <v>0</v>
@@ -3206,7 +3206,7 @@
         <v>0</v>
       </c>
       <c r="J15" s="2">
-        <v>500</v>
+        <v>750</v>
       </c>
       <c r="K15" s="2">
         <v>0</v>
@@ -4546,16 +4546,16 @@
         <v>1</v>
       </c>
       <c r="U30" s="21">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="V30" s="21">
+        <v>20000</v>
+      </c>
+      <c r="W30" s="21">
+        <v>0</v>
+      </c>
+      <c r="X30" s="21">
         <v>12000</v>
-      </c>
-      <c r="W30" s="21">
-        <v>5</v>
-      </c>
-      <c r="X30" s="21">
-        <v>7200</v>
       </c>
       <c r="Y30" s="21">
         <v>0</v>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2D193E54-C71D-48A7-AEFB-007D38D85585}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04FC212-D0B1-4530-9E46-1D26952C6008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$77</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$104</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -271,7 +271,24 @@
         </r>
       </text>
     </comment>
-    <comment ref="AB4" authorId="1" shapeId="0" xr:uid="{01D943CF-AECD-4005-A6CE-59046F14F27A}">
+    <comment ref="U4" authorId="1" shapeId="0" xr:uid="{5C377855-6EBD-4812-909F-8B6A79057BC3}">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <family val="3"/>
+            <charset val="134"/>
+          </rPr>
+          <t>0-没有直接效果
+1-直接伤害：根据释放者的攻击力万分比
+2-直接回血：根据释放者的攻击力万分比
+3-直接回血：根据目标的生命最大值计算，百万分比</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="AC4" authorId="1" shapeId="0" xr:uid="{01D943CF-AECD-4005-A6CE-59046F14F27A}">
       <text>
         <r>
           <rPr>
@@ -302,7 +319,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC4" authorId="1" shapeId="0" xr:uid="{FF5772BF-0DF9-41C0-B44E-0880B3623722}">
+    <comment ref="AD4" authorId="1" shapeId="0" xr:uid="{FF5772BF-0DF9-41C0-B44E-0880B3623722}">
       <text>
         <r>
           <rPr>
@@ -338,7 +355,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="764" uniqueCount="296">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="303">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1355,6 +1372,33 @@
   </si>
   <si>
     <t>击杀回血效果提高</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>受到的伤害总加成</t>
+  </si>
+  <si>
+    <t>受到的伤害总加成，永久</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>damage_element</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>LIST&lt;INT&gt;_S_C</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>参与伤害计算的攻击元素类型（0-物理、1-冰、2-火、3-毒、4-电）</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>1,2,3,4,0</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1362,7 +1406,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="21" x14ac:knownFonts="1">
+  <fonts count="23" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1516,6 +1560,20 @@
       <family val="3"/>
       <charset val="134"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C5700"/>
+      <name val="宋体"/>
+      <family val="3"/>
+      <charset val="134"/>
+    </font>
   </fonts>
   <fills count="14">
     <fill>
@@ -1650,7 +1708,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="32">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1717,6 +1775,16 @@
     </xf>
     <xf numFmtId="0" fontId="19" fillId="3" borderId="0" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1"/>
     <xf numFmtId="0" fontId="20" fillId="13" borderId="0" xfId="4" applyFont="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="18" fillId="12" borderId="1" xfId="0" quotePrefix="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="0" xfId="0" applyFont="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="4" borderId="1" xfId="1" applyFill="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="5">
     <cellStyle name="差" xfId="4" builtinId="27"/>
@@ -2017,7 +2085,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AC103"/>
+  <dimension ref="A1:AD104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -2035,24 +2103,25 @@
     <col min="18" max="18" width="12.5" style="5" bestFit="1" customWidth="1"/>
     <col min="19" max="19" width="9.5" style="5" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="12.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="17.5" style="5" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="20.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="19.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="15.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="24.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="28.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="30" max="16384" width="9" style="5"/>
+    <col min="21" max="21" width="60" style="5" customWidth="1"/>
+    <col min="22" max="22" width="19.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="17.5" style="5" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="20.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="19.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="15.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.875" style="5" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="24.125" style="5" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="28.25" style="5" bestFit="1" customWidth="1"/>
+    <col min="31" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:30" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
@@ -2113,35 +2182,38 @@
       <c r="T2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="U2" s="5" t="s">
-        <v>75</v>
+      <c r="U2" s="33" t="s">
+        <v>300</v>
       </c>
       <c r="V2" s="5" t="s">
         <v>75</v>
       </c>
-      <c r="W2" s="1" t="s">
+      <c r="W2" s="5" t="s">
         <v>75</v>
       </c>
       <c r="X2" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="Y2" s="5" t="s">
-        <v>78</v>
+      <c r="Y2" s="1" t="s">
+        <v>75</v>
       </c>
       <c r="Z2" s="5" t="s">
         <v>78</v>
       </c>
       <c r="AA2" s="5" t="s">
+        <v>78</v>
+      </c>
+      <c r="AB2" s="5" t="s">
         <v>79</v>
-      </c>
-      <c r="AB2" s="1" t="s">
-        <v>78</v>
       </c>
       <c r="AC2" s="1" t="s">
         <v>78</v>
       </c>
+      <c r="AD2" s="1" t="s">
+        <v>78</v>
+      </c>
     </row>
-    <row r="3" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:30" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2202,35 +2274,38 @@
       <c r="T3" s="5" t="s">
         <v>14</v>
       </c>
-      <c r="U3" s="5" t="s">
+      <c r="U3" s="33" t="s">
+        <v>299</v>
+      </c>
+      <c r="V3" s="5" t="s">
         <v>36</v>
       </c>
-      <c r="V3" s="5" t="s">
+      <c r="W3" s="5" t="s">
         <v>15</v>
       </c>
-      <c r="W3" s="1" t="s">
+      <c r="X3" s="1" t="s">
         <v>42</v>
       </c>
-      <c r="X3" s="1" t="s">
+      <c r="Y3" s="1" t="s">
         <v>44</v>
       </c>
-      <c r="Y3" s="5" t="s">
+      <c r="Z3" s="5" t="s">
         <v>16</v>
       </c>
-      <c r="Z3" s="5" t="s">
+      <c r="AA3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AA3" s="5" t="s">
+      <c r="AB3" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AB3" s="1" t="s">
+      <c r="AC3" s="1" t="s">
         <v>57</v>
       </c>
-      <c r="AC3" s="1" t="s">
+      <c r="AD3" s="1" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="4" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A4" s="5" t="s">
         <v>19</v>
       </c>
@@ -2291,35 +2366,38 @@
       <c r="T4" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="U4" s="5" t="s">
+      <c r="U4" s="33" t="s">
+        <v>301</v>
+      </c>
+      <c r="V4" s="5" t="s">
         <v>37</v>
       </c>
-      <c r="V4" s="5" t="s">
+      <c r="W4" s="5" t="s">
         <v>30</v>
       </c>
-      <c r="W4" s="5" t="s">
+      <c r="X4" s="5" t="s">
         <v>43</v>
       </c>
-      <c r="X4" s="5" t="s">
+      <c r="Y4" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="Y4" s="5" t="s">
+      <c r="Z4" s="5" t="s">
         <v>31</v>
       </c>
-      <c r="Z4" s="5" t="s">
+      <c r="AA4" s="5" t="s">
         <v>32</v>
       </c>
-      <c r="AA4" s="5" t="s">
+      <c r="AB4" s="5" t="s">
         <v>33</v>
       </c>
-      <c r="AB4" s="5" t="s">
+      <c r="AC4" s="5" t="s">
         <v>59</v>
       </c>
-      <c r="AC4" s="5" t="s">
+      <c r="AD4" s="5" t="s">
         <v>60</v>
       </c>
     </row>
-    <row r="5" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>10101</v>
       </c>
@@ -2369,42 +2447,47 @@
       <c r="Q5" s="9">
         <v>2</v>
       </c>
-      <c r="R5" s="9"/>
+      <c r="R5" s="9">
+        <v>0</v>
+      </c>
       <c r="S5" s="9">
         <v>1</v>
       </c>
       <c r="T5" s="9">
         <v>0</v>
       </c>
-      <c r="U5" s="9">
+      <c r="U5" s="34">
         <v>0</v>
       </c>
       <c r="V5" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W5" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X5" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y5" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA5" s="10" t="s">
-        <v>34</v>
+        <v>10000</v>
+      </c>
+      <c r="Z5" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA5" s="10">
+        <v>0</v>
       </c>
       <c r="AB5" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC5" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AC5" s="10" t="s">
+      <c r="AD5" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="6" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>10102</v>
       </c>
@@ -2454,42 +2537,47 @@
       <c r="Q6" s="9">
         <v>2</v>
       </c>
-      <c r="R6" s="9"/>
+      <c r="R6" s="9">
+        <v>0</v>
+      </c>
       <c r="S6" s="9">
         <v>1</v>
       </c>
       <c r="T6" s="9">
         <v>0</v>
       </c>
-      <c r="U6" s="9">
+      <c r="U6" s="34">
         <v>0</v>
       </c>
       <c r="V6" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W6" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X6" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y6" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z6" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA6" s="10" t="s">
-        <v>34</v>
+        <v>10000</v>
+      </c>
+      <c r="Z6" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA6" s="10">
+        <v>0</v>
       </c>
       <c r="AB6" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC6" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AC6" s="10" t="s">
+      <c r="AD6" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>10201</v>
       </c>
@@ -2539,42 +2627,47 @@
       <c r="Q7" s="9">
         <v>2</v>
       </c>
-      <c r="R7" s="9"/>
+      <c r="R7" s="9">
+        <v>0</v>
+      </c>
       <c r="S7" s="9">
         <v>1</v>
       </c>
       <c r="T7" s="9">
         <v>0</v>
       </c>
-      <c r="U7" s="9">
+      <c r="U7" s="34">
         <v>0</v>
       </c>
       <c r="V7" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W7" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X7" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y7" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z7" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA7" s="10" t="s">
-        <v>34</v>
+        <v>10000</v>
+      </c>
+      <c r="Z7" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA7" s="10">
+        <v>0</v>
       </c>
       <c r="AB7" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC7" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AC7" s="10" t="s">
+      <c r="AD7" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="8" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>10202</v>
       </c>
@@ -2624,42 +2717,47 @@
       <c r="Q8" s="9">
         <v>2</v>
       </c>
-      <c r="R8" s="9"/>
+      <c r="R8" s="9">
+        <v>0</v>
+      </c>
       <c r="S8" s="9">
         <v>1</v>
       </c>
       <c r="T8" s="9">
         <v>0</v>
       </c>
-      <c r="U8" s="9">
+      <c r="U8" s="34">
         <v>0</v>
       </c>
       <c r="V8" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W8" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X8" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y8" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z8" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA8" s="10" t="s">
-        <v>34</v>
+        <v>10000</v>
+      </c>
+      <c r="Z8" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA8" s="10">
+        <v>0</v>
       </c>
       <c r="AB8" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC8" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AC8" s="10" t="s">
+      <c r="AD8" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="9" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>10301</v>
       </c>
@@ -2709,42 +2807,47 @@
       <c r="Q9" s="9">
         <v>2</v>
       </c>
-      <c r="R9" s="9"/>
+      <c r="R9" s="9">
+        <v>0</v>
+      </c>
       <c r="S9" s="9">
         <v>1</v>
       </c>
       <c r="T9" s="9">
         <v>0</v>
       </c>
-      <c r="U9" s="9">
+      <c r="U9" s="34">
         <v>0</v>
       </c>
       <c r="V9" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W9" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X9" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y9" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z9" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA9" s="10" t="s">
-        <v>34</v>
+        <v>10000</v>
+      </c>
+      <c r="Z9" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA9" s="10">
+        <v>0</v>
       </c>
       <c r="AB9" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC9" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AC9" s="10" t="s">
+      <c r="AD9" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="10" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>10302</v>
       </c>
@@ -2794,42 +2897,47 @@
       <c r="Q10" s="9">
         <v>2</v>
       </c>
-      <c r="R10" s="9"/>
+      <c r="R10" s="9">
+        <v>0</v>
+      </c>
       <c r="S10" s="9">
         <v>1</v>
       </c>
       <c r="T10" s="9">
         <v>0</v>
       </c>
-      <c r="U10" s="9">
+      <c r="U10" s="34">
         <v>0</v>
       </c>
       <c r="V10" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W10" s="9">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X10" s="9">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y10" s="9">
-        <v>0</v>
-      </c>
-      <c r="Z10" s="10">
-        <v>0</v>
-      </c>
-      <c r="AA10" s="10" t="s">
-        <v>34</v>
+        <v>10000</v>
+      </c>
+      <c r="Z10" s="9">
+        <v>0</v>
+      </c>
+      <c r="AA10" s="10">
+        <v>0</v>
       </c>
       <c r="AB10" s="10" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC10" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="AC10" s="10" t="s">
+      <c r="AD10" s="10" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="11" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>20001</v>
       </c>
@@ -2881,42 +2989,47 @@
       <c r="Q11" s="2">
         <v>2</v>
       </c>
-      <c r="R11" s="2"/>
+      <c r="R11" s="2">
+        <v>0</v>
+      </c>
       <c r="S11" s="2">
         <v>1</v>
       </c>
       <c r="T11" s="2">
         <v>1</v>
       </c>
-      <c r="U11" s="2">
+      <c r="U11" s="35">
         <v>0</v>
       </c>
       <c r="V11" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W11" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X11" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y11" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z11" s="2">
         <v>0</v>
       </c>
-      <c r="AA11" s="2" t="s">
-        <v>34</v>
+      <c r="AA11" s="2">
+        <v>0</v>
       </c>
       <c r="AB11" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC11" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC11" s="2" t="s">
+      <c r="AD11" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="12" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>20010001</v>
       </c>
@@ -2968,42 +3081,47 @@
       <c r="Q12" s="2">
         <v>2</v>
       </c>
-      <c r="R12" s="2"/>
+      <c r="R12" s="2">
+        <v>0</v>
+      </c>
       <c r="S12" s="2">
         <v>1</v>
       </c>
       <c r="T12" s="2">
         <v>1</v>
       </c>
-      <c r="U12" s="2">
+      <c r="U12" s="35">
         <v>0</v>
       </c>
       <c r="V12" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W12" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X12" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y12" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z12" s="2">
         <v>0</v>
       </c>
-      <c r="AA12" s="2" t="s">
-        <v>34</v>
+      <c r="AA12" s="2">
+        <v>0</v>
       </c>
       <c r="AB12" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC12" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC12" s="2" t="s">
+      <c r="AD12" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="13" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>20020001</v>
       </c>
@@ -3055,42 +3173,47 @@
       <c r="Q13" s="2">
         <v>2</v>
       </c>
-      <c r="R13" s="2"/>
+      <c r="R13" s="2">
+        <v>0</v>
+      </c>
       <c r="S13" s="2">
         <v>1</v>
       </c>
       <c r="T13" s="2">
         <v>1</v>
       </c>
-      <c r="U13" s="2">
+      <c r="U13" s="35">
         <v>0</v>
       </c>
       <c r="V13" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W13" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X13" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y13" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z13" s="2">
         <v>0</v>
       </c>
-      <c r="AA13" s="2" t="s">
-        <v>34</v>
+      <c r="AA13" s="2">
+        <v>0</v>
       </c>
       <c r="AB13" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC13" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC13" s="2" t="s">
+      <c r="AD13" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="14" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>20030001</v>
       </c>
@@ -3142,42 +3265,47 @@
       <c r="Q14" s="2">
         <v>2</v>
       </c>
-      <c r="R14" s="2"/>
+      <c r="R14" s="2">
+        <v>0</v>
+      </c>
       <c r="S14" s="2">
         <v>1</v>
       </c>
       <c r="T14" s="2">
         <v>1</v>
       </c>
-      <c r="U14" s="2">
+      <c r="U14" s="35">
         <v>0</v>
       </c>
       <c r="V14" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W14" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X14" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y14" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z14" s="2">
         <v>0</v>
       </c>
-      <c r="AA14" s="2" t="s">
-        <v>34</v>
+      <c r="AA14" s="2">
+        <v>0</v>
       </c>
       <c r="AB14" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC14" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC14" s="2" t="s">
+      <c r="AD14" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="15" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>20040001</v>
       </c>
@@ -3229,42 +3357,47 @@
       <c r="Q15" s="2">
         <v>2</v>
       </c>
-      <c r="R15" s="2"/>
+      <c r="R15" s="2">
+        <v>0</v>
+      </c>
       <c r="S15" s="2">
         <v>1</v>
       </c>
       <c r="T15" s="2">
         <v>1</v>
       </c>
-      <c r="U15" s="2">
+      <c r="U15" s="35">
         <v>0</v>
       </c>
       <c r="V15" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W15" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X15" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y15" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z15" s="2">
         <v>0</v>
       </c>
-      <c r="AA15" s="2" t="s">
-        <v>34</v>
+      <c r="AA15" s="2">
+        <v>0</v>
       </c>
       <c r="AB15" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC15" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC15" s="2" t="s">
+      <c r="AD15" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="16" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>20050001</v>
       </c>
@@ -3316,42 +3449,47 @@
       <c r="Q16" s="2">
         <v>2</v>
       </c>
-      <c r="R16" s="2"/>
+      <c r="R16" s="2">
+        <v>0</v>
+      </c>
       <c r="S16" s="2">
         <v>1</v>
       </c>
       <c r="T16" s="2">
         <v>1</v>
       </c>
-      <c r="U16" s="2">
+      <c r="U16" s="35">
         <v>0</v>
       </c>
       <c r="V16" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W16" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X16" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y16" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z16" s="2">
         <v>0</v>
       </c>
-      <c r="AA16" s="2" t="s">
-        <v>34</v>
+      <c r="AA16" s="2">
+        <v>0</v>
       </c>
       <c r="AB16" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC16" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC16" s="2" t="s">
+      <c r="AD16" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="17" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>20060001</v>
       </c>
@@ -3403,42 +3541,47 @@
       <c r="Q17" s="2">
         <v>2</v>
       </c>
-      <c r="R17" s="2"/>
+      <c r="R17" s="2">
+        <v>0</v>
+      </c>
       <c r="S17" s="2">
         <v>1</v>
       </c>
       <c r="T17" s="2">
         <v>1</v>
       </c>
-      <c r="U17" s="2">
+      <c r="U17" s="35">
         <v>0</v>
       </c>
       <c r="V17" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W17" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X17" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y17" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z17" s="2">
         <v>0</v>
       </c>
-      <c r="AA17" s="2" t="s">
-        <v>34</v>
+      <c r="AA17" s="2">
+        <v>0</v>
       </c>
       <c r="AB17" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC17" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC17" s="2" t="s">
+      <c r="AD17" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="18" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>20070001</v>
       </c>
@@ -3490,42 +3633,47 @@
       <c r="Q18" s="2">
         <v>2</v>
       </c>
-      <c r="R18" s="2"/>
+      <c r="R18" s="2">
+        <v>0</v>
+      </c>
       <c r="S18" s="2">
         <v>1</v>
       </c>
       <c r="T18" s="2">
         <v>1</v>
       </c>
-      <c r="U18" s="2">
+      <c r="U18" s="35">
         <v>0</v>
       </c>
       <c r="V18" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W18" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X18" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y18" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z18" s="2">
         <v>0</v>
       </c>
-      <c r="AA18" s="2" t="s">
-        <v>34</v>
+      <c r="AA18" s="2">
+        <v>0</v>
       </c>
       <c r="AB18" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC18" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC18" s="2" t="s">
+      <c r="AD18" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>20080001</v>
       </c>
@@ -3577,7 +3725,9 @@
       <c r="Q19" s="2">
         <v>2</v>
       </c>
-      <c r="R19" s="2"/>
+      <c r="R19" s="2">
+        <v>0</v>
+      </c>
       <c r="S19" s="2">
         <v>1</v>
       </c>
@@ -3588,31 +3738,34 @@
         <v>0</v>
       </c>
       <c r="V19" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W19" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X19" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y19" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z19" s="2">
         <v>0</v>
       </c>
-      <c r="AA19" s="2" t="s">
-        <v>34</v>
+      <c r="AA19" s="2">
+        <v>0</v>
       </c>
       <c r="AB19" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC19" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC19" s="2" t="s">
+      <c r="AD19" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="20" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>20090001</v>
       </c>
@@ -3664,7 +3817,9 @@
       <c r="Q20" s="2">
         <v>2</v>
       </c>
-      <c r="R20" s="2"/>
+      <c r="R20" s="2">
+        <v>0</v>
+      </c>
       <c r="S20" s="2">
         <v>1</v>
       </c>
@@ -3675,31 +3830,34 @@
         <v>0</v>
       </c>
       <c r="V20" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W20" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X20" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y20" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z20" s="2">
         <v>0</v>
       </c>
-      <c r="AA20" s="2" t="s">
-        <v>34</v>
+      <c r="AA20" s="2">
+        <v>0</v>
       </c>
       <c r="AB20" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC20" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC20" s="2" t="s">
+      <c r="AD20" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="21" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20100001</v>
       </c>
@@ -3751,7 +3909,9 @@
       <c r="Q21" s="2">
         <v>2</v>
       </c>
-      <c r="R21" s="2"/>
+      <c r="R21" s="2">
+        <v>0</v>
+      </c>
       <c r="S21" s="2">
         <v>1</v>
       </c>
@@ -3762,31 +3922,34 @@
         <v>0</v>
       </c>
       <c r="V21" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W21" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X21" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y21" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z21" s="2">
         <v>0</v>
       </c>
-      <c r="AA21" s="2" t="s">
-        <v>34</v>
+      <c r="AA21" s="2">
+        <v>0</v>
       </c>
       <c r="AB21" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC21" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC21" s="2" t="s">
+      <c r="AD21" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="22" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20110001</v>
       </c>
@@ -3838,7 +4001,9 @@
       <c r="Q22" s="2">
         <v>2</v>
       </c>
-      <c r="R22" s="2"/>
+      <c r="R22" s="2">
+        <v>0</v>
+      </c>
       <c r="S22" s="2">
         <v>1</v>
       </c>
@@ -3849,31 +4014,34 @@
         <v>0</v>
       </c>
       <c r="V22" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W22" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X22" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y22" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z22" s="2">
         <v>0</v>
       </c>
-      <c r="AA22" s="2" t="s">
-        <v>34</v>
+      <c r="AA22" s="2">
+        <v>0</v>
       </c>
       <c r="AB22" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC22" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC22" s="2" t="s">
+      <c r="AD22" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="23" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20120001</v>
       </c>
@@ -3925,7 +4093,9 @@
       <c r="Q23" s="2">
         <v>2</v>
       </c>
-      <c r="R23" s="2"/>
+      <c r="R23" s="2">
+        <v>0</v>
+      </c>
       <c r="S23" s="2">
         <v>1</v>
       </c>
@@ -3936,31 +4106,34 @@
         <v>0</v>
       </c>
       <c r="V23" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W23" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X23" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y23" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z23" s="2">
         <v>0</v>
       </c>
-      <c r="AA23" s="2" t="s">
-        <v>34</v>
+      <c r="AA23" s="2">
+        <v>0</v>
       </c>
       <c r="AB23" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC23" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC23" s="2" t="s">
+      <c r="AD23" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="24" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>20130001</v>
       </c>
@@ -4012,7 +4185,9 @@
       <c r="Q24" s="2">
         <v>2</v>
       </c>
-      <c r="R24" s="2"/>
+      <c r="R24" s="2">
+        <v>0</v>
+      </c>
       <c r="S24" s="2">
         <v>1</v>
       </c>
@@ -4023,31 +4198,34 @@
         <v>0</v>
       </c>
       <c r="V24" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W24" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X24" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y24" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z24" s="2">
         <v>0</v>
       </c>
-      <c r="AA24" s="2" t="s">
-        <v>34</v>
+      <c r="AA24" s="2">
+        <v>0</v>
       </c>
       <c r="AB24" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC24" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC24" s="2" t="s">
+      <c r="AD24" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="25" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>20140001</v>
       </c>
@@ -4099,7 +4277,9 @@
       <c r="Q25" s="2">
         <v>2</v>
       </c>
-      <c r="R25" s="2"/>
+      <c r="R25" s="2">
+        <v>0</v>
+      </c>
       <c r="S25" s="2">
         <v>1</v>
       </c>
@@ -4110,31 +4290,34 @@
         <v>0</v>
       </c>
       <c r="V25" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W25" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X25" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y25" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z25" s="2">
         <v>0</v>
       </c>
-      <c r="AA25" s="2" t="s">
-        <v>34</v>
+      <c r="AA25" s="2">
+        <v>0</v>
       </c>
       <c r="AB25" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC25" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC25" s="2" t="s">
+      <c r="AD25" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="26" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>20150001</v>
       </c>
@@ -4186,7 +4369,9 @@
       <c r="Q26" s="2">
         <v>2</v>
       </c>
-      <c r="R26" s="2"/>
+      <c r="R26" s="2">
+        <v>0</v>
+      </c>
       <c r="S26" s="2">
         <v>1</v>
       </c>
@@ -4197,31 +4382,34 @@
         <v>0</v>
       </c>
       <c r="V26" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W26" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X26" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y26" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z26" s="2">
         <v>0</v>
       </c>
-      <c r="AA26" s="2" t="s">
-        <v>34</v>
+      <c r="AA26" s="2">
+        <v>0</v>
       </c>
       <c r="AB26" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC26" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC26" s="2" t="s">
+      <c r="AD26" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="27" spans="1:29" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>20160001</v>
       </c>
@@ -4273,7 +4461,9 @@
       <c r="Q27" s="2">
         <v>2</v>
       </c>
-      <c r="R27" s="2"/>
+      <c r="R27" s="2">
+        <v>0</v>
+      </c>
       <c r="S27" s="2">
         <v>1</v>
       </c>
@@ -4284,400 +4474,419 @@
         <v>0</v>
       </c>
       <c r="V27" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W27" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X27" s="2">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y27" s="2">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z27" s="2">
         <v>0</v>
       </c>
-      <c r="AA27" s="2" t="s">
-        <v>34</v>
+      <c r="AA27" s="2">
+        <v>0</v>
       </c>
       <c r="AB27" s="2" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC27" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="AC27" s="2" t="s">
+      <c r="AD27" s="2" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="28" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A28" s="3">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A28" s="23">
+        <v>25010001</v>
+      </c>
+      <c r="B28" s="23">
+        <v>2</v>
+      </c>
+      <c r="C28" s="23">
+        <v>2501</v>
+      </c>
+      <c r="D28" s="23">
+        <v>1</v>
+      </c>
+      <c r="E28" s="18" t="s">
+        <v>296</v>
+      </c>
+      <c r="F28" s="23" t="s">
+        <v>297</v>
+      </c>
+      <c r="G28" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H28" s="23" t="s">
+        <v>298</v>
+      </c>
+      <c r="I28" s="23">
+        <v>0</v>
+      </c>
+      <c r="J28" s="23">
+        <v>1000</v>
+      </c>
+      <c r="K28" s="23">
+        <v>1000</v>
+      </c>
+      <c r="L28" s="23">
+        <v>0</v>
+      </c>
+      <c r="M28" s="23">
+        <v>10000</v>
+      </c>
+      <c r="N28" s="23">
+        <v>0</v>
+      </c>
+      <c r="O28" s="23">
+        <v>0</v>
+      </c>
+      <c r="P28" s="23">
+        <v>2</v>
+      </c>
+      <c r="Q28" s="23">
+        <v>1</v>
+      </c>
+      <c r="R28" s="23">
+        <v>0</v>
+      </c>
+      <c r="S28" s="23">
+        <v>1</v>
+      </c>
+      <c r="T28" s="23">
+        <v>0</v>
+      </c>
+      <c r="U28" s="23">
+        <v>0</v>
+      </c>
+      <c r="V28" s="23">
+        <v>0</v>
+      </c>
+      <c r="W28" s="23">
+        <v>0</v>
+      </c>
+      <c r="X28" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y28" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z28" s="23">
+        <v>54150001</v>
+      </c>
+      <c r="AA28" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB28" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC28" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD28" s="23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A29" s="3">
         <v>30001</v>
       </c>
-      <c r="B28" s="3">
+      <c r="B29" s="3">
         <v>3</v>
       </c>
-      <c r="C28" s="3">
+      <c r="C29" s="3">
         <v>3</v>
       </c>
-      <c r="D28" s="3">
-        <v>1</v>
-      </c>
-      <c r="E28" s="4" t="s">
+      <c r="D29" s="3">
+        <v>1</v>
+      </c>
+      <c r="E29" s="4" t="s">
         <v>175</v>
       </c>
-      <c r="F28" s="3" t="s">
+      <c r="F29" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="G28" s="3" t="s">
+      <c r="G29" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="H28" s="3" t="s">
+      <c r="H29" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="I28" s="3">
-        <v>0</v>
-      </c>
-      <c r="J28" s="3">
-        <v>0</v>
-      </c>
-      <c r="K28" s="3">
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
+      </c>
+      <c r="K29" s="3">
         <v>20000</v>
       </c>
-      <c r="L28" s="3">
-        <v>0</v>
-      </c>
-      <c r="M28" s="3">
-        <v>10000</v>
-      </c>
-      <c r="N28" s="3">
-        <v>0</v>
-      </c>
-      <c r="O28" s="3">
-        <v>1</v>
-      </c>
-      <c r="P28" s="3">
+      <c r="L29" s="3">
+        <v>0</v>
+      </c>
+      <c r="M29" s="3">
+        <v>10000</v>
+      </c>
+      <c r="N29" s="3">
+        <v>0</v>
+      </c>
+      <c r="O29" s="3">
+        <v>1</v>
+      </c>
+      <c r="P29" s="3">
         <v>2</v>
       </c>
-      <c r="Q28" s="3">
-        <v>1</v>
-      </c>
-      <c r="R28" s="3"/>
-      <c r="S28" s="3">
-        <v>1</v>
-      </c>
-      <c r="T28" s="3">
+      <c r="Q29" s="3">
+        <v>1</v>
+      </c>
+      <c r="R29" s="3">
+        <v>0</v>
+      </c>
+      <c r="S29" s="3">
+        <v>1</v>
+      </c>
+      <c r="T29" s="3">
         <v>3</v>
       </c>
-      <c r="U28" s="3">
-        <v>0</v>
-      </c>
-      <c r="V28" s="3">
-        <v>0</v>
-      </c>
-      <c r="W28" s="3">
-        <v>0</v>
-      </c>
-      <c r="X28" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y28" s="3">
+      <c r="U29" s="3">
+        <v>0</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z29" s="3">
         <v>1000001</v>
       </c>
-      <c r="Z28" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA28" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB28" s="3" t="s">
+      <c r="AA29" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB29" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC29" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AC28" s="3" t="s">
+      <c r="AD29" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="29" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A29" s="3">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A30" s="3">
         <v>4000001</v>
       </c>
-      <c r="B29" s="3">
+      <c r="B30" s="3">
         <v>4</v>
       </c>
-      <c r="C29" s="3">
+      <c r="C30" s="3">
         <v>400</v>
       </c>
-      <c r="D29" s="3">
-        <v>1</v>
-      </c>
-      <c r="E29" s="4" t="s">
+      <c r="D30" s="3">
+        <v>1</v>
+      </c>
+      <c r="E30" s="4" t="s">
         <v>80</v>
       </c>
-      <c r="F29" s="3" t="s">
+      <c r="F30" s="3" t="s">
         <v>117</v>
       </c>
-      <c r="G29" s="3" t="s">
+      <c r="G30" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="H29" s="3" t="s">
+      <c r="H30" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
-      </c>
-      <c r="K29" s="3">
-        <v>0</v>
-      </c>
-      <c r="L29" s="3">
-        <v>0</v>
-      </c>
-      <c r="M29" s="3">
-        <v>0</v>
-      </c>
-      <c r="N29" s="3">
-        <v>0</v>
-      </c>
-      <c r="O29" s="3">
-        <v>0</v>
-      </c>
-      <c r="P29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Q29" s="3">
-        <v>0</v>
-      </c>
-      <c r="R29" s="3">
-        <v>0</v>
-      </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3">
+      <c r="I30" s="3">
+        <v>0</v>
+      </c>
+      <c r="J30" s="3">
+        <v>0</v>
+      </c>
+      <c r="K30" s="3">
+        <v>0</v>
+      </c>
+      <c r="L30" s="3">
+        <v>0</v>
+      </c>
+      <c r="M30" s="3">
+        <v>0</v>
+      </c>
+      <c r="N30" s="3">
+        <v>0</v>
+      </c>
+      <c r="O30" s="3">
+        <v>0</v>
+      </c>
+      <c r="P30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q30" s="3">
+        <v>0</v>
+      </c>
+      <c r="R30" s="3">
+        <v>0</v>
+      </c>
+      <c r="S30" s="3">
+        <v>0</v>
+      </c>
+      <c r="T30" s="3">
+        <v>0</v>
+      </c>
+      <c r="U30" s="3">
+        <v>0</v>
+      </c>
+      <c r="V30" s="3">
+        <v>0</v>
+      </c>
+      <c r="W30" s="3">
+        <v>0</v>
+      </c>
+      <c r="X30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y30" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z30" s="3">
         <v>2000001</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AA30" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB30" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC30" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="AC29" s="3" t="s">
+      <c r="AD30" s="3" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="30" spans="1:29" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
-      <c r="A30" s="21">
+    <row r="31" spans="1:30" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+      <c r="A31" s="21">
         <v>5000001</v>
       </c>
-      <c r="B30" s="21">
+      <c r="B31" s="21">
         <v>5</v>
       </c>
-      <c r="C30" s="21">
+      <c r="C31" s="21">
         <v>500</v>
       </c>
-      <c r="D30" s="21">
-        <v>1</v>
-      </c>
-      <c r="E30" s="22" t="s">
+      <c r="D31" s="21">
+        <v>1</v>
+      </c>
+      <c r="E31" s="22" t="s">
         <v>118</v>
       </c>
-      <c r="F30" s="21" t="s">
+      <c r="F31" s="21" t="s">
         <v>84</v>
       </c>
-      <c r="G30" s="21" t="s">
+      <c r="G31" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="H30" s="21" t="s">
+      <c r="H31" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="I30" s="21">
+      <c r="I31" s="21">
         <v>8000</v>
       </c>
-      <c r="J30" s="21">
+      <c r="J31" s="21">
         <v>800</v>
       </c>
-      <c r="K30" s="21">
+      <c r="K31" s="21">
         <v>8000</v>
       </c>
-      <c r="L30" s="21">
-        <v>0</v>
-      </c>
-      <c r="M30" s="21">
-        <v>10000</v>
-      </c>
-      <c r="N30" s="21">
-        <v>0</v>
-      </c>
-      <c r="O30" s="21">
-        <v>0</v>
-      </c>
-      <c r="P30" s="21">
+      <c r="L31" s="21">
+        <v>0</v>
+      </c>
+      <c r="M31" s="21">
+        <v>10000</v>
+      </c>
+      <c r="N31" s="21">
+        <v>0</v>
+      </c>
+      <c r="O31" s="21">
+        <v>0</v>
+      </c>
+      <c r="P31" s="21">
         <v>3</v>
       </c>
-      <c r="Q30" s="21">
+      <c r="Q31" s="21">
         <v>2</v>
       </c>
-      <c r="R30" s="21">
+      <c r="R31" s="21">
         <v>5000</v>
       </c>
-      <c r="S30" s="21">
+      <c r="S31" s="21">
         <v>9</v>
       </c>
-      <c r="T30" s="21">
-        <v>1</v>
-      </c>
-      <c r="U30" s="21">
-        <v>0</v>
-      </c>
-      <c r="V30" s="21">
-        <v>20000</v>
-      </c>
-      <c r="W30" s="21">
-        <v>0</v>
-      </c>
-      <c r="X30" s="21">
+      <c r="T31" s="21">
+        <v>1</v>
+      </c>
+      <c r="U31" s="21">
+        <v>1</v>
+      </c>
+      <c r="V31" s="21">
+        <v>0</v>
+      </c>
+      <c r="W31" s="21">
         <v>12000</v>
       </c>
-      <c r="Y30" s="21">
-        <v>0</v>
-      </c>
-      <c r="Z30" s="21">
+      <c r="X31" s="21">
+        <v>0</v>
+      </c>
+      <c r="Y31" s="21">
+        <v>8000</v>
+      </c>
+      <c r="Z31" s="21">
+        <v>0</v>
+      </c>
+      <c r="AA31" s="21">
         <v>55010001</v>
       </c>
-      <c r="AA30" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB30" s="21" t="s">
+      <c r="AB31" s="21" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC31" s="21" t="s">
         <v>61</v>
       </c>
-      <c r="AC30" s="21" t="s">
+      <c r="AD31" s="21" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="31" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A31" s="17">
+    <row r="32" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A32" s="17">
         <v>6000001</v>
-      </c>
-      <c r="B31" s="17">
-        <v>5</v>
-      </c>
-      <c r="C31" s="17">
-        <v>600</v>
-      </c>
-      <c r="D31" s="17">
-        <v>1</v>
-      </c>
-      <c r="E31" s="18" t="s">
-        <v>136</v>
-      </c>
-      <c r="F31" s="17" t="s">
-        <v>129</v>
-      </c>
-      <c r="G31" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="H31" s="17"/>
-      <c r="I31" s="17">
-        <v>100</v>
-      </c>
-      <c r="J31" s="17">
-        <v>100</v>
-      </c>
-      <c r="K31" s="17">
-        <v>100</v>
-      </c>
-      <c r="L31" s="17">
-        <v>0</v>
-      </c>
-      <c r="M31" s="17">
-        <v>10000</v>
-      </c>
-      <c r="N31" s="17">
-        <v>0</v>
-      </c>
-      <c r="O31" s="17">
-        <v>0</v>
-      </c>
-      <c r="P31" s="17">
-        <v>3</v>
-      </c>
-      <c r="Q31" s="17">
-        <v>2</v>
-      </c>
-      <c r="R31" s="17">
-        <v>0</v>
-      </c>
-      <c r="S31" s="17">
-        <v>9</v>
-      </c>
-      <c r="T31" s="17">
-        <v>0</v>
-      </c>
-      <c r="U31" s="17">
-        <v>150</v>
-      </c>
-      <c r="V31" s="17">
-        <v>15000</v>
-      </c>
-      <c r="W31" s="17">
-        <v>120</v>
-      </c>
-      <c r="X31" s="17">
-        <v>12000</v>
-      </c>
-      <c r="Y31" s="17">
-        <v>0</v>
-      </c>
-      <c r="Z31" s="17">
-        <v>56010001</v>
-      </c>
-      <c r="AA31" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB31" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC31" s="17" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="32" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A32" s="17">
-        <v>6010001</v>
       </c>
       <c r="B32" s="17">
         <v>5</v>
       </c>
       <c r="C32" s="17">
-        <v>601</v>
+        <v>600</v>
       </c>
       <c r="D32" s="17">
         <v>1</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="G32" s="17" t="s">
         <v>34</v>
@@ -4702,7 +4911,7 @@
         <v>0</v>
       </c>
       <c r="O32" s="17">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P32" s="17">
         <v>3</v>
@@ -4720,138 +4929,144 @@
         <v>0</v>
       </c>
       <c r="U32" s="17">
+        <v>2</v>
+      </c>
+      <c r="V32" s="17">
         <v>150</v>
       </c>
-      <c r="V32" s="17">
+      <c r="W32" s="17">
         <v>15000</v>
       </c>
-      <c r="W32" s="17">
+      <c r="X32" s="17">
         <v>120</v>
       </c>
-      <c r="X32" s="17">
+      <c r="Y32" s="17">
         <v>12000</v>
       </c>
-      <c r="Y32" s="17">
-        <v>0</v>
-      </c>
       <c r="Z32" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA32" s="17">
         <v>56010001</v>
       </c>
-      <c r="AA32" s="17" t="s">
-        <v>34</v>
-      </c>
       <c r="AB32" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC32" s="17" t="s">
         <v>61</v>
       </c>
-      <c r="AC32" s="17" t="s">
+      <c r="AD32" s="17" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="33" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A33" s="19">
+    <row r="33" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A33" s="17">
+        <v>6010001</v>
+      </c>
+      <c r="B33" s="17">
+        <v>5</v>
+      </c>
+      <c r="C33" s="17">
+        <v>601</v>
+      </c>
+      <c r="D33" s="17">
+        <v>1</v>
+      </c>
+      <c r="E33" s="18" t="s">
+        <v>141</v>
+      </c>
+      <c r="F33" s="17" t="s">
+        <v>130</v>
+      </c>
+      <c r="G33" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="H33" s="17"/>
+      <c r="I33" s="17">
+        <v>100</v>
+      </c>
+      <c r="J33" s="17">
+        <v>100</v>
+      </c>
+      <c r="K33" s="17">
+        <v>100</v>
+      </c>
+      <c r="L33" s="17">
+        <v>0</v>
+      </c>
+      <c r="M33" s="17">
+        <v>10000</v>
+      </c>
+      <c r="N33" s="17">
+        <v>0</v>
+      </c>
+      <c r="O33" s="17">
+        <v>1</v>
+      </c>
+      <c r="P33" s="17">
+        <v>3</v>
+      </c>
+      <c r="Q33" s="17">
+        <v>2</v>
+      </c>
+      <c r="R33" s="17">
+        <v>0</v>
+      </c>
+      <c r="S33" s="17">
+        <v>9</v>
+      </c>
+      <c r="T33" s="17">
+        <v>0</v>
+      </c>
+      <c r="U33" s="17">
+        <v>2</v>
+      </c>
+      <c r="V33" s="17">
+        <v>150</v>
+      </c>
+      <c r="W33" s="17">
+        <v>15000</v>
+      </c>
+      <c r="X33" s="17">
+        <v>120</v>
+      </c>
+      <c r="Y33" s="17">
+        <v>12000</v>
+      </c>
+      <c r="Z33" s="17">
+        <v>0</v>
+      </c>
+      <c r="AA33" s="17">
+        <v>56010001</v>
+      </c>
+      <c r="AB33" s="17" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC33" s="17" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD33" s="17" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="34" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A34" s="19">
         <v>7000001</v>
-      </c>
-      <c r="B33" s="19">
-        <v>5</v>
-      </c>
-      <c r="C33" s="19">
-        <v>700</v>
-      </c>
-      <c r="D33" s="19">
-        <v>1</v>
-      </c>
-      <c r="E33" s="18" t="s">
-        <v>143</v>
-      </c>
-      <c r="F33" s="19" t="s">
-        <v>131</v>
-      </c>
-      <c r="G33" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="H33" s="19"/>
-      <c r="I33" s="19">
-        <v>100</v>
-      </c>
-      <c r="J33" s="19">
-        <v>100</v>
-      </c>
-      <c r="K33" s="19">
-        <v>100</v>
-      </c>
-      <c r="L33" s="19">
-        <v>0</v>
-      </c>
-      <c r="M33" s="19">
-        <v>10000</v>
-      </c>
-      <c r="N33" s="19">
-        <v>0</v>
-      </c>
-      <c r="O33" s="19">
-        <v>0</v>
-      </c>
-      <c r="P33" s="19">
-        <v>3</v>
-      </c>
-      <c r="Q33" s="19">
-        <v>2</v>
-      </c>
-      <c r="R33" s="19">
-        <v>0</v>
-      </c>
-      <c r="S33" s="19">
-        <v>1</v>
-      </c>
-      <c r="T33" s="19">
-        <v>0</v>
-      </c>
-      <c r="U33" s="19">
-        <v>150</v>
-      </c>
-      <c r="V33" s="19">
-        <v>15000</v>
-      </c>
-      <c r="W33" s="19">
-        <v>120</v>
-      </c>
-      <c r="X33" s="19">
-        <v>12000</v>
-      </c>
-      <c r="Y33" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z33" s="19">
-        <v>57010001</v>
-      </c>
-      <c r="AA33" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB33" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC33" s="19" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="34" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A34" s="19">
-        <v>7010001</v>
       </c>
       <c r="B34" s="19">
         <v>5</v>
       </c>
       <c r="C34" s="19">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D34" s="19">
         <v>1</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>149</v>
+        <v>143</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G34" s="19" t="s">
         <v>34</v>
@@ -4876,7 +5091,7 @@
         <v>0</v>
       </c>
       <c r="O34" s="19">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P34" s="19">
         <v>3</v>
@@ -4888,144 +5103,150 @@
         <v>0</v>
       </c>
       <c r="S34" s="19">
+        <v>1</v>
+      </c>
+      <c r="T34" s="19">
+        <v>0</v>
+      </c>
+      <c r="U34" s="19">
+        <v>4</v>
+      </c>
+      <c r="V34" s="19">
+        <v>150</v>
+      </c>
+      <c r="W34" s="19">
+        <v>15000</v>
+      </c>
+      <c r="X34" s="19">
+        <v>120</v>
+      </c>
+      <c r="Y34" s="19">
+        <v>12000</v>
+      </c>
+      <c r="Z34" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA34" s="19">
+        <v>57010001</v>
+      </c>
+      <c r="AB34" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC34" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD34" s="19" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="35" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A35" s="19">
+        <v>7010001</v>
+      </c>
+      <c r="B35" s="19">
+        <v>5</v>
+      </c>
+      <c r="C35" s="19">
+        <v>701</v>
+      </c>
+      <c r="D35" s="19">
+        <v>1</v>
+      </c>
+      <c r="E35" s="18" t="s">
+        <v>149</v>
+      </c>
+      <c r="F35" s="19" t="s">
+        <v>132</v>
+      </c>
+      <c r="G35" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="H35" s="19"/>
+      <c r="I35" s="19">
+        <v>100</v>
+      </c>
+      <c r="J35" s="19">
+        <v>100</v>
+      </c>
+      <c r="K35" s="19">
+        <v>100</v>
+      </c>
+      <c r="L35" s="19">
+        <v>0</v>
+      </c>
+      <c r="M35" s="19">
+        <v>10000</v>
+      </c>
+      <c r="N35" s="19">
+        <v>0</v>
+      </c>
+      <c r="O35" s="19">
+        <v>1</v>
+      </c>
+      <c r="P35" s="19">
+        <v>3</v>
+      </c>
+      <c r="Q35" s="19">
+        <v>2</v>
+      </c>
+      <c r="R35" s="19">
+        <v>0</v>
+      </c>
+      <c r="S35" s="19">
         <v>9</v>
       </c>
-      <c r="T34" s="19">
-        <v>0</v>
-      </c>
-      <c r="U34" s="19">
+      <c r="T35" s="19">
+        <v>0</v>
+      </c>
+      <c r="U35" s="19">
+        <v>4</v>
+      </c>
+      <c r="V35" s="19">
         <v>150</v>
       </c>
-      <c r="V34" s="19">
+      <c r="W35" s="19">
         <v>15000</v>
       </c>
-      <c r="W34" s="19">
+      <c r="X35" s="19">
         <v>120</v>
       </c>
-      <c r="X34" s="19">
+      <c r="Y35" s="19">
         <v>12000</v>
       </c>
-      <c r="Y34" s="19">
-        <v>0</v>
-      </c>
-      <c r="Z34" s="19">
+      <c r="Z35" s="19">
+        <v>0</v>
+      </c>
+      <c r="AA35" s="19">
         <v>57010001</v>
       </c>
-      <c r="AA34" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB34" s="19" t="s">
+      <c r="AB35" s="19" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC35" s="19" t="s">
         <v>61</v>
       </c>
-      <c r="AC34" s="19" t="s">
+      <c r="AD35" s="19" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="35" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A35" s="20">
+    <row r="36" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A36" s="20">
         <v>8000001</v>
-      </c>
-      <c r="B35" s="20">
-        <v>5</v>
-      </c>
-      <c r="C35" s="20">
-        <v>800</v>
-      </c>
-      <c r="D35" s="20">
-        <v>1</v>
-      </c>
-      <c r="E35" s="18" t="s">
-        <v>151</v>
-      </c>
-      <c r="F35" s="20" t="s">
-        <v>133</v>
-      </c>
-      <c r="G35" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="H35" s="20"/>
-      <c r="I35" s="20">
-        <v>100</v>
-      </c>
-      <c r="J35" s="20">
-        <v>100</v>
-      </c>
-      <c r="K35" s="20">
-        <v>100</v>
-      </c>
-      <c r="L35" s="20">
-        <v>0</v>
-      </c>
-      <c r="M35" s="20">
-        <v>10000</v>
-      </c>
-      <c r="N35" s="20">
-        <v>0</v>
-      </c>
-      <c r="O35" s="20">
-        <v>0</v>
-      </c>
-      <c r="P35" s="20">
-        <v>3</v>
-      </c>
-      <c r="Q35" s="20">
-        <v>2</v>
-      </c>
-      <c r="R35" s="20">
-        <v>0</v>
-      </c>
-      <c r="S35" s="20">
-        <v>9</v>
-      </c>
-      <c r="T35" s="20">
-        <v>0</v>
-      </c>
-      <c r="U35" s="20">
-        <v>150</v>
-      </c>
-      <c r="V35" s="20">
-        <v>15000</v>
-      </c>
-      <c r="W35" s="20">
-        <v>120</v>
-      </c>
-      <c r="X35" s="20">
-        <v>12000</v>
-      </c>
-      <c r="Y35" s="20">
-        <v>0</v>
-      </c>
-      <c r="Z35" s="20">
-        <v>58010001</v>
-      </c>
-      <c r="AA35" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB35" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC35" s="20" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="36" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A36" s="20">
-        <v>8010001</v>
       </c>
       <c r="B36" s="20">
         <v>5</v>
       </c>
       <c r="C36" s="20">
-        <v>801</v>
+        <v>800</v>
       </c>
       <c r="D36" s="20">
         <v>1</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="G36" s="20" t="s">
         <v>34</v>
@@ -5050,7 +5271,7 @@
         <v>0</v>
       </c>
       <c r="O36" s="20">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P36" s="20">
         <v>3</v>
@@ -5068,225 +5289,234 @@
         <v>0</v>
       </c>
       <c r="U36" s="20">
+        <v>3</v>
+      </c>
+      <c r="V36" s="20">
         <v>150</v>
       </c>
-      <c r="V36" s="20">
+      <c r="W36" s="20">
         <v>15000</v>
       </c>
-      <c r="W36" s="20">
+      <c r="X36" s="20">
         <v>120</v>
       </c>
-      <c r="X36" s="20">
+      <c r="Y36" s="20">
         <v>12000</v>
       </c>
-      <c r="Y36" s="20">
-        <v>0</v>
-      </c>
       <c r="Z36" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA36" s="20">
+        <v>58010001</v>
+      </c>
+      <c r="AB36" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC36" s="20" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD36" s="20" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="37" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A37" s="20">
+        <v>8010001</v>
+      </c>
+      <c r="B37" s="20">
+        <v>5</v>
+      </c>
+      <c r="C37" s="20">
+        <v>801</v>
+      </c>
+      <c r="D37" s="20">
+        <v>1</v>
+      </c>
+      <c r="E37" s="18" t="s">
+        <v>154</v>
+      </c>
+      <c r="F37" s="20" t="s">
+        <v>134</v>
+      </c>
+      <c r="G37" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="H37" s="20"/>
+      <c r="I37" s="20">
+        <v>100</v>
+      </c>
+      <c r="J37" s="20">
+        <v>100</v>
+      </c>
+      <c r="K37" s="20">
+        <v>100</v>
+      </c>
+      <c r="L37" s="20">
+        <v>0</v>
+      </c>
+      <c r="M37" s="20">
+        <v>10000</v>
+      </c>
+      <c r="N37" s="20">
+        <v>0</v>
+      </c>
+      <c r="O37" s="20">
+        <v>1</v>
+      </c>
+      <c r="P37" s="20">
+        <v>3</v>
+      </c>
+      <c r="Q37" s="20">
+        <v>2</v>
+      </c>
+      <c r="R37" s="20">
+        <v>0</v>
+      </c>
+      <c r="S37" s="20">
+        <v>9</v>
+      </c>
+      <c r="T37" s="20">
+        <v>0</v>
+      </c>
+      <c r="U37" s="20">
+        <v>3</v>
+      </c>
+      <c r="V37" s="20">
+        <v>150</v>
+      </c>
+      <c r="W37" s="20">
+        <v>15000</v>
+      </c>
+      <c r="X37" s="20">
+        <v>120</v>
+      </c>
+      <c r="Y37" s="20">
+        <v>12000</v>
+      </c>
+      <c r="Z37" s="20">
+        <v>0</v>
+      </c>
+      <c r="AA37" s="20">
         <v>58050001</v>
       </c>
-      <c r="AA36" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB36" s="20" t="s">
+      <c r="AB37" s="20" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC37" s="20" t="s">
         <v>61</v>
       </c>
-      <c r="AC36" s="20" t="s">
+      <c r="AD37" s="20" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="37" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A37" s="28">
+    <row r="38" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A38" s="28">
         <v>9000001</v>
       </c>
-      <c r="B37" s="28">
+      <c r="B38" s="28">
         <v>5</v>
       </c>
-      <c r="C37" s="28">
+      <c r="C38" s="28">
         <v>900</v>
       </c>
-      <c r="D37" s="28">
-        <v>1</v>
-      </c>
-      <c r="E37" s="18" t="s">
+      <c r="D38" s="28">
+        <v>1</v>
+      </c>
+      <c r="E38" s="18" t="s">
         <v>218</v>
       </c>
-      <c r="F37" s="28" t="s">
+      <c r="F38" s="28" t="s">
         <v>116</v>
       </c>
-      <c r="G37" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="H37" s="28"/>
-      <c r="I37" s="28">
+      <c r="G38" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="H38" s="28"/>
+      <c r="I38" s="28">
         <v>100</v>
       </c>
-      <c r="J37" s="28">
+      <c r="J38" s="28">
         <v>100</v>
       </c>
-      <c r="K37" s="28">
+      <c r="K38" s="28">
         <v>100</v>
       </c>
-      <c r="L37" s="28">
-        <v>0</v>
-      </c>
-      <c r="M37" s="28">
-        <v>10000</v>
-      </c>
-      <c r="N37" s="28">
-        <v>0</v>
-      </c>
-      <c r="O37" s="28">
-        <v>1</v>
-      </c>
-      <c r="P37" s="28">
-        <v>0</v>
-      </c>
-      <c r="Q37" s="28">
-        <v>0</v>
-      </c>
-      <c r="R37" s="28">
-        <v>0</v>
-      </c>
-      <c r="S37" s="28">
-        <v>1</v>
-      </c>
-      <c r="T37" s="28">
-        <v>0</v>
-      </c>
-      <c r="U37" s="28">
+      <c r="L38" s="28">
+        <v>0</v>
+      </c>
+      <c r="M38" s="28">
+        <v>10000</v>
+      </c>
+      <c r="N38" s="28">
+        <v>0</v>
+      </c>
+      <c r="O38" s="28">
+        <v>1</v>
+      </c>
+      <c r="P38" s="28">
+        <v>0</v>
+      </c>
+      <c r="Q38" s="28">
+        <v>0</v>
+      </c>
+      <c r="R38" s="28">
+        <v>0</v>
+      </c>
+      <c r="S38" s="28">
+        <v>1</v>
+      </c>
+      <c r="T38" s="28">
+        <v>0</v>
+      </c>
+      <c r="U38" s="32" t="s">
+        <v>302</v>
+      </c>
+      <c r="V38" s="28">
         <v>150</v>
       </c>
-      <c r="V37" s="28">
+      <c r="W38" s="28">
         <v>15000</v>
       </c>
-      <c r="W37" s="28">
+      <c r="X38" s="28">
         <v>120</v>
       </c>
-      <c r="X37" s="28">
+      <c r="Y38" s="28">
         <v>12000</v>
       </c>
-      <c r="Y37" s="28">
-        <v>0</v>
-      </c>
-      <c r="Z37" s="28">
-        <v>0</v>
-      </c>
-      <c r="AA37" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB37" s="28">
-        <v>1</v>
-      </c>
-      <c r="AC37" s="28">
+      <c r="Z38" s="28">
+        <v>0</v>
+      </c>
+      <c r="AA38" s="28">
+        <v>0</v>
+      </c>
+      <c r="AB38" s="28" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC38" s="28">
+        <v>1</v>
+      </c>
+      <c r="AD38" s="28">
         <v>1</v>
       </c>
     </row>
-    <row r="38" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A38" s="30">
+    <row r="39" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A39" s="30">
         <v>10010001</v>
-      </c>
-      <c r="B38" s="30">
-        <v>5</v>
-      </c>
-      <c r="C38" s="30">
-        <v>1001</v>
-      </c>
-      <c r="D38" s="30">
-        <v>1</v>
-      </c>
-      <c r="E38" s="18" t="s">
-        <v>219</v>
-      </c>
-      <c r="F38" s="30" t="s">
-        <v>220</v>
-      </c>
-      <c r="G38" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="H38" s="30"/>
-      <c r="I38" s="30">
-        <v>100</v>
-      </c>
-      <c r="J38" s="30">
-        <v>100</v>
-      </c>
-      <c r="K38" s="30">
-        <v>100</v>
-      </c>
-      <c r="L38" s="30">
-        <v>0</v>
-      </c>
-      <c r="M38" s="30">
-        <v>10000</v>
-      </c>
-      <c r="N38" s="30">
-        <v>0</v>
-      </c>
-      <c r="O38" s="30">
-        <v>0</v>
-      </c>
-      <c r="P38" s="30">
-        <v>3</v>
-      </c>
-      <c r="Q38" s="30">
-        <v>2</v>
-      </c>
-      <c r="R38" s="30">
-        <v>0</v>
-      </c>
-      <c r="S38" s="30">
-        <v>9</v>
-      </c>
-      <c r="T38" s="30">
-        <v>0</v>
-      </c>
-      <c r="U38" s="30">
-        <v>150</v>
-      </c>
-      <c r="V38" s="30">
-        <v>15000</v>
-      </c>
-      <c r="W38" s="30">
-        <v>120</v>
-      </c>
-      <c r="X38" s="30">
-        <v>12000</v>
-      </c>
-      <c r="Y38" s="30">
-        <v>0</v>
-      </c>
-      <c r="Z38" s="30">
-        <v>0</v>
-      </c>
-      <c r="AA38" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB38" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC38" s="30" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="39" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A39" s="30">
-        <v>10020001</v>
       </c>
       <c r="B39" s="30">
         <v>5</v>
       </c>
       <c r="C39" s="30">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="D39" s="30">
         <v>1</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="G39" s="30" t="s">
         <v>100</v>
@@ -5329,233 +5559,240 @@
         <v>0</v>
       </c>
       <c r="U39" s="30">
+        <v>0</v>
+      </c>
+      <c r="V39" s="30">
         <v>150</v>
       </c>
-      <c r="V39" s="30">
+      <c r="W39" s="30">
         <v>15000</v>
       </c>
-      <c r="W39" s="30">
+      <c r="X39" s="30">
         <v>120</v>
       </c>
-      <c r="X39" s="30">
+      <c r="Y39" s="30">
         <v>12000</v>
       </c>
-      <c r="Y39" s="30">
-        <v>0</v>
-      </c>
       <c r="Z39" s="30">
         <v>0</v>
       </c>
-      <c r="AA39" s="30" t="s">
+      <c r="AA39" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB39" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="AB39" s="30" t="s">
+      <c r="AC39" s="30" t="s">
         <v>63</v>
       </c>
-      <c r="AC39" s="30" t="s">
+      <c r="AD39" s="30" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="40" spans="1:29" s="29" customFormat="1" x14ac:dyDescent="0.15">
-      <c r="A40" s="31">
+    <row r="40" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A40" s="30">
+        <v>10020001</v>
+      </c>
+      <c r="B40" s="30">
+        <v>5</v>
+      </c>
+      <c r="C40" s="30">
+        <v>1002</v>
+      </c>
+      <c r="D40" s="30">
+        <v>1</v>
+      </c>
+      <c r="E40" s="18" t="s">
+        <v>221</v>
+      </c>
+      <c r="F40" s="30" t="s">
+        <v>222</v>
+      </c>
+      <c r="G40" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="H40" s="30"/>
+      <c r="I40" s="30">
+        <v>100</v>
+      </c>
+      <c r="J40" s="30">
+        <v>100</v>
+      </c>
+      <c r="K40" s="30">
+        <v>100</v>
+      </c>
+      <c r="L40" s="30">
+        <v>0</v>
+      </c>
+      <c r="M40" s="30">
+        <v>10000</v>
+      </c>
+      <c r="N40" s="30">
+        <v>0</v>
+      </c>
+      <c r="O40" s="30">
+        <v>0</v>
+      </c>
+      <c r="P40" s="30">
+        <v>3</v>
+      </c>
+      <c r="Q40" s="30">
+        <v>2</v>
+      </c>
+      <c r="R40" s="30">
+        <v>0</v>
+      </c>
+      <c r="S40" s="30">
+        <v>9</v>
+      </c>
+      <c r="T40" s="30">
+        <v>0</v>
+      </c>
+      <c r="U40" s="30">
+        <v>0</v>
+      </c>
+      <c r="V40" s="30">
+        <v>150</v>
+      </c>
+      <c r="W40" s="30">
+        <v>15000</v>
+      </c>
+      <c r="X40" s="30">
+        <v>120</v>
+      </c>
+      <c r="Y40" s="30">
+        <v>12000</v>
+      </c>
+      <c r="Z40" s="30">
+        <v>0</v>
+      </c>
+      <c r="AA40" s="30">
+        <v>0</v>
+      </c>
+      <c r="AB40" s="30" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC40" s="30" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD40" s="30" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="41" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+      <c r="A41" s="31">
         <v>11010001</v>
       </c>
-      <c r="B40" s="31">
+      <c r="B41" s="31">
         <v>5</v>
       </c>
-      <c r="C40" s="31">
+      <c r="C41" s="31">
         <v>1101</v>
       </c>
-      <c r="D40" s="31">
-        <v>1</v>
-      </c>
-      <c r="E40" s="18" t="s">
+      <c r="D41" s="31">
+        <v>1</v>
+      </c>
+      <c r="E41" s="18" t="s">
         <v>223</v>
       </c>
-      <c r="F40" s="31" t="s">
+      <c r="F41" s="31" t="s">
         <v>224</v>
       </c>
-      <c r="G40" s="31" t="s">
+      <c r="G41" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="H40" s="31"/>
-      <c r="I40" s="31">
+      <c r="H41" s="31"/>
+      <c r="I41" s="31">
         <v>100</v>
       </c>
-      <c r="J40" s="31">
+      <c r="J41" s="31">
         <v>100</v>
       </c>
-      <c r="K40" s="31">
+      <c r="K41" s="31">
         <v>100</v>
       </c>
-      <c r="L40" s="31">
-        <v>0</v>
-      </c>
-      <c r="M40" s="31">
-        <v>10000</v>
-      </c>
-      <c r="N40" s="31">
-        <v>0</v>
-      </c>
-      <c r="O40" s="31">
-        <v>0</v>
-      </c>
-      <c r="P40" s="31">
+      <c r="L41" s="31">
+        <v>0</v>
+      </c>
+      <c r="M41" s="31">
+        <v>10000</v>
+      </c>
+      <c r="N41" s="31">
+        <v>0</v>
+      </c>
+      <c r="O41" s="31">
+        <v>0</v>
+      </c>
+      <c r="P41" s="31">
         <v>3</v>
       </c>
-      <c r="Q40" s="31">
+      <c r="Q41" s="31">
         <v>2</v>
       </c>
-      <c r="R40" s="31">
-        <v>0</v>
-      </c>
-      <c r="S40" s="31">
+      <c r="R41" s="31">
+        <v>0</v>
+      </c>
+      <c r="S41" s="31">
         <v>9</v>
       </c>
-      <c r="T40" s="31">
-        <v>0</v>
-      </c>
-      <c r="U40" s="31">
+      <c r="T41" s="31">
+        <v>0</v>
+      </c>
+      <c r="U41" s="31">
+        <v>0</v>
+      </c>
+      <c r="V41" s="31">
         <v>150</v>
       </c>
-      <c r="V40" s="31">
+      <c r="W41" s="31">
         <v>15000</v>
       </c>
-      <c r="W40" s="31">
+      <c r="X41" s="31">
         <v>120</v>
       </c>
-      <c r="X40" s="31">
+      <c r="Y41" s="31">
         <v>12000</v>
       </c>
-      <c r="Y40" s="31">
-        <v>0</v>
-      </c>
-      <c r="Z40" s="31">
-        <v>0</v>
-      </c>
-      <c r="AA40" s="31" t="s">
+      <c r="Z41" s="31">
+        <v>0</v>
+      </c>
+      <c r="AA41" s="31">
+        <v>0</v>
+      </c>
+      <c r="AB41" s="31" t="s">
         <v>100</v>
       </c>
-      <c r="AB40" s="31" t="s">
+      <c r="AC41" s="31" t="s">
         <v>63</v>
       </c>
-      <c r="AC40" s="31" t="s">
+      <c r="AD41" s="31" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="41" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A41" s="23">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A42" s="23">
         <v>54010001</v>
-      </c>
-      <c r="B41" s="23">
-        <v>4</v>
-      </c>
-      <c r="C41" s="23">
-        <v>5401</v>
-      </c>
-      <c r="D41" s="23">
-        <v>1</v>
-      </c>
-      <c r="E41" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="F41" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="G41" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="H41" s="23" t="s">
-        <v>89</v>
-      </c>
-      <c r="I41" s="23">
-        <v>0</v>
-      </c>
-      <c r="J41" s="23">
-        <v>0</v>
-      </c>
-      <c r="K41" s="23">
-        <v>0</v>
-      </c>
-      <c r="L41" s="23">
-        <v>0</v>
-      </c>
-      <c r="M41" s="23">
-        <v>0</v>
-      </c>
-      <c r="N41" s="23">
-        <v>0</v>
-      </c>
-      <c r="O41" s="23">
-        <v>0</v>
-      </c>
-      <c r="P41" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q41" s="23">
-        <v>0</v>
-      </c>
-      <c r="R41" s="23">
-        <v>0</v>
-      </c>
-      <c r="S41" s="23">
-        <v>0</v>
-      </c>
-      <c r="T41" s="23">
-        <v>0</v>
-      </c>
-      <c r="U41" s="23">
-        <v>0</v>
-      </c>
-      <c r="V41" s="23">
-        <v>0</v>
-      </c>
-      <c r="W41" s="23">
-        <v>0</v>
-      </c>
-      <c r="X41" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y41" s="23">
-        <v>54010001</v>
-      </c>
-      <c r="Z41" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA41" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB41" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC41" s="23" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="42" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A42" s="23">
-        <v>54030001</v>
       </c>
       <c r="B42" s="23">
         <v>4</v>
       </c>
       <c r="C42" s="23">
-        <v>5403</v>
+        <v>5401</v>
       </c>
       <c r="D42" s="23">
         <v>1</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F42" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="G42" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="I42" s="23">
         <v>0</v>
@@ -5606,45 +5843,48 @@
         <v>0</v>
       </c>
       <c r="Y42" s="23">
-        <v>54020001</v>
+        <v>0</v>
       </c>
       <c r="Z42" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA42" s="23" t="s">
-        <v>34</v>
+        <v>54010001</v>
+      </c>
+      <c r="AA42" s="23">
+        <v>0</v>
       </c>
       <c r="AB42" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC42" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC42" s="23" t="s">
+      <c r="AD42" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="43" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A43" s="23">
-        <v>54050001</v>
+        <v>54030001</v>
       </c>
       <c r="B43" s="23">
         <v>4</v>
       </c>
       <c r="C43" s="23">
-        <v>5405</v>
+        <v>5403</v>
       </c>
       <c r="D43" s="23">
         <v>1</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="G43" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="I43" s="23">
         <v>0</v>
@@ -5695,45 +5935,48 @@
         <v>0</v>
       </c>
       <c r="Y43" s="23">
-        <v>54030001</v>
+        <v>0</v>
       </c>
       <c r="Z43" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA43" s="23" t="s">
-        <v>34</v>
+        <v>54020001</v>
+      </c>
+      <c r="AA43" s="23">
+        <v>0</v>
       </c>
       <c r="AB43" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC43" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC43" s="23" t="s">
+      <c r="AD43" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="44" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A44" s="23">
-        <v>54070001</v>
+        <v>54050001</v>
       </c>
       <c r="B44" s="23">
         <v>4</v>
       </c>
       <c r="C44" s="23">
-        <v>5407</v>
+        <v>5405</v>
       </c>
       <c r="D44" s="23">
         <v>1</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="G44" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="I44" s="23">
         <v>0</v>
@@ -5784,45 +6027,48 @@
         <v>0</v>
       </c>
       <c r="Y44" s="23">
-        <v>54040001</v>
+        <v>0</v>
       </c>
       <c r="Z44" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA44" s="23" t="s">
-        <v>34</v>
+        <v>54030001</v>
+      </c>
+      <c r="AA44" s="23">
+        <v>0</v>
       </c>
       <c r="AB44" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC44" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC44" s="23" t="s">
+      <c r="AD44" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="45" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A45" s="23">
-        <v>54090001</v>
+        <v>54070001</v>
       </c>
       <c r="B45" s="23">
         <v>4</v>
       </c>
       <c r="C45" s="23">
-        <v>5409</v>
+        <v>5407</v>
       </c>
       <c r="D45" s="23">
         <v>1</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="G45" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="I45" s="23">
         <v>0</v>
@@ -5873,45 +6119,48 @@
         <v>0</v>
       </c>
       <c r="Y45" s="23">
-        <v>54050001</v>
+        <v>0</v>
       </c>
       <c r="Z45" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA45" s="23" t="s">
-        <v>34</v>
+        <v>54040001</v>
+      </c>
+      <c r="AA45" s="23">
+        <v>0</v>
       </c>
       <c r="AB45" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC45" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC45" s="23" t="s">
+      <c r="AD45" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="46" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A46" s="23">
-        <v>54110001</v>
+        <v>54090001</v>
       </c>
       <c r="B46" s="23">
         <v>4</v>
       </c>
       <c r="C46" s="23">
-        <v>5411</v>
+        <v>5409</v>
       </c>
       <c r="D46" s="23">
         <v>1</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="G46" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="I46" s="23">
         <v>0</v>
@@ -5962,45 +6211,48 @@
         <v>0</v>
       </c>
       <c r="Y46" s="23">
-        <v>54060001</v>
+        <v>0</v>
       </c>
       <c r="Z46" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA46" s="23" t="s">
-        <v>34</v>
+        <v>54050001</v>
+      </c>
+      <c r="AA46" s="23">
+        <v>0</v>
       </c>
       <c r="AB46" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC46" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC46" s="23" t="s">
+      <c r="AD46" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="47" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A47" s="23">
-        <v>54130001</v>
+        <v>54110001</v>
       </c>
       <c r="B47" s="23">
         <v>4</v>
       </c>
       <c r="C47" s="23">
-        <v>5413</v>
+        <v>5411</v>
       </c>
       <c r="D47" s="23">
         <v>1</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="G47" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="I47" s="23">
         <v>0</v>
@@ -6051,45 +6303,48 @@
         <v>0</v>
       </c>
       <c r="Y47" s="23">
-        <v>54070001</v>
+        <v>0</v>
       </c>
       <c r="Z47" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA47" s="23" t="s">
-        <v>34</v>
+        <v>54060001</v>
+      </c>
+      <c r="AA47" s="23">
+        <v>0</v>
       </c>
       <c r="AB47" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC47" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC47" s="23" t="s">
+      <c r="AD47" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="48" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A48" s="23">
-        <v>54150001</v>
+        <v>54130001</v>
       </c>
       <c r="B48" s="23">
         <v>4</v>
       </c>
       <c r="C48" s="23">
-        <v>5415</v>
+        <v>5413</v>
       </c>
       <c r="D48" s="23">
         <v>1</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="G48" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="I48" s="23">
         <v>0</v>
@@ -6140,45 +6395,48 @@
         <v>0</v>
       </c>
       <c r="Y48" s="23">
-        <v>54080001</v>
+        <v>0</v>
       </c>
       <c r="Z48" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA48" s="23" t="s">
-        <v>34</v>
+        <v>54070001</v>
+      </c>
+      <c r="AA48" s="23">
+        <v>0</v>
       </c>
       <c r="AB48" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC48" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC48" s="23" t="s">
+      <c r="AD48" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="49" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A49" s="23">
-        <v>54170001</v>
+        <v>54150001</v>
       </c>
       <c r="B49" s="23">
         <v>4</v>
       </c>
       <c r="C49" s="23">
-        <v>5417</v>
+        <v>5415</v>
       </c>
       <c r="D49" s="23">
         <v>1</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="G49" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>112</v>
+        <v>96</v>
       </c>
       <c r="I49" s="23">
         <v>0</v>
@@ -6232,42 +6490,45 @@
         <v>0</v>
       </c>
       <c r="Z49" s="23">
-        <v>54090001</v>
-      </c>
-      <c r="AA49" s="23" t="s">
-        <v>34</v>
+        <v>54080001</v>
+      </c>
+      <c r="AA49" s="23">
+        <v>0</v>
       </c>
       <c r="AB49" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC49" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC49" s="23" t="s">
+      <c r="AD49" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="50" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A50" s="23">
-        <v>54190001</v>
+        <v>54170001</v>
       </c>
       <c r="B50" s="23">
         <v>4</v>
       </c>
       <c r="C50" s="23">
-        <v>5419</v>
+        <v>5417</v>
       </c>
       <c r="D50" s="23">
         <v>1</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="G50" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>98</v>
+        <v>112</v>
       </c>
       <c r="I50" s="23">
         <v>0</v>
@@ -6318,45 +6579,48 @@
         <v>0</v>
       </c>
       <c r="Y50" s="23">
-        <v>54100001</v>
+        <v>0</v>
       </c>
       <c r="Z50" s="23">
         <v>0</v>
       </c>
-      <c r="AA50" s="23" t="s">
-        <v>34</v>
+      <c r="AA50" s="23">
+        <v>54090001</v>
       </c>
       <c r="AB50" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC50" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC50" s="23" t="s">
+      <c r="AD50" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="51" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A51" s="23">
-        <v>54210001</v>
+        <v>54190001</v>
       </c>
       <c r="B51" s="23">
         <v>4</v>
       </c>
       <c r="C51" s="23">
-        <v>5421</v>
+        <v>5419</v>
       </c>
       <c r="D51" s="23">
         <v>1</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="G51" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H51" s="23" t="s">
-        <v>113</v>
+        <v>98</v>
       </c>
       <c r="I51" s="23">
         <v>0</v>
@@ -6410,42 +6674,45 @@
         <v>0</v>
       </c>
       <c r="Z51" s="23">
-        <v>54110001</v>
-      </c>
-      <c r="AA51" s="23" t="s">
-        <v>34</v>
+        <v>54100001</v>
+      </c>
+      <c r="AA51" s="23">
+        <v>0</v>
       </c>
       <c r="AB51" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC51" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC51" s="23" t="s">
+      <c r="AD51" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="52" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A52" s="23">
-        <v>54230001</v>
+        <v>54210001</v>
       </c>
       <c r="B52" s="23">
         <v>4</v>
       </c>
       <c r="C52" s="23">
-        <v>5423</v>
+        <v>5421</v>
       </c>
       <c r="D52" s="23">
         <v>1</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>157</v>
+        <v>111</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>114</v>
+        <v>99</v>
       </c>
       <c r="G52" s="23" t="s">
         <v>34</v>
       </c>
       <c r="H52" s="23" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
       <c r="I52" s="23">
         <v>0</v>
@@ -6496,30 +6763,33 @@
         <v>0</v>
       </c>
       <c r="Y52" s="23">
-        <v>54120001</v>
+        <v>0</v>
       </c>
       <c r="Z52" s="23">
         <v>0</v>
       </c>
-      <c r="AA52" s="23" t="s">
-        <v>34</v>
+      <c r="AA52" s="23">
+        <v>54110001</v>
       </c>
       <c r="AB52" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC52" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC52" s="23" t="s">
+      <c r="AD52" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="53" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A53" s="23">
-        <v>54250001</v>
+        <v>54230001</v>
       </c>
       <c r="B53" s="23">
         <v>4</v>
       </c>
       <c r="C53" s="23">
-        <v>5425</v>
+        <v>5423</v>
       </c>
       <c r="D53" s="23">
         <v>1</v>
@@ -6528,191 +6798,197 @@
         <v>157</v>
       </c>
       <c r="F53" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="G53" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H53" s="23" t="s">
+        <v>114</v>
+      </c>
+      <c r="I53" s="23">
+        <v>0</v>
+      </c>
+      <c r="J53" s="23">
+        <v>0</v>
+      </c>
+      <c r="K53" s="23">
+        <v>0</v>
+      </c>
+      <c r="L53" s="23">
+        <v>0</v>
+      </c>
+      <c r="M53" s="23">
+        <v>0</v>
+      </c>
+      <c r="N53" s="23">
+        <v>0</v>
+      </c>
+      <c r="O53" s="23">
+        <v>0</v>
+      </c>
+      <c r="P53" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q53" s="23">
+        <v>0</v>
+      </c>
+      <c r="R53" s="23">
+        <v>0</v>
+      </c>
+      <c r="S53" s="23">
+        <v>0</v>
+      </c>
+      <c r="T53" s="23">
+        <v>0</v>
+      </c>
+      <c r="U53" s="23">
+        <v>0</v>
+      </c>
+      <c r="V53" s="23">
+        <v>0</v>
+      </c>
+      <c r="W53" s="23">
+        <v>0</v>
+      </c>
+      <c r="X53" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y53" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z53" s="23">
+        <v>54120001</v>
+      </c>
+      <c r="AA53" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB53" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC53" s="23" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD53" s="23" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="54" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A54" s="23">
+        <v>54250001</v>
+      </c>
+      <c r="B54" s="23">
+        <v>4</v>
+      </c>
+      <c r="C54" s="23">
+        <v>5425</v>
+      </c>
+      <c r="D54" s="23">
+        <v>1</v>
+      </c>
+      <c r="E54" s="18" t="s">
+        <v>157</v>
+      </c>
+      <c r="F54" s="23" t="s">
         <v>128</v>
       </c>
-      <c r="G53" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="H53" s="23" t="s">
+      <c r="G54" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="H54" s="23" t="s">
         <v>269</v>
       </c>
-      <c r="I53" s="23">
-        <v>0</v>
-      </c>
-      <c r="J53" s="23">
-        <v>0</v>
-      </c>
-      <c r="K53" s="23">
-        <v>0</v>
-      </c>
-      <c r="L53" s="23">
-        <v>0</v>
-      </c>
-      <c r="M53" s="23">
-        <v>0</v>
-      </c>
-      <c r="N53" s="23">
-        <v>0</v>
-      </c>
-      <c r="O53" s="23">
-        <v>0</v>
-      </c>
-      <c r="P53" s="23">
-        <v>0</v>
-      </c>
-      <c r="Q53" s="23">
-        <v>0</v>
-      </c>
-      <c r="R53" s="23">
-        <v>0</v>
-      </c>
-      <c r="S53" s="23">
-        <v>0</v>
-      </c>
-      <c r="T53" s="23">
-        <v>0</v>
-      </c>
-      <c r="U53" s="23">
-        <v>0</v>
-      </c>
-      <c r="V53" s="23">
-        <v>0</v>
-      </c>
-      <c r="W53" s="23">
-        <v>0</v>
-      </c>
-      <c r="X53" s="23">
-        <v>0</v>
-      </c>
-      <c r="Y53" s="23">
+      <c r="I54" s="23">
+        <v>0</v>
+      </c>
+      <c r="J54" s="23">
+        <v>0</v>
+      </c>
+      <c r="K54" s="23">
+        <v>0</v>
+      </c>
+      <c r="L54" s="23">
+        <v>0</v>
+      </c>
+      <c r="M54" s="23">
+        <v>0</v>
+      </c>
+      <c r="N54" s="23">
+        <v>0</v>
+      </c>
+      <c r="O54" s="23">
+        <v>0</v>
+      </c>
+      <c r="P54" s="23">
+        <v>0</v>
+      </c>
+      <c r="Q54" s="23">
+        <v>0</v>
+      </c>
+      <c r="R54" s="23">
+        <v>0</v>
+      </c>
+      <c r="S54" s="23">
+        <v>0</v>
+      </c>
+      <c r="T54" s="23">
+        <v>0</v>
+      </c>
+      <c r="U54" s="23">
+        <v>0</v>
+      </c>
+      <c r="V54" s="23">
+        <v>0</v>
+      </c>
+      <c r="W54" s="23">
+        <v>0</v>
+      </c>
+      <c r="X54" s="23">
+        <v>0</v>
+      </c>
+      <c r="Y54" s="23">
+        <v>0</v>
+      </c>
+      <c r="Z54" s="23">
         <v>54130001</v>
       </c>
-      <c r="Z53" s="23">
-        <v>0</v>
-      </c>
-      <c r="AA53" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB53" s="23" t="s">
+      <c r="AA54" s="23">
+        <v>0</v>
+      </c>
+      <c r="AB54" s="23" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC54" s="23" t="s">
         <v>61</v>
       </c>
-      <c r="AC53" s="23" t="s">
+      <c r="AD54" s="23" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="54" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A54" s="13">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A55" s="13">
         <v>55010001</v>
-      </c>
-      <c r="B54" s="13">
-        <v>4</v>
-      </c>
-      <c r="C54" s="13">
-        <v>5501</v>
-      </c>
-      <c r="D54" s="13">
-        <v>1</v>
-      </c>
-      <c r="E54" s="4" t="s">
-        <v>81</v>
-      </c>
-      <c r="F54" s="13" t="s">
-        <v>279</v>
-      </c>
-      <c r="G54" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="H54" s="13" t="s">
-        <v>82</v>
-      </c>
-      <c r="I54" s="13">
-        <v>0</v>
-      </c>
-      <c r="J54" s="13">
-        <v>0</v>
-      </c>
-      <c r="K54" s="13">
-        <v>0</v>
-      </c>
-      <c r="L54" s="13">
-        <v>0</v>
-      </c>
-      <c r="M54" s="13">
-        <v>0</v>
-      </c>
-      <c r="N54" s="13">
-        <v>0</v>
-      </c>
-      <c r="O54" s="13">
-        <v>0</v>
-      </c>
-      <c r="P54" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q54" s="13">
-        <v>0</v>
-      </c>
-      <c r="R54" s="13">
-        <v>0</v>
-      </c>
-      <c r="S54" s="13">
-        <v>0</v>
-      </c>
-      <c r="T54" s="13">
-        <v>0</v>
-      </c>
-      <c r="U54" s="13">
-        <v>0</v>
-      </c>
-      <c r="V54" s="13">
-        <v>10000</v>
-      </c>
-      <c r="W54" s="13">
-        <v>0</v>
-      </c>
-      <c r="X54" s="13">
-        <v>10000</v>
-      </c>
-      <c r="Y54" s="13">
-        <v>0</v>
-      </c>
-      <c r="Z54" s="13">
-        <v>55010001</v>
-      </c>
-      <c r="AA54" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB54" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC54" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="55" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A55" s="13">
-        <v>55020001</v>
       </c>
       <c r="B55" s="13">
         <v>4</v>
       </c>
       <c r="C55" s="13">
-        <v>5502</v>
+        <v>5501</v>
       </c>
       <c r="D55" s="13">
         <v>1</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>121</v>
+        <v>81</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>122</v>
+        <v>82</v>
       </c>
       <c r="I55" s="13">
         <v>0</v>
@@ -6751,57 +7027,60 @@
         <v>0</v>
       </c>
       <c r="U55" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V55" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W55" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X55" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y55" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z55" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA55" s="13">
+        <v>55010001</v>
+      </c>
+      <c r="AB55" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC55" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD55" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A56" s="13">
         <v>55020001</v>
-      </c>
-      <c r="Z55" s="13">
-        <v>55010001</v>
-      </c>
-      <c r="AA55" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB55" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC55" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="56" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A56" s="13">
-        <v>55030001</v>
       </c>
       <c r="B56" s="13">
         <v>4</v>
       </c>
       <c r="C56" s="13">
-        <v>5503</v>
+        <v>5502</v>
       </c>
       <c r="D56" s="13">
         <v>1</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>123</v>
+        <v>121</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="I56" s="13">
         <v>0</v>
@@ -6840,57 +7119,60 @@
         <v>0</v>
       </c>
       <c r="U56" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V56" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W56" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X56" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y56" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z56" s="13">
+        <v>55020001</v>
+      </c>
+      <c r="AA56" s="13">
+        <v>55010001</v>
+      </c>
+      <c r="AB56" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC56" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD56" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A57" s="13">
         <v>55030001</v>
-      </c>
-      <c r="Z56" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA56" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB56" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC56" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="57" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A57" s="13">
-        <v>55040001</v>
       </c>
       <c r="B57" s="13">
         <v>4</v>
       </c>
       <c r="C57" s="13">
-        <v>5504</v>
+        <v>5503</v>
       </c>
       <c r="D57" s="13">
         <v>1</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>85</v>
+        <v>123</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>83</v>
+        <v>124</v>
       </c>
       <c r="I57" s="13">
         <v>0</v>
@@ -6929,57 +7211,60 @@
         <v>0</v>
       </c>
       <c r="U57" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V57" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W57" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X57" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y57" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z57" s="13">
+        <v>55030001</v>
+      </c>
+      <c r="AA57" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB57" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC57" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD57" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A58" s="13">
         <v>55040001</v>
-      </c>
-      <c r="Z57" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA57" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB57" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC57" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="58" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A58" s="13">
-        <v>55050001</v>
       </c>
       <c r="B58" s="13">
         <v>4</v>
       </c>
       <c r="C58" s="13">
-        <v>5505</v>
+        <v>5504</v>
       </c>
       <c r="D58" s="13">
         <v>1</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>88</v>
+        <v>83</v>
       </c>
       <c r="I58" s="13">
         <v>0</v>
@@ -7018,57 +7303,60 @@
         <v>0</v>
       </c>
       <c r="U58" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V58" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W58" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X58" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y58" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z58" s="13">
+        <v>55040001</v>
+      </c>
+      <c r="AA58" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB58" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC58" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD58" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A59" s="13">
         <v>55050001</v>
-      </c>
-      <c r="AA58" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB58" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC58" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="59" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A59" s="13">
-        <v>55060001</v>
       </c>
       <c r="B59" s="13">
         <v>4</v>
       </c>
       <c r="C59" s="13">
-        <v>5506</v>
+        <v>5505</v>
       </c>
       <c r="D59" s="13">
         <v>1</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>126</v>
+        <v>86</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>34</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>119</v>
+        <v>88</v>
       </c>
       <c r="I59" s="13">
         <v>0</v>
@@ -7107,235 +7395,244 @@
         <v>0</v>
       </c>
       <c r="U59" s="13">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V59" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W59" s="13">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X59" s="13">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y59" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z59" s="13">
+        <v>0</v>
+      </c>
+      <c r="AA59" s="13">
+        <v>55050001</v>
+      </c>
+      <c r="AB59" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC59" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD59" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A60" s="13">
         <v>55060001</v>
-      </c>
-      <c r="Z59" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA59" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB59" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC59" s="13" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="60" spans="1:29" x14ac:dyDescent="0.2">
-      <c r="A60" s="13">
-        <v>55070001</v>
       </c>
       <c r="B60" s="13">
         <v>4</v>
       </c>
       <c r="C60" s="13">
+        <v>5506</v>
+      </c>
+      <c r="D60" s="13">
+        <v>1</v>
+      </c>
+      <c r="E60" s="4" t="s">
+        <v>126</v>
+      </c>
+      <c r="F60" s="13" t="s">
+        <v>284</v>
+      </c>
+      <c r="G60" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H60" s="13" t="s">
+        <v>119</v>
+      </c>
+      <c r="I60" s="13">
+        <v>0</v>
+      </c>
+      <c r="J60" s="13">
+        <v>0</v>
+      </c>
+      <c r="K60" s="13">
+        <v>0</v>
+      </c>
+      <c r="L60" s="13">
+        <v>0</v>
+      </c>
+      <c r="M60" s="13">
+        <v>0</v>
+      </c>
+      <c r="N60" s="13">
+        <v>0</v>
+      </c>
+      <c r="O60" s="13">
+        <v>0</v>
+      </c>
+      <c r="P60" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q60" s="13">
+        <v>0</v>
+      </c>
+      <c r="R60" s="13">
+        <v>0</v>
+      </c>
+      <c r="S60" s="13">
+        <v>0</v>
+      </c>
+      <c r="T60" s="13">
+        <v>0</v>
+      </c>
+      <c r="U60" s="13">
+        <v>1</v>
+      </c>
+      <c r="V60" s="13">
+        <v>0</v>
+      </c>
+      <c r="W60" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X60" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y60" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z60" s="13">
+        <v>55060001</v>
+      </c>
+      <c r="AA60" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB60" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC60" s="13" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD60" s="13" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="61" spans="1:30" x14ac:dyDescent="0.2">
+      <c r="A61" s="13">
+        <v>55070001</v>
+      </c>
+      <c r="B61" s="13">
+        <v>4</v>
+      </c>
+      <c r="C61" s="13">
         <v>5507</v>
       </c>
-      <c r="D60" s="13">
-        <v>1</v>
-      </c>
-      <c r="E60" s="4" t="s">
+      <c r="D61" s="13">
+        <v>1</v>
+      </c>
+      <c r="E61" s="4" t="s">
         <v>127</v>
       </c>
-      <c r="F60" s="13" t="s">
+      <c r="F61" s="13" t="s">
         <v>285</v>
       </c>
-      <c r="G60" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="H60" s="13" t="s">
+      <c r="G61" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="H61" s="13" t="s">
         <v>120</v>
       </c>
-      <c r="I60" s="13">
-        <v>0</v>
-      </c>
-      <c r="J60" s="13">
-        <v>0</v>
-      </c>
-      <c r="K60" s="13">
-        <v>0</v>
-      </c>
-      <c r="L60" s="13">
-        <v>0</v>
-      </c>
-      <c r="M60" s="13">
-        <v>0</v>
-      </c>
-      <c r="N60" s="13">
-        <v>0</v>
-      </c>
-      <c r="O60" s="13">
-        <v>0</v>
-      </c>
-      <c r="P60" s="13">
-        <v>0</v>
-      </c>
-      <c r="Q60" s="13">
-        <v>0</v>
-      </c>
-      <c r="R60" s="13">
-        <v>0</v>
-      </c>
-      <c r="S60" s="13">
-        <v>0</v>
-      </c>
-      <c r="T60" s="13">
-        <v>0</v>
-      </c>
-      <c r="U60" s="13">
-        <v>0</v>
-      </c>
-      <c r="V60" s="13">
-        <v>10000</v>
-      </c>
-      <c r="W60" s="13">
-        <v>0</v>
-      </c>
-      <c r="X60" s="13">
-        <v>10000</v>
-      </c>
-      <c r="Y60" s="13">
+      <c r="I61" s="13">
+        <v>0</v>
+      </c>
+      <c r="J61" s="13">
+        <v>0</v>
+      </c>
+      <c r="K61" s="13">
+        <v>0</v>
+      </c>
+      <c r="L61" s="13">
+        <v>0</v>
+      </c>
+      <c r="M61" s="13">
+        <v>0</v>
+      </c>
+      <c r="N61" s="13">
+        <v>0</v>
+      </c>
+      <c r="O61" s="13">
+        <v>0</v>
+      </c>
+      <c r="P61" s="13">
+        <v>0</v>
+      </c>
+      <c r="Q61" s="13">
+        <v>0</v>
+      </c>
+      <c r="R61" s="13">
+        <v>0</v>
+      </c>
+      <c r="S61" s="13">
+        <v>0</v>
+      </c>
+      <c r="T61" s="13">
+        <v>0</v>
+      </c>
+      <c r="U61" s="13">
+        <v>1</v>
+      </c>
+      <c r="V61" s="13">
+        <v>0</v>
+      </c>
+      <c r="W61" s="13">
+        <v>10000</v>
+      </c>
+      <c r="X61" s="13">
+        <v>0</v>
+      </c>
+      <c r="Y61" s="13">
+        <v>10000</v>
+      </c>
+      <c r="Z61" s="13">
         <v>55070001</v>
       </c>
-      <c r="Z60" s="13">
-        <v>0</v>
-      </c>
-      <c r="AA60" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB60" s="13" t="s">
+      <c r="AA61" s="13">
+        <v>0</v>
+      </c>
+      <c r="AB61" s="13" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC61" s="13" t="s">
         <v>61</v>
       </c>
-      <c r="AC60" s="13" t="s">
+      <c r="AD61" s="13" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="61" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A61" s="14">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A62" s="14">
         <v>56010001</v>
-      </c>
-      <c r="B61" s="14">
-        <v>4</v>
-      </c>
-      <c r="C61" s="14">
-        <v>5601</v>
-      </c>
-      <c r="D61" s="14">
-        <v>1</v>
-      </c>
-      <c r="E61" s="12" t="s">
-        <v>135</v>
-      </c>
-      <c r="F61" s="14" t="s">
-        <v>225</v>
-      </c>
-      <c r="G61" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H61" s="14" t="s">
-        <v>251</v>
-      </c>
-      <c r="I61" s="14">
-        <v>0</v>
-      </c>
-      <c r="J61" s="14">
-        <v>0</v>
-      </c>
-      <c r="K61" s="14">
-        <v>0</v>
-      </c>
-      <c r="L61" s="14">
-        <v>0</v>
-      </c>
-      <c r="M61" s="14">
-        <v>0</v>
-      </c>
-      <c r="N61" s="14">
-        <v>0</v>
-      </c>
-      <c r="O61" s="14">
-        <v>0</v>
-      </c>
-      <c r="P61" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q61" s="14">
-        <v>0</v>
-      </c>
-      <c r="R61" s="14">
-        <v>0</v>
-      </c>
-      <c r="S61" s="14">
-        <v>0</v>
-      </c>
-      <c r="T61" s="14">
-        <v>0</v>
-      </c>
-      <c r="U61" s="14">
-        <v>0</v>
-      </c>
-      <c r="V61" s="14">
-        <v>10000</v>
-      </c>
-      <c r="W61" s="14">
-        <v>0</v>
-      </c>
-      <c r="X61" s="14">
-        <v>10000</v>
-      </c>
-      <c r="Y61" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z61" s="14">
-        <v>56010001</v>
-      </c>
-      <c r="AA61" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB61" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC61" s="14" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="62" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A62" s="14">
-        <v>56040001</v>
       </c>
       <c r="B62" s="14">
         <v>4</v>
       </c>
       <c r="C62" s="14">
-        <v>5604</v>
+        <v>5601</v>
       </c>
       <c r="D62" s="14">
         <v>1</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="G62" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="I62" s="14">
         <v>0</v>
@@ -7374,57 +7671,60 @@
         <v>0</v>
       </c>
       <c r="U62" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V62" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W62" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X62" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y62" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z62" s="14">
         <v>0</v>
       </c>
-      <c r="AA62" s="14" t="s">
-        <v>34</v>
+      <c r="AA62" s="14">
+        <v>56010001</v>
       </c>
       <c r="AB62" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC62" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AC62" s="14" t="s">
+      <c r="AD62" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="63" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A63" s="14">
-        <v>56060001</v>
+        <v>56040001</v>
       </c>
       <c r="B63" s="14">
         <v>4</v>
       </c>
       <c r="C63" s="14">
-        <v>5606</v>
+        <v>5604</v>
       </c>
       <c r="D63" s="14">
         <v>1</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
       <c r="G63" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H63" s="14" t="s">
-        <v>253</v>
+        <v>252</v>
       </c>
       <c r="I63" s="14">
         <v>0</v>
@@ -7463,57 +7763,60 @@
         <v>0</v>
       </c>
       <c r="U63" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V63" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W63" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X63" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y63" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z63" s="14">
-        <v>56030001</v>
-      </c>
-      <c r="AA63" s="14" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="AA63" s="14">
+        <v>0</v>
       </c>
       <c r="AB63" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC63" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AC63" s="14" t="s">
+      <c r="AD63" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="64" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A64" s="14">
-        <v>56080001</v>
+        <v>56060001</v>
       </c>
       <c r="B64" s="14">
         <v>4</v>
       </c>
       <c r="C64" s="14">
-        <v>5608</v>
+        <v>5606</v>
       </c>
       <c r="D64" s="14">
         <v>1</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>228</v>
+        <v>227</v>
       </c>
       <c r="G64" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>254</v>
+        <v>253</v>
       </c>
       <c r="I64" s="14">
         <v>0</v>
@@ -7552,57 +7855,60 @@
         <v>0</v>
       </c>
       <c r="U64" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V64" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W64" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X64" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y64" s="14">
-        <v>56040001</v>
+        <v>10000</v>
       </c>
       <c r="Z64" s="14">
         <v>0</v>
       </c>
-      <c r="AA64" s="14" t="s">
-        <v>34</v>
+      <c r="AA64" s="14">
+        <v>56030001</v>
       </c>
       <c r="AB64" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC64" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AC64" s="14" t="s">
+      <c r="AD64" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="65" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A65" s="14">
-        <v>56100001</v>
+        <v>56080001</v>
       </c>
       <c r="B65" s="14">
         <v>4</v>
       </c>
       <c r="C65" s="14">
-        <v>5610</v>
+        <v>5608</v>
       </c>
       <c r="D65" s="14">
         <v>1</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>291</v>
+        <v>228</v>
       </c>
       <c r="G65" s="14" t="s">
         <v>34</v>
       </c>
       <c r="H65" s="14" t="s">
-        <v>289</v>
+        <v>254</v>
       </c>
       <c r="I65" s="14">
         <v>0</v>
@@ -7641,42 +7947,45 @@
         <v>0</v>
       </c>
       <c r="U65" s="14">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="V65" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W65" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X65" s="14">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y65" s="14">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z65" s="14">
-        <v>56050001</v>
-      </c>
-      <c r="AA65" s="14" t="s">
-        <v>34</v>
+        <v>56040001</v>
+      </c>
+      <c r="AA65" s="14">
+        <v>0</v>
       </c>
       <c r="AB65" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC65" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AC65" s="14" t="s">
+      <c r="AD65" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="66" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A66" s="14">
-        <v>56130001</v>
+        <v>56100001</v>
       </c>
       <c r="B66" s="14">
         <v>4</v>
       </c>
       <c r="C66" s="14">
-        <v>5613</v>
+        <v>5610</v>
       </c>
       <c r="D66" s="14">
         <v>1</v>
@@ -7685,191 +7994,197 @@
         <v>140</v>
       </c>
       <c r="F66" s="14" t="s">
+        <v>291</v>
+      </c>
+      <c r="G66" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H66" s="14" t="s">
+        <v>289</v>
+      </c>
+      <c r="I66" s="14">
+        <v>0</v>
+      </c>
+      <c r="J66" s="14">
+        <v>0</v>
+      </c>
+      <c r="K66" s="14">
+        <v>0</v>
+      </c>
+      <c r="L66" s="14">
+        <v>0</v>
+      </c>
+      <c r="M66" s="14">
+        <v>0</v>
+      </c>
+      <c r="N66" s="14">
+        <v>0</v>
+      </c>
+      <c r="O66" s="14">
+        <v>0</v>
+      </c>
+      <c r="P66" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q66" s="14">
+        <v>0</v>
+      </c>
+      <c r="R66" s="14">
+        <v>0</v>
+      </c>
+      <c r="S66" s="14">
+        <v>0</v>
+      </c>
+      <c r="T66" s="14">
+        <v>0</v>
+      </c>
+      <c r="U66" s="14">
+        <v>2</v>
+      </c>
+      <c r="V66" s="14">
+        <v>0</v>
+      </c>
+      <c r="W66" s="14">
+        <v>10000</v>
+      </c>
+      <c r="X66" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y66" s="14">
+        <v>10000</v>
+      </c>
+      <c r="Z66" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA66" s="14">
+        <v>56050001</v>
+      </c>
+      <c r="AB66" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC66" s="14" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD66" s="14" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="67" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A67" s="14">
+        <v>56130001</v>
+      </c>
+      <c r="B67" s="14">
+        <v>4</v>
+      </c>
+      <c r="C67" s="14">
+        <v>5613</v>
+      </c>
+      <c r="D67" s="14">
+        <v>1</v>
+      </c>
+      <c r="E67" s="12" t="s">
+        <v>140</v>
+      </c>
+      <c r="F67" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="G66" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="H66" s="14" t="s">
+      <c r="G67" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="H67" s="14" t="s">
         <v>290</v>
       </c>
-      <c r="I66" s="14">
-        <v>0</v>
-      </c>
-      <c r="J66" s="14">
-        <v>0</v>
-      </c>
-      <c r="K66" s="14">
-        <v>0</v>
-      </c>
-      <c r="L66" s="14">
-        <v>0</v>
-      </c>
-      <c r="M66" s="14">
-        <v>0</v>
-      </c>
-      <c r="N66" s="14">
-        <v>0</v>
-      </c>
-      <c r="O66" s="14">
-        <v>0</v>
-      </c>
-      <c r="P66" s="14">
-        <v>0</v>
-      </c>
-      <c r="Q66" s="14">
-        <v>0</v>
-      </c>
-      <c r="R66" s="14">
-        <v>0</v>
-      </c>
-      <c r="S66" s="14">
-        <v>0</v>
-      </c>
-      <c r="T66" s="14">
-        <v>0</v>
-      </c>
-      <c r="U66" s="14">
-        <v>0</v>
-      </c>
-      <c r="V66" s="14">
-        <v>10000</v>
-      </c>
-      <c r="W66" s="14">
-        <v>0</v>
-      </c>
-      <c r="X66" s="14">
-        <v>10000</v>
-      </c>
-      <c r="Y66" s="14">
-        <v>0</v>
-      </c>
-      <c r="Z66" s="14">
+      <c r="I67" s="14">
+        <v>0</v>
+      </c>
+      <c r="J67" s="14">
+        <v>0</v>
+      </c>
+      <c r="K67" s="14">
+        <v>0</v>
+      </c>
+      <c r="L67" s="14">
+        <v>0</v>
+      </c>
+      <c r="M67" s="14">
+        <v>0</v>
+      </c>
+      <c r="N67" s="14">
+        <v>0</v>
+      </c>
+      <c r="O67" s="14">
+        <v>0</v>
+      </c>
+      <c r="P67" s="14">
+        <v>0</v>
+      </c>
+      <c r="Q67" s="14">
+        <v>0</v>
+      </c>
+      <c r="R67" s="14">
+        <v>0</v>
+      </c>
+      <c r="S67" s="14">
+        <v>0</v>
+      </c>
+      <c r="T67" s="14">
+        <v>0</v>
+      </c>
+      <c r="U67" s="14">
+        <v>2</v>
+      </c>
+      <c r="V67" s="14">
+        <v>0</v>
+      </c>
+      <c r="W67" s="14">
+        <v>10000</v>
+      </c>
+      <c r="X67" s="14">
+        <v>0</v>
+      </c>
+      <c r="Y67" s="14">
+        <v>10000</v>
+      </c>
+      <c r="Z67" s="14">
+        <v>0</v>
+      </c>
+      <c r="AA67" s="14">
         <v>56060001</v>
       </c>
-      <c r="AA66" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB66" s="14" t="s">
+      <c r="AB67" s="14" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC67" s="14" t="s">
         <v>61</v>
       </c>
-      <c r="AC66" s="14" t="s">
+      <c r="AD67" s="14" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="67" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A67" s="15">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A68" s="15">
         <v>57010001</v>
-      </c>
-      <c r="B67" s="15">
-        <v>4</v>
-      </c>
-      <c r="C67" s="15">
-        <v>5701</v>
-      </c>
-      <c r="D67" s="15">
-        <v>1</v>
-      </c>
-      <c r="E67" s="12" t="s">
-        <v>142</v>
-      </c>
-      <c r="F67" s="15" t="s">
-        <v>229</v>
-      </c>
-      <c r="G67" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H67" s="15" t="s">
-        <v>255</v>
-      </c>
-      <c r="I67" s="15">
-        <v>0</v>
-      </c>
-      <c r="J67" s="15">
-        <v>0</v>
-      </c>
-      <c r="K67" s="15">
-        <v>0</v>
-      </c>
-      <c r="L67" s="15">
-        <v>0</v>
-      </c>
-      <c r="M67" s="15">
-        <v>0</v>
-      </c>
-      <c r="N67" s="15">
-        <v>0</v>
-      </c>
-      <c r="O67" s="15">
-        <v>0</v>
-      </c>
-      <c r="P67" s="15">
-        <v>0</v>
-      </c>
-      <c r="Q67" s="15">
-        <v>0</v>
-      </c>
-      <c r="R67" s="15">
-        <v>0</v>
-      </c>
-      <c r="S67" s="15">
-        <v>0</v>
-      </c>
-      <c r="T67" s="15">
-        <v>0</v>
-      </c>
-      <c r="U67" s="15">
-        <v>0</v>
-      </c>
-      <c r="V67" s="15">
-        <v>10000</v>
-      </c>
-      <c r="W67" s="15">
-        <v>0</v>
-      </c>
-      <c r="X67" s="15">
-        <v>10000</v>
-      </c>
-      <c r="Y67" s="15">
-        <v>0</v>
-      </c>
-      <c r="Z67" s="15">
-        <v>57010001</v>
-      </c>
-      <c r="AA67" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB67" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC67" s="15" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="68" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A68" s="15">
-        <v>57040001</v>
       </c>
       <c r="B68" s="15">
         <v>4</v>
       </c>
       <c r="C68" s="15">
-        <v>5704</v>
+        <v>5701</v>
       </c>
       <c r="D68" s="15">
         <v>1</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>230</v>
+        <v>229</v>
       </c>
       <c r="G68" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>256</v>
+        <v>255</v>
       </c>
       <c r="I68" s="15">
         <v>0</v>
@@ -7908,57 +8223,60 @@
         <v>0</v>
       </c>
       <c r="U68" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V68" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W68" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X68" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y68" s="15">
-        <v>57020001</v>
+        <v>10000</v>
       </c>
       <c r="Z68" s="15">
         <v>0</v>
       </c>
-      <c r="AA68" s="15" t="s">
-        <v>34</v>
+      <c r="AA68" s="15">
+        <v>57010001</v>
       </c>
       <c r="AB68" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC68" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AC68" s="15" t="s">
+      <c r="AD68" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="69" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A69" s="15">
-        <v>57060001</v>
+        <v>57040001</v>
       </c>
       <c r="B69" s="15">
         <v>4</v>
       </c>
       <c r="C69" s="15">
-        <v>5706</v>
+        <v>5704</v>
       </c>
       <c r="D69" s="15">
         <v>1</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>231</v>
+        <v>230</v>
       </c>
       <c r="G69" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
       <c r="I69" s="15">
         <v>0</v>
@@ -7997,57 +8315,60 @@
         <v>0</v>
       </c>
       <c r="U69" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V69" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W69" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X69" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y69" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z69" s="15">
-        <v>0</v>
-      </c>
-      <c r="AA69" s="15" t="s">
-        <v>34</v>
+        <v>57020001</v>
+      </c>
+      <c r="AA69" s="15">
+        <v>0</v>
       </c>
       <c r="AB69" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC69" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AC69" s="15" t="s">
+      <c r="AD69" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="70" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A70" s="15">
-        <v>57080001</v>
+        <v>57060001</v>
       </c>
       <c r="B70" s="15">
         <v>4</v>
       </c>
       <c r="C70" s="15">
-        <v>5708</v>
+        <v>5706</v>
       </c>
       <c r="D70" s="15">
         <v>1</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>293</v>
+        <v>231</v>
       </c>
       <c r="G70" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>292</v>
+        <v>257</v>
       </c>
       <c r="I70" s="15">
         <v>0</v>
@@ -8086,57 +8407,60 @@
         <v>0</v>
       </c>
       <c r="U70" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V70" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W70" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X70" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y70" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z70" s="15">
-        <v>57040001</v>
-      </c>
-      <c r="AA70" s="15" t="s">
-        <v>34</v>
+        <v>0</v>
+      </c>
+      <c r="AA70" s="15">
+        <v>0</v>
       </c>
       <c r="AB70" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC70" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AC70" s="15" t="s">
+      <c r="AD70" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="71" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A71" s="15">
-        <v>57100001</v>
+        <v>57080001</v>
       </c>
       <c r="B71" s="15">
         <v>4</v>
       </c>
       <c r="C71" s="15">
-        <v>5710</v>
+        <v>5708</v>
       </c>
       <c r="D71" s="15">
         <v>1</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="G71" s="15" t="s">
         <v>34</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>258</v>
+        <v>292</v>
       </c>
       <c r="I71" s="15">
         <v>0</v>
@@ -8175,235 +8499,244 @@
         <v>0</v>
       </c>
       <c r="U71" s="15">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="V71" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W71" s="15">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X71" s="15">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y71" s="15">
-        <v>57050001</v>
+        <v>10000</v>
       </c>
       <c r="Z71" s="15">
         <v>0</v>
       </c>
-      <c r="AA71" s="15" t="s">
-        <v>34</v>
+      <c r="AA71" s="15">
+        <v>57040001</v>
       </c>
       <c r="AB71" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC71" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AC71" s="15" t="s">
+      <c r="AD71" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="72" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A72" s="15">
-        <v>57120001</v>
+        <v>57100001</v>
       </c>
       <c r="B72" s="15">
         <v>4</v>
       </c>
       <c r="C72" s="15">
+        <v>5710</v>
+      </c>
+      <c r="D72" s="15">
+        <v>1</v>
+      </c>
+      <c r="E72" s="12" t="s">
+        <v>147</v>
+      </c>
+      <c r="F72" s="15" t="s">
+        <v>287</v>
+      </c>
+      <c r="G72" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H72" s="15" t="s">
+        <v>258</v>
+      </c>
+      <c r="I72" s="15">
+        <v>0</v>
+      </c>
+      <c r="J72" s="15">
+        <v>0</v>
+      </c>
+      <c r="K72" s="15">
+        <v>0</v>
+      </c>
+      <c r="L72" s="15">
+        <v>0</v>
+      </c>
+      <c r="M72" s="15">
+        <v>0</v>
+      </c>
+      <c r="N72" s="15">
+        <v>0</v>
+      </c>
+      <c r="O72" s="15">
+        <v>0</v>
+      </c>
+      <c r="P72" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q72" s="15">
+        <v>0</v>
+      </c>
+      <c r="R72" s="15">
+        <v>0</v>
+      </c>
+      <c r="S72" s="15">
+        <v>0</v>
+      </c>
+      <c r="T72" s="15">
+        <v>0</v>
+      </c>
+      <c r="U72" s="15">
+        <v>3</v>
+      </c>
+      <c r="V72" s="15">
+        <v>0</v>
+      </c>
+      <c r="W72" s="15">
+        <v>10000</v>
+      </c>
+      <c r="X72" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y72" s="15">
+        <v>10000</v>
+      </c>
+      <c r="Z72" s="15">
+        <v>57050001</v>
+      </c>
+      <c r="AA72" s="15">
+        <v>0</v>
+      </c>
+      <c r="AB72" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC72" s="15" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD72" s="15" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="73" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A73" s="15">
+        <v>57120001</v>
+      </c>
+      <c r="B73" s="15">
+        <v>4</v>
+      </c>
+      <c r="C73" s="15">
         <v>5712</v>
       </c>
-      <c r="D72" s="15">
-        <v>1</v>
-      </c>
-      <c r="E72" s="12" t="s">
+      <c r="D73" s="15">
+        <v>1</v>
+      </c>
+      <c r="E73" s="12" t="s">
         <v>148</v>
       </c>
-      <c r="F72" s="15" t="s">
+      <c r="F73" s="15" t="s">
         <v>288</v>
       </c>
-      <c r="G72" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="H72" s="15" t="s">
+      <c r="G73" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="H73" s="15" t="s">
         <v>259</v>
       </c>
-      <c r="I72" s="15">
-        <v>0</v>
-      </c>
-      <c r="J72" s="15">
-        <v>0</v>
-      </c>
-      <c r="K72" s="15">
-        <v>0</v>
-      </c>
-      <c r="L72" s="15">
-        <v>0</v>
-      </c>
-      <c r="M72" s="15">
-        <v>0</v>
-      </c>
-      <c r="N72" s="15">
-        <v>0</v>
-      </c>
-      <c r="O72" s="15">
-        <v>0</v>
-      </c>
-      <c r="P72" s="15">
-        <v>0</v>
-      </c>
-      <c r="Q72" s="15">
-        <v>0</v>
-      </c>
-      <c r="R72" s="15">
-        <v>0</v>
-      </c>
-      <c r="S72" s="15">
-        <v>0</v>
-      </c>
-      <c r="T72" s="15">
-        <v>0</v>
-      </c>
-      <c r="U72" s="15">
-        <v>0</v>
-      </c>
-      <c r="V72" s="15">
-        <v>10000</v>
-      </c>
-      <c r="W72" s="15">
-        <v>0</v>
-      </c>
-      <c r="X72" s="15">
-        <v>10000</v>
-      </c>
-      <c r="Y72" s="15">
-        <v>0</v>
-      </c>
-      <c r="Z72" s="15">
+      <c r="I73" s="15">
+        <v>0</v>
+      </c>
+      <c r="J73" s="15">
+        <v>0</v>
+      </c>
+      <c r="K73" s="15">
+        <v>0</v>
+      </c>
+      <c r="L73" s="15">
+        <v>0</v>
+      </c>
+      <c r="M73" s="15">
+        <v>0</v>
+      </c>
+      <c r="N73" s="15">
+        <v>0</v>
+      </c>
+      <c r="O73" s="15">
+        <v>0</v>
+      </c>
+      <c r="P73" s="15">
+        <v>0</v>
+      </c>
+      <c r="Q73" s="15">
+        <v>0</v>
+      </c>
+      <c r="R73" s="15">
+        <v>0</v>
+      </c>
+      <c r="S73" s="15">
+        <v>0</v>
+      </c>
+      <c r="T73" s="15">
+        <v>0</v>
+      </c>
+      <c r="U73" s="15">
+        <v>3</v>
+      </c>
+      <c r="V73" s="15">
+        <v>0</v>
+      </c>
+      <c r="W73" s="15">
+        <v>10000</v>
+      </c>
+      <c r="X73" s="15">
+        <v>0</v>
+      </c>
+      <c r="Y73" s="15">
+        <v>10000</v>
+      </c>
+      <c r="Z73" s="15">
+        <v>0</v>
+      </c>
+      <c r="AA73" s="15">
         <v>57060001</v>
       </c>
-      <c r="AA72" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB72" s="15" t="s">
+      <c r="AB73" s="15" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC73" s="15" t="s">
         <v>61</v>
       </c>
-      <c r="AC72" s="15" t="s">
+      <c r="AD73" s="15" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="73" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A73" s="16">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A74" s="16">
         <v>58010001</v>
-      </c>
-      <c r="B73" s="16">
-        <v>4</v>
-      </c>
-      <c r="C73" s="16">
-        <v>5801</v>
-      </c>
-      <c r="D73" s="16">
-        <v>1</v>
-      </c>
-      <c r="E73" s="12" t="s">
-        <v>150</v>
-      </c>
-      <c r="F73" s="16" t="s">
-        <v>232</v>
-      </c>
-      <c r="G73" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H73" s="16" t="s">
-        <v>260</v>
-      </c>
-      <c r="I73" s="16">
-        <v>0</v>
-      </c>
-      <c r="J73" s="16">
-        <v>0</v>
-      </c>
-      <c r="K73" s="16">
-        <v>0</v>
-      </c>
-      <c r="L73" s="16">
-        <v>0</v>
-      </c>
-      <c r="M73" s="16">
-        <v>0</v>
-      </c>
-      <c r="N73" s="16">
-        <v>0</v>
-      </c>
-      <c r="O73" s="16">
-        <v>0</v>
-      </c>
-      <c r="P73" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q73" s="16">
-        <v>0</v>
-      </c>
-      <c r="R73" s="16">
-        <v>0</v>
-      </c>
-      <c r="S73" s="16">
-        <v>0</v>
-      </c>
-      <c r="T73" s="16">
-        <v>0</v>
-      </c>
-      <c r="U73" s="16">
-        <v>0</v>
-      </c>
-      <c r="V73" s="16">
-        <v>10000</v>
-      </c>
-      <c r="W73" s="16">
-        <v>0</v>
-      </c>
-      <c r="X73" s="16">
-        <v>10000</v>
-      </c>
-      <c r="Y73" s="16">
-        <v>0</v>
-      </c>
-      <c r="Z73" s="16">
-        <v>58010001</v>
-      </c>
-      <c r="AA73" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB73" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC73" s="16" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="74" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A74" s="16">
-        <v>58040001</v>
       </c>
       <c r="B74" s="16">
         <v>4</v>
       </c>
       <c r="C74" s="16">
-        <v>5804</v>
+        <v>5801</v>
       </c>
       <c r="D74" s="16">
         <v>1</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>156</v>
+        <v>150</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="G74" s="16" t="s">
         <v>34</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="I74" s="16">
         <v>0</v>
@@ -8442,57 +8775,60 @@
         <v>0</v>
       </c>
       <c r="U74" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V74" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W74" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X74" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y74" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z74" s="16">
         <v>0</v>
       </c>
-      <c r="AA74" s="16" t="s">
-        <v>34</v>
+      <c r="AA74" s="16">
+        <v>58010001</v>
       </c>
       <c r="AB74" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC74" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AC74" s="16" t="s">
+      <c r="AD74" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="75" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A75" s="16">
-        <v>58060001</v>
+        <v>58040001</v>
       </c>
       <c r="B75" s="16">
         <v>4</v>
       </c>
       <c r="C75" s="16">
-        <v>5806</v>
+        <v>5804</v>
       </c>
       <c r="D75" s="16">
         <v>1</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="G75" s="16" t="s">
         <v>34</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="I75" s="16">
         <v>0</v>
@@ -8531,57 +8867,60 @@
         <v>0</v>
       </c>
       <c r="U75" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V75" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W75" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X75" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y75" s="16">
-        <v>58030001</v>
+        <v>10000</v>
       </c>
       <c r="Z75" s="16">
         <v>0</v>
       </c>
-      <c r="AA75" s="16" t="s">
-        <v>34</v>
+      <c r="AA75" s="16">
+        <v>0</v>
       </c>
       <c r="AB75" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC75" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AC75" s="16" t="s">
+      <c r="AD75" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="76" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A76" s="16">
-        <v>58080001</v>
+        <v>58060001</v>
       </c>
       <c r="B76" s="16">
         <v>4</v>
       </c>
       <c r="C76" s="16">
-        <v>5808</v>
+        <v>5806</v>
       </c>
       <c r="D76" s="16">
         <v>1</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>235</v>
+        <v>234</v>
       </c>
       <c r="G76" s="16" t="s">
         <v>34</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>263</v>
+        <v>262</v>
       </c>
       <c r="I76" s="16">
         <v>0</v>
@@ -8620,235 +8959,244 @@
         <v>0</v>
       </c>
       <c r="U76" s="16">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="V76" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W76" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X76" s="16">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y76" s="16">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="Z76" s="16">
-        <v>58040001</v>
-      </c>
-      <c r="AA76" s="16" t="s">
-        <v>34</v>
+        <v>58030001</v>
+      </c>
+      <c r="AA76" s="16">
+        <v>0</v>
       </c>
       <c r="AB76" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC76" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AC76" s="16" t="s">
+      <c r="AD76" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="77" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A77" s="16">
-        <v>58110001</v>
+        <v>58080001</v>
       </c>
       <c r="B77" s="16">
         <v>4</v>
       </c>
       <c r="C77" s="16">
+        <v>5808</v>
+      </c>
+      <c r="D77" s="16">
+        <v>1</v>
+      </c>
+      <c r="E77" s="12" t="s">
+        <v>153</v>
+      </c>
+      <c r="F77" s="16" t="s">
+        <v>235</v>
+      </c>
+      <c r="G77" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H77" s="16" t="s">
+        <v>263</v>
+      </c>
+      <c r="I77" s="16">
+        <v>0</v>
+      </c>
+      <c r="J77" s="16">
+        <v>0</v>
+      </c>
+      <c r="K77" s="16">
+        <v>0</v>
+      </c>
+      <c r="L77" s="16">
+        <v>0</v>
+      </c>
+      <c r="M77" s="16">
+        <v>0</v>
+      </c>
+      <c r="N77" s="16">
+        <v>0</v>
+      </c>
+      <c r="O77" s="16">
+        <v>0</v>
+      </c>
+      <c r="P77" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q77" s="16">
+        <v>0</v>
+      </c>
+      <c r="R77" s="16">
+        <v>0</v>
+      </c>
+      <c r="S77" s="16">
+        <v>0</v>
+      </c>
+      <c r="T77" s="16">
+        <v>0</v>
+      </c>
+      <c r="U77" s="16">
+        <v>4</v>
+      </c>
+      <c r="V77" s="16">
+        <v>0</v>
+      </c>
+      <c r="W77" s="16">
+        <v>10000</v>
+      </c>
+      <c r="X77" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y77" s="16">
+        <v>10000</v>
+      </c>
+      <c r="Z77" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA77" s="16">
+        <v>58040001</v>
+      </c>
+      <c r="AB77" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC77" s="16" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD77" s="16" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="78" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A78" s="16">
+        <v>58110001</v>
+      </c>
+      <c r="B78" s="16">
+        <v>4</v>
+      </c>
+      <c r="C78" s="16">
         <v>5811</v>
       </c>
-      <c r="D77" s="16">
-        <v>1</v>
-      </c>
-      <c r="E77" s="12" t="s">
+      <c r="D78" s="16">
+        <v>1</v>
+      </c>
+      <c r="E78" s="12" t="s">
         <v>155</v>
       </c>
-      <c r="F77" s="16" t="s">
+      <c r="F78" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="G77" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="H77" s="16" t="s">
+      <c r="G78" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="H78" s="16" t="s">
         <v>264</v>
       </c>
-      <c r="I77" s="16">
-        <v>0</v>
-      </c>
-      <c r="J77" s="16">
-        <v>0</v>
-      </c>
-      <c r="K77" s="16">
-        <v>0</v>
-      </c>
-      <c r="L77" s="16">
-        <v>0</v>
-      </c>
-      <c r="M77" s="16">
-        <v>0</v>
-      </c>
-      <c r="N77" s="16">
-        <v>0</v>
-      </c>
-      <c r="O77" s="16">
-        <v>0</v>
-      </c>
-      <c r="P77" s="16">
-        <v>0</v>
-      </c>
-      <c r="Q77" s="16">
-        <v>0</v>
-      </c>
-      <c r="R77" s="16">
-        <v>0</v>
-      </c>
-      <c r="S77" s="16">
-        <v>0</v>
-      </c>
-      <c r="T77" s="16">
-        <v>0</v>
-      </c>
-      <c r="U77" s="16">
-        <v>0</v>
-      </c>
-      <c r="V77" s="16">
-        <v>10000</v>
-      </c>
-      <c r="W77" s="16">
-        <v>0</v>
-      </c>
-      <c r="X77" s="16">
-        <v>10000</v>
-      </c>
-      <c r="Y77" s="16">
-        <v>0</v>
-      </c>
-      <c r="Z77" s="16">
+      <c r="I78" s="16">
+        <v>0</v>
+      </c>
+      <c r="J78" s="16">
+        <v>0</v>
+      </c>
+      <c r="K78" s="16">
+        <v>0</v>
+      </c>
+      <c r="L78" s="16">
+        <v>0</v>
+      </c>
+      <c r="M78" s="16">
+        <v>0</v>
+      </c>
+      <c r="N78" s="16">
+        <v>0</v>
+      </c>
+      <c r="O78" s="16">
+        <v>0</v>
+      </c>
+      <c r="P78" s="16">
+        <v>0</v>
+      </c>
+      <c r="Q78" s="16">
+        <v>0</v>
+      </c>
+      <c r="R78" s="16">
+        <v>0</v>
+      </c>
+      <c r="S78" s="16">
+        <v>0</v>
+      </c>
+      <c r="T78" s="16">
+        <v>0</v>
+      </c>
+      <c r="U78" s="16">
+        <v>4</v>
+      </c>
+      <c r="V78" s="16">
+        <v>0</v>
+      </c>
+      <c r="W78" s="16">
+        <v>10000</v>
+      </c>
+      <c r="X78" s="16">
+        <v>0</v>
+      </c>
+      <c r="Y78" s="16">
+        <v>10000</v>
+      </c>
+      <c r="Z78" s="16">
+        <v>0</v>
+      </c>
+      <c r="AA78" s="16">
         <v>58050001</v>
       </c>
-      <c r="AA77" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB77" s="16" t="s">
+      <c r="AB78" s="16" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC78" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="AC77" s="16" t="s">
+      <c r="AD78" s="16" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="78" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A78" s="24">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A79" s="24">
         <v>59010001</v>
-      </c>
-      <c r="B78" s="24">
-        <v>4</v>
-      </c>
-      <c r="C78" s="24">
-        <v>5901</v>
-      </c>
-      <c r="D78" s="24">
-        <v>1</v>
-      </c>
-      <c r="E78" s="12" t="s">
-        <v>178</v>
-      </c>
-      <c r="F78" s="24" t="s">
-        <v>236</v>
-      </c>
-      <c r="G78" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="H78" s="24" t="s">
-        <v>179</v>
-      </c>
-      <c r="I78" s="24">
-        <v>0</v>
-      </c>
-      <c r="J78" s="24">
-        <v>0</v>
-      </c>
-      <c r="K78" s="24">
-        <v>0</v>
-      </c>
-      <c r="L78" s="24">
-        <v>0</v>
-      </c>
-      <c r="M78" s="24">
-        <v>0</v>
-      </c>
-      <c r="N78" s="24">
-        <v>0</v>
-      </c>
-      <c r="O78" s="24">
-        <v>0</v>
-      </c>
-      <c r="P78" s="24">
-        <v>0</v>
-      </c>
-      <c r="Q78" s="24">
-        <v>0</v>
-      </c>
-      <c r="R78" s="24">
-        <v>0</v>
-      </c>
-      <c r="S78" s="24">
-        <v>0</v>
-      </c>
-      <c r="T78" s="24">
-        <v>0</v>
-      </c>
-      <c r="U78" s="24">
-        <v>0</v>
-      </c>
-      <c r="V78" s="24">
-        <v>10000</v>
-      </c>
-      <c r="W78" s="24">
-        <v>0</v>
-      </c>
-      <c r="X78" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Y78" s="24">
-        <v>59010001</v>
-      </c>
-      <c r="Z78" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA78" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB78" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC78" s="24" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="79" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A79" s="24">
-        <v>59030001</v>
       </c>
       <c r="B79" s="24">
         <v>4</v>
       </c>
       <c r="C79" s="24">
-        <v>5903</v>
+        <v>5901</v>
       </c>
       <c r="D79" s="24">
         <v>1</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="G79" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
       <c r="I79" s="24">
         <v>0</v>
@@ -8890,54 +9238,57 @@
         <v>0</v>
       </c>
       <c r="V79" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W79" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X79" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y79" s="24">
-        <v>59020001</v>
+        <v>10000</v>
       </c>
       <c r="Z79" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA79" s="24" t="s">
-        <v>34</v>
+        <v>59010001</v>
+      </c>
+      <c r="AA79" s="24">
+        <v>0</v>
       </c>
       <c r="AB79" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC79" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC79" s="24" t="s">
+      <c r="AD79" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="80" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A80" s="24">
-        <v>59050001</v>
+        <v>59030001</v>
       </c>
       <c r="B80" s="24">
         <v>4</v>
       </c>
       <c r="C80" s="24">
-        <v>5905</v>
+        <v>5903</v>
       </c>
       <c r="D80" s="24">
         <v>1</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="G80" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>265</v>
+        <v>115</v>
       </c>
       <c r="I80" s="24">
         <v>0</v>
@@ -8979,54 +9330,57 @@
         <v>0</v>
       </c>
       <c r="V80" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W80" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X80" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y80" s="24">
-        <v>59030001</v>
+        <v>10000</v>
       </c>
       <c r="Z80" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA80" s="24" t="s">
-        <v>34</v>
+        <v>59020001</v>
+      </c>
+      <c r="AA80" s="24">
+        <v>0</v>
       </c>
       <c r="AB80" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC80" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC80" s="24" t="s">
+      <c r="AD80" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="81" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A81" s="24">
-        <v>59070001</v>
+        <v>59050001</v>
       </c>
       <c r="B81" s="24">
         <v>4</v>
       </c>
       <c r="C81" s="24">
-        <v>5907</v>
+        <v>5905</v>
       </c>
       <c r="D81" s="24">
         <v>1</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="G81" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>183</v>
+        <v>265</v>
       </c>
       <c r="I81" s="24">
         <v>0</v>
@@ -9068,54 +9422,57 @@
         <v>0</v>
       </c>
       <c r="V81" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W81" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X81" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y81" s="24">
-        <v>59040001</v>
+        <v>10000</v>
       </c>
       <c r="Z81" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA81" s="24" t="s">
-        <v>34</v>
+        <v>59030001</v>
+      </c>
+      <c r="AA81" s="24">
+        <v>0</v>
       </c>
       <c r="AB81" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC81" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC81" s="24" t="s">
+      <c r="AD81" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="82" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A82" s="24">
-        <v>59090001</v>
+        <v>59070001</v>
       </c>
       <c r="B82" s="24">
         <v>4</v>
       </c>
       <c r="C82" s="24">
-        <v>5909</v>
+        <v>5907</v>
       </c>
       <c r="D82" s="24">
         <v>1</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="G82" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="I82" s="24">
         <v>0</v>
@@ -9157,54 +9514,57 @@
         <v>0</v>
       </c>
       <c r="V82" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W82" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X82" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y82" s="24">
-        <v>59050001</v>
+        <v>10000</v>
       </c>
       <c r="Z82" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA82" s="24" t="s">
-        <v>34</v>
+        <v>59040001</v>
+      </c>
+      <c r="AA82" s="24">
+        <v>0</v>
       </c>
       <c r="AB82" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC82" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC82" s="24" t="s">
+      <c r="AD82" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="83" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A83" s="24">
-        <v>59110001</v>
+        <v>59090001</v>
       </c>
       <c r="B83" s="24">
         <v>4</v>
       </c>
       <c r="C83" s="24">
-        <v>5911</v>
+        <v>5909</v>
       </c>
       <c r="D83" s="24">
         <v>1</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="G83" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I83" s="24">
         <v>0</v>
@@ -9246,54 +9606,57 @@
         <v>0</v>
       </c>
       <c r="V83" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W83" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X83" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y83" s="24">
-        <v>59060001</v>
+        <v>10000</v>
       </c>
       <c r="Z83" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA83" s="24" t="s">
-        <v>34</v>
+        <v>59050001</v>
+      </c>
+      <c r="AA83" s="24">
+        <v>0</v>
       </c>
       <c r="AB83" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC83" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC83" s="24" t="s">
+      <c r="AD83" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="84" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A84" s="24">
-        <v>59130001</v>
+        <v>59110001</v>
       </c>
       <c r="B84" s="24">
         <v>4</v>
       </c>
       <c r="C84" s="24">
-        <v>5913</v>
+        <v>5911</v>
       </c>
       <c r="D84" s="24">
         <v>1</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="G84" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="I84" s="24">
         <v>0</v>
@@ -9335,54 +9698,57 @@
         <v>0</v>
       </c>
       <c r="V84" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W84" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X84" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y84" s="24">
-        <v>59070001</v>
+        <v>10000</v>
       </c>
       <c r="Z84" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA84" s="24" t="s">
-        <v>34</v>
+        <v>59060001</v>
+      </c>
+      <c r="AA84" s="24">
+        <v>0</v>
       </c>
       <c r="AB84" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC84" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC84" s="24" t="s">
+      <c r="AD84" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="85" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A85" s="24">
-        <v>59150001</v>
+        <v>59130001</v>
       </c>
       <c r="B85" s="24">
         <v>4</v>
       </c>
       <c r="C85" s="24">
-        <v>5915</v>
+        <v>5913</v>
       </c>
       <c r="D85" s="24">
         <v>1</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="G85" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="I85" s="24">
         <v>0</v>
@@ -9424,54 +9790,57 @@
         <v>0</v>
       </c>
       <c r="V85" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W85" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X85" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y85" s="24">
-        <v>59080001</v>
+        <v>10000</v>
       </c>
       <c r="Z85" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA85" s="24" t="s">
-        <v>34</v>
+        <v>59070001</v>
+      </c>
+      <c r="AA85" s="24">
+        <v>0</v>
       </c>
       <c r="AB85" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC85" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC85" s="24" t="s">
+      <c r="AD85" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="86" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A86" s="24">
-        <v>59180001</v>
+        <v>59150001</v>
       </c>
       <c r="B86" s="24">
         <v>4</v>
       </c>
       <c r="C86" s="24">
-        <v>5918</v>
+        <v>5915</v>
       </c>
       <c r="D86" s="24">
         <v>1</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="G86" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="I86" s="24">
         <v>0</v>
@@ -9513,54 +9882,57 @@
         <v>0</v>
       </c>
       <c r="V86" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W86" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X86" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y86" s="24">
-        <v>59090001</v>
+        <v>10000</v>
       </c>
       <c r="Z86" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA86" s="24" t="s">
-        <v>34</v>
+        <v>59080001</v>
+      </c>
+      <c r="AA86" s="24">
+        <v>0</v>
       </c>
       <c r="AB86" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC86" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC86" s="24" t="s">
+      <c r="AD86" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="87" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A87" s="24">
-        <v>59200001</v>
+        <v>59180001</v>
       </c>
       <c r="B87" s="24">
         <v>4</v>
       </c>
       <c r="C87" s="24">
-        <v>5920</v>
+        <v>5918</v>
       </c>
       <c r="D87" s="24">
         <v>1</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="G87" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>245</v>
+        <v>193</v>
       </c>
       <c r="I87" s="24">
         <v>0</v>
@@ -9602,54 +9974,57 @@
         <v>0</v>
       </c>
       <c r="V87" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W87" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X87" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y87" s="24">
-        <v>59100001</v>
+        <v>10000</v>
       </c>
       <c r="Z87" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA87" s="24" t="s">
-        <v>34</v>
+        <v>59090001</v>
+      </c>
+      <c r="AA87" s="24">
+        <v>0</v>
       </c>
       <c r="AB87" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC87" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC87" s="24" t="s">
+      <c r="AD87" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="88" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A88" s="24">
-        <v>59220001</v>
+        <v>59200001</v>
       </c>
       <c r="B88" s="24">
         <v>4</v>
       </c>
       <c r="C88" s="24">
-        <v>5922</v>
+        <v>5920</v>
       </c>
       <c r="D88" s="24">
         <v>1</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>195</v>
+        <v>194</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="G88" s="24" t="s">
         <v>34</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="I88" s="24">
         <v>0</v>
@@ -9691,232 +10066,241 @@
         <v>0</v>
       </c>
       <c r="V88" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W88" s="24">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X88" s="24">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y88" s="24">
-        <v>59110001</v>
+        <v>10000</v>
       </c>
       <c r="Z88" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA88" s="24" t="s">
-        <v>34</v>
+        <v>59100001</v>
+      </c>
+      <c r="AA88" s="24">
+        <v>0</v>
       </c>
       <c r="AB88" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC88" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC88" s="24" t="s">
+      <c r="AD88" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="89" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A89" s="24">
-        <v>59240001</v>
+        <v>59220001</v>
       </c>
       <c r="B89" s="24">
         <v>4</v>
       </c>
       <c r="C89" s="24">
+        <v>5922</v>
+      </c>
+      <c r="D89" s="24">
+        <v>1</v>
+      </c>
+      <c r="E89" s="12" t="s">
+        <v>195</v>
+      </c>
+      <c r="F89" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="G89" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H89" s="24" t="s">
+        <v>246</v>
+      </c>
+      <c r="I89" s="24">
+        <v>0</v>
+      </c>
+      <c r="J89" s="24">
+        <v>0</v>
+      </c>
+      <c r="K89" s="24">
+        <v>0</v>
+      </c>
+      <c r="L89" s="24">
+        <v>0</v>
+      </c>
+      <c r="M89" s="24">
+        <v>0</v>
+      </c>
+      <c r="N89" s="24">
+        <v>0</v>
+      </c>
+      <c r="O89" s="24">
+        <v>0</v>
+      </c>
+      <c r="P89" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q89" s="24">
+        <v>0</v>
+      </c>
+      <c r="R89" s="24">
+        <v>0</v>
+      </c>
+      <c r="S89" s="24">
+        <v>0</v>
+      </c>
+      <c r="T89" s="24">
+        <v>0</v>
+      </c>
+      <c r="U89" s="24">
+        <v>0</v>
+      </c>
+      <c r="V89" s="24">
+        <v>0</v>
+      </c>
+      <c r="W89" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X89" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y89" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z89" s="24">
+        <v>59110001</v>
+      </c>
+      <c r="AA89" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB89" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC89" s="24" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD89" s="24" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="90" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A90" s="24">
+        <v>59240001</v>
+      </c>
+      <c r="B90" s="24">
+        <v>4</v>
+      </c>
+      <c r="C90" s="24">
         <v>5924</v>
       </c>
-      <c r="D89" s="24">
-        <v>1</v>
-      </c>
-      <c r="E89" s="12" t="s">
+      <c r="D90" s="24">
+        <v>1</v>
+      </c>
+      <c r="E90" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="F89" s="24" t="s">
+      <c r="F90" s="24" t="s">
         <v>294</v>
       </c>
-      <c r="G89" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="H89" s="24" t="s">
+      <c r="G90" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="H90" s="24" t="s">
         <v>294</v>
       </c>
-      <c r="I89" s="24">
-        <v>0</v>
-      </c>
-      <c r="J89" s="24">
-        <v>0</v>
-      </c>
-      <c r="K89" s="24">
-        <v>0</v>
-      </c>
-      <c r="L89" s="24">
-        <v>0</v>
-      </c>
-      <c r="M89" s="24">
-        <v>0</v>
-      </c>
-      <c r="N89" s="24">
-        <v>0</v>
-      </c>
-      <c r="O89" s="24">
-        <v>0</v>
-      </c>
-      <c r="P89" s="24">
-        <v>0</v>
-      </c>
-      <c r="Q89" s="24">
-        <v>0</v>
-      </c>
-      <c r="R89" s="24">
-        <v>0</v>
-      </c>
-      <c r="S89" s="24">
-        <v>0</v>
-      </c>
-      <c r="T89" s="24">
-        <v>0</v>
-      </c>
-      <c r="U89" s="24">
-        <v>0</v>
-      </c>
-      <c r="V89" s="24">
-        <v>10000</v>
-      </c>
-      <c r="W89" s="24">
-        <v>0</v>
-      </c>
-      <c r="X89" s="24">
-        <v>10000</v>
-      </c>
-      <c r="Y89" s="24">
+      <c r="I90" s="24">
+        <v>0</v>
+      </c>
+      <c r="J90" s="24">
+        <v>0</v>
+      </c>
+      <c r="K90" s="24">
+        <v>0</v>
+      </c>
+      <c r="L90" s="24">
+        <v>0</v>
+      </c>
+      <c r="M90" s="24">
+        <v>0</v>
+      </c>
+      <c r="N90" s="24">
+        <v>0</v>
+      </c>
+      <c r="O90" s="24">
+        <v>0</v>
+      </c>
+      <c r="P90" s="24">
+        <v>0</v>
+      </c>
+      <c r="Q90" s="24">
+        <v>0</v>
+      </c>
+      <c r="R90" s="24">
+        <v>0</v>
+      </c>
+      <c r="S90" s="24">
+        <v>0</v>
+      </c>
+      <c r="T90" s="24">
+        <v>0</v>
+      </c>
+      <c r="U90" s="24">
+        <v>0</v>
+      </c>
+      <c r="V90" s="24">
+        <v>0</v>
+      </c>
+      <c r="W90" s="24">
+        <v>10000</v>
+      </c>
+      <c r="X90" s="24">
+        <v>0</v>
+      </c>
+      <c r="Y90" s="24">
+        <v>10000</v>
+      </c>
+      <c r="Z90" s="24">
         <v>59120001</v>
       </c>
-      <c r="Z89" s="24">
-        <v>0</v>
-      </c>
-      <c r="AA89" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB89" s="24" t="s">
+      <c r="AA90" s="24">
+        <v>0</v>
+      </c>
+      <c r="AB90" s="24" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC90" s="24" t="s">
         <v>61</v>
       </c>
-      <c r="AC89" s="24" t="s">
+      <c r="AD90" s="24" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="90" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A90" s="25">
+    <row r="91" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A91" s="25">
         <v>60010001</v>
-      </c>
-      <c r="B90" s="25">
-        <v>4</v>
-      </c>
-      <c r="C90" s="25">
-        <v>6001</v>
-      </c>
-      <c r="D90" s="25">
-        <v>1</v>
-      </c>
-      <c r="E90" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="F90" s="25" t="s">
-        <v>247</v>
-      </c>
-      <c r="G90" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="H90" s="25" t="s">
-        <v>197</v>
-      </c>
-      <c r="I90" s="25">
-        <v>0</v>
-      </c>
-      <c r="J90" s="25">
-        <v>0</v>
-      </c>
-      <c r="K90" s="25">
-        <v>0</v>
-      </c>
-      <c r="L90" s="25">
-        <v>0</v>
-      </c>
-      <c r="M90" s="25">
-        <v>0</v>
-      </c>
-      <c r="N90" s="25">
-        <v>0</v>
-      </c>
-      <c r="O90" s="25">
-        <v>0</v>
-      </c>
-      <c r="P90" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q90" s="25">
-        <v>0</v>
-      </c>
-      <c r="R90" s="25">
-        <v>0</v>
-      </c>
-      <c r="S90" s="25">
-        <v>0</v>
-      </c>
-      <c r="T90" s="25">
-        <v>0</v>
-      </c>
-      <c r="U90" s="25">
-        <v>0</v>
-      </c>
-      <c r="V90" s="25">
-        <v>10000</v>
-      </c>
-      <c r="W90" s="25">
-        <v>0</v>
-      </c>
-      <c r="X90" s="25">
-        <v>10000</v>
-      </c>
-      <c r="Y90" s="25">
-        <v>60010001</v>
-      </c>
-      <c r="Z90" s="25">
-        <v>0</v>
-      </c>
-      <c r="AA90" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AB90" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AC90" s="25" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="91" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A91" s="25">
-        <v>60030001</v>
       </c>
       <c r="B91" s="25">
         <v>4</v>
       </c>
       <c r="C91" s="25">
-        <v>6003</v>
+        <v>6001</v>
       </c>
       <c r="D91" s="25">
         <v>1</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="G91" s="25" t="s">
         <v>100</v>
       </c>
       <c r="H91" s="25" t="s">
-        <v>266</v>
+        <v>197</v>
       </c>
       <c r="I91" s="25">
         <v>0</v>
@@ -9958,54 +10342,57 @@
         <v>0</v>
       </c>
       <c r="V91" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W91" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X91" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y91" s="25">
-        <v>60020001</v>
+        <v>10000</v>
       </c>
       <c r="Z91" s="25">
-        <v>0</v>
-      </c>
-      <c r="AA91" s="25" t="s">
+        <v>60010001</v>
+      </c>
+      <c r="AA91" s="25">
+        <v>0</v>
+      </c>
+      <c r="AB91" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="AB91" s="25" t="s">
+      <c r="AC91" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="AC91" s="25" t="s">
+      <c r="AD91" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="92" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A92" s="25">
-        <v>60060001</v>
+        <v>60030001</v>
       </c>
       <c r="B92" s="25">
         <v>4</v>
       </c>
       <c r="C92" s="25">
-        <v>6006</v>
+        <v>6003</v>
       </c>
       <c r="D92" s="25">
         <v>1</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="F92" s="25" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="G92" s="25" t="s">
         <v>100</v>
       </c>
       <c r="H92" s="25" t="s">
-        <v>200</v>
+        <v>266</v>
       </c>
       <c r="I92" s="25">
         <v>0</v>
@@ -10047,54 +10434,57 @@
         <v>0</v>
       </c>
       <c r="V92" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W92" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X92" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y92" s="25">
-        <v>60030001</v>
+        <v>10000</v>
       </c>
       <c r="Z92" s="25">
-        <v>0</v>
-      </c>
-      <c r="AA92" s="25" t="s">
+        <v>60020001</v>
+      </c>
+      <c r="AA92" s="25">
+        <v>0</v>
+      </c>
+      <c r="AB92" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="AB92" s="25" t="s">
+      <c r="AC92" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="AC92" s="25" t="s">
+      <c r="AD92" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="93" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A93" s="25">
-        <v>60090001</v>
+        <v>60060001</v>
       </c>
       <c r="B93" s="25">
         <v>4</v>
       </c>
       <c r="C93" s="25">
-        <v>6009</v>
+        <v>6006</v>
       </c>
       <c r="D93" s="25">
         <v>1</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F93" s="25" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="G93" s="25" t="s">
         <v>100</v>
       </c>
       <c r="H93" s="25" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I93" s="25">
         <v>0</v>
@@ -10136,232 +10526,241 @@
         <v>0</v>
       </c>
       <c r="V93" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W93" s="25">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X93" s="25">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y93" s="25">
-        <v>60040001</v>
+        <v>10000</v>
       </c>
       <c r="Z93" s="25">
-        <v>0</v>
-      </c>
-      <c r="AA93" s="25" t="s">
+        <v>60030001</v>
+      </c>
+      <c r="AA93" s="25">
+        <v>0</v>
+      </c>
+      <c r="AB93" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="AB93" s="25" t="s">
+      <c r="AC93" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="AC93" s="25" t="s">
+      <c r="AD93" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="94" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A94" s="25">
-        <v>60110001</v>
+        <v>60090001</v>
       </c>
       <c r="B94" s="25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C94" s="25">
-        <v>6011</v>
+        <v>6009</v>
       </c>
       <c r="D94" s="25">
         <v>1</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>268</v>
+        <v>250</v>
       </c>
       <c r="G94" s="25" t="s">
         <v>100</v>
       </c>
       <c r="H94" s="25" t="s">
+        <v>202</v>
+      </c>
+      <c r="I94" s="25">
+        <v>0</v>
+      </c>
+      <c r="J94" s="25">
+        <v>0</v>
+      </c>
+      <c r="K94" s="25">
+        <v>0</v>
+      </c>
+      <c r="L94" s="25">
+        <v>0</v>
+      </c>
+      <c r="M94" s="25">
+        <v>0</v>
+      </c>
+      <c r="N94" s="25">
+        <v>0</v>
+      </c>
+      <c r="O94" s="25">
+        <v>0</v>
+      </c>
+      <c r="P94" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q94" s="25">
+        <v>0</v>
+      </c>
+      <c r="R94" s="25">
+        <v>0</v>
+      </c>
+      <c r="S94" s="25">
+        <v>0</v>
+      </c>
+      <c r="T94" s="25">
+        <v>0</v>
+      </c>
+      <c r="U94" s="25">
+        <v>0</v>
+      </c>
+      <c r="V94" s="25">
+        <v>0</v>
+      </c>
+      <c r="W94" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X94" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y94" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z94" s="25">
+        <v>60040001</v>
+      </c>
+      <c r="AA94" s="25">
+        <v>0</v>
+      </c>
+      <c r="AB94" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="AC94" s="25" t="s">
+        <v>63</v>
+      </c>
+      <c r="AD94" s="25" t="s">
+        <v>64</v>
+      </c>
+    </row>
+    <row r="95" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A95" s="25">
+        <v>60110001</v>
+      </c>
+      <c r="B95" s="25">
+        <v>6</v>
+      </c>
+      <c r="C95" s="25">
+        <v>6011</v>
+      </c>
+      <c r="D95" s="25">
+        <v>1</v>
+      </c>
+      <c r="E95" s="12" t="s">
+        <v>203</v>
+      </c>
+      <c r="F95" s="25" t="s">
+        <v>268</v>
+      </c>
+      <c r="G95" s="25" t="s">
+        <v>100</v>
+      </c>
+      <c r="H95" s="25" t="s">
         <v>267</v>
       </c>
-      <c r="I94" s="25">
-        <v>0</v>
-      </c>
-      <c r="J94" s="25">
-        <v>0</v>
-      </c>
-      <c r="K94" s="25">
-        <v>0</v>
-      </c>
-      <c r="L94" s="25">
-        <v>0</v>
-      </c>
-      <c r="M94" s="25">
-        <v>0</v>
-      </c>
-      <c r="N94" s="25">
-        <v>0</v>
-      </c>
-      <c r="O94" s="25">
-        <v>0</v>
-      </c>
-      <c r="P94" s="25">
-        <v>0</v>
-      </c>
-      <c r="Q94" s="25">
-        <v>0</v>
-      </c>
-      <c r="R94" s="25">
-        <v>0</v>
-      </c>
-      <c r="S94" s="25">
-        <v>0</v>
-      </c>
-      <c r="T94" s="25">
-        <v>0</v>
-      </c>
-      <c r="U94" s="25">
-        <v>0</v>
-      </c>
-      <c r="V94" s="25">
-        <v>10000</v>
-      </c>
-      <c r="W94" s="25">
-        <v>0</v>
-      </c>
-      <c r="X94" s="25">
-        <v>10000</v>
-      </c>
-      <c r="Y94" s="25">
+      <c r="I95" s="25">
+        <v>0</v>
+      </c>
+      <c r="J95" s="25">
+        <v>0</v>
+      </c>
+      <c r="K95" s="25">
+        <v>0</v>
+      </c>
+      <c r="L95" s="25">
+        <v>0</v>
+      </c>
+      <c r="M95" s="25">
+        <v>0</v>
+      </c>
+      <c r="N95" s="25">
+        <v>0</v>
+      </c>
+      <c r="O95" s="25">
+        <v>0</v>
+      </c>
+      <c r="P95" s="25">
+        <v>0</v>
+      </c>
+      <c r="Q95" s="25">
+        <v>0</v>
+      </c>
+      <c r="R95" s="25">
+        <v>0</v>
+      </c>
+      <c r="S95" s="25">
+        <v>0</v>
+      </c>
+      <c r="T95" s="25">
+        <v>0</v>
+      </c>
+      <c r="U95" s="25">
+        <v>0</v>
+      </c>
+      <c r="V95" s="25">
+        <v>0</v>
+      </c>
+      <c r="W95" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X95" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y95" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z95" s="25">
         <v>60070001</v>
       </c>
-      <c r="Z94" s="26" t="s">
+      <c r="AA95" s="26" t="s">
         <v>204</v>
       </c>
-      <c r="AA94" s="25" t="s">
+      <c r="AB95" s="25" t="s">
         <v>100</v>
       </c>
-      <c r="AB94" s="25" t="s">
+      <c r="AC95" s="25" t="s">
         <v>63</v>
       </c>
-      <c r="AC94" s="25" t="s">
+      <c r="AD95" s="25" t="s">
         <v>64</v>
       </c>
     </row>
-    <row r="95" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A95" s="27">
+    <row r="96" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A96" s="27">
         <v>61020001</v>
-      </c>
-      <c r="B95" s="27">
-        <v>4</v>
-      </c>
-      <c r="C95" s="27">
-        <v>6102</v>
-      </c>
-      <c r="D95" s="27">
-        <v>1</v>
-      </c>
-      <c r="E95" s="12" t="s">
-        <v>205</v>
-      </c>
-      <c r="F95" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="G95" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H95" s="27" t="s">
-        <v>206</v>
-      </c>
-      <c r="I95" s="27">
-        <v>0</v>
-      </c>
-      <c r="J95" s="27">
-        <v>0</v>
-      </c>
-      <c r="K95" s="27">
-        <v>0</v>
-      </c>
-      <c r="L95" s="27">
-        <v>0</v>
-      </c>
-      <c r="M95" s="27">
-        <v>0</v>
-      </c>
-      <c r="N95" s="27">
-        <v>0</v>
-      </c>
-      <c r="O95" s="27">
-        <v>0</v>
-      </c>
-      <c r="P95" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q95" s="27">
-        <v>0</v>
-      </c>
-      <c r="R95" s="27">
-        <v>0</v>
-      </c>
-      <c r="S95" s="27">
-        <v>0</v>
-      </c>
-      <c r="T95" s="27">
-        <v>0</v>
-      </c>
-      <c r="U95" s="27">
-        <v>0</v>
-      </c>
-      <c r="V95" s="27">
-        <v>10000</v>
-      </c>
-      <c r="W95" s="27">
-        <v>0</v>
-      </c>
-      <c r="X95" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Y95" s="27">
-        <v>61010001</v>
-      </c>
-      <c r="Z95" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA95" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB95" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AC95" s="27" t="s">
-        <v>62</v>
-      </c>
-    </row>
-    <row r="96" spans="1:29" x14ac:dyDescent="0.15">
-      <c r="A96" s="27">
-        <v>61040001</v>
       </c>
       <c r="B96" s="27">
         <v>4</v>
       </c>
       <c r="C96" s="27">
-        <v>6104</v>
+        <v>6102</v>
       </c>
       <c r="D96" s="27">
         <v>1</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="F96" s="27" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="G96" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H96" s="27" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="I96" s="27">
         <v>0</v>
@@ -10403,54 +10802,57 @@
         <v>0</v>
       </c>
       <c r="V96" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W96" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X96" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y96" s="27">
-        <v>61020001</v>
+        <v>10000</v>
       </c>
       <c r="Z96" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA96" s="27" t="s">
-        <v>34</v>
+        <v>61010001</v>
+      </c>
+      <c r="AA96" s="27">
+        <v>0</v>
       </c>
       <c r="AB96" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC96" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC96" s="27" t="s">
+      <c r="AD96" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="97" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A97" s="27">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="B97" s="27">
         <v>4</v>
       </c>
       <c r="C97" s="27">
-        <v>6106</v>
+        <v>6104</v>
       </c>
       <c r="D97" s="27">
         <v>1</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="F97" s="27" t="s">
-        <v>270</v>
+        <v>208</v>
       </c>
       <c r="G97" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H97" s="27" t="s">
-        <v>271</v>
+        <v>208</v>
       </c>
       <c r="I97" s="27">
         <v>0</v>
@@ -10492,54 +10894,57 @@
         <v>0</v>
       </c>
       <c r="V97" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W97" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X97" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y97" s="27">
-        <v>61030001</v>
+        <v>10000</v>
       </c>
       <c r="Z97" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA97" s="27" t="s">
-        <v>34</v>
+        <v>61020001</v>
+      </c>
+      <c r="AA97" s="27">
+        <v>0</v>
       </c>
       <c r="AB97" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC97" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC97" s="27" t="s">
+      <c r="AD97" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="98" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A98" s="27">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="B98" s="27">
         <v>4</v>
       </c>
       <c r="C98" s="27">
-        <v>6108</v>
+        <v>6106</v>
       </c>
       <c r="D98" s="27">
         <v>1</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F98" s="27" t="s">
-        <v>95</v>
+        <v>270</v>
       </c>
       <c r="G98" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H98" s="27" t="s">
-        <v>95</v>
+        <v>271</v>
       </c>
       <c r="I98" s="27">
         <v>0</v>
@@ -10581,54 +10986,57 @@
         <v>0</v>
       </c>
       <c r="V98" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W98" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X98" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y98" s="27">
-        <v>61040001</v>
+        <v>10000</v>
       </c>
       <c r="Z98" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA98" s="27" t="s">
-        <v>34</v>
+        <v>61030001</v>
+      </c>
+      <c r="AA98" s="27">
+        <v>0</v>
       </c>
       <c r="AB98" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC98" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC98" s="27" t="s">
+      <c r="AD98" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="99" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A99" s="27">
-        <v>61100001</v>
+        <v>61080001</v>
       </c>
       <c r="B99" s="27">
         <v>4</v>
       </c>
       <c r="C99" s="27">
-        <v>6110</v>
+        <v>6108</v>
       </c>
       <c r="D99" s="27">
         <v>1</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="F99" s="27" t="s">
-        <v>212</v>
+        <v>95</v>
       </c>
       <c r="G99" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H99" s="27" t="s">
-        <v>212</v>
+        <v>95</v>
       </c>
       <c r="I99" s="27">
         <v>0</v>
@@ -10670,54 +11078,57 @@
         <v>0</v>
       </c>
       <c r="V99" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W99" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X99" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y99" s="27">
-        <v>61050001</v>
+        <v>10000</v>
       </c>
       <c r="Z99" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA99" s="27" t="s">
-        <v>34</v>
+        <v>61040001</v>
+      </c>
+      <c r="AA99" s="27">
+        <v>0</v>
       </c>
       <c r="AB99" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC99" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC99" s="27" t="s">
+      <c r="AD99" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="100" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A100" s="27">
-        <v>61120001</v>
+        <v>61100001</v>
       </c>
       <c r="B100" s="27">
         <v>4</v>
       </c>
       <c r="C100" s="27">
-        <v>6112</v>
+        <v>6110</v>
       </c>
       <c r="D100" s="27">
         <v>1</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F100" s="27" t="s">
-        <v>272</v>
+        <v>212</v>
       </c>
       <c r="G100" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H100" s="27" t="s">
-        <v>273</v>
+        <v>212</v>
       </c>
       <c r="I100" s="27">
         <v>0</v>
@@ -10759,54 +11170,57 @@
         <v>0</v>
       </c>
       <c r="V100" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W100" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X100" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y100" s="27">
-        <v>61060001</v>
+        <v>10000</v>
       </c>
       <c r="Z100" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA100" s="27" t="s">
-        <v>34</v>
+        <v>61050001</v>
+      </c>
+      <c r="AA100" s="27">
+        <v>0</v>
       </c>
       <c r="AB100" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC100" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC100" s="27" t="s">
+      <c r="AD100" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="101" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A101" s="27">
-        <v>61140001</v>
+        <v>61120001</v>
       </c>
       <c r="B101" s="27">
         <v>4</v>
       </c>
       <c r="C101" s="27">
-        <v>6114</v>
+        <v>6112</v>
       </c>
       <c r="D101" s="27">
         <v>1</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F101" s="27" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="G101" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H101" s="27" t="s">
-        <v>215</v>
+        <v>273</v>
       </c>
       <c r="I101" s="27">
         <v>0</v>
@@ -10848,54 +11262,57 @@
         <v>0</v>
       </c>
       <c r="V101" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W101" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X101" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y101" s="27">
-        <v>61070001</v>
+        <v>10000</v>
       </c>
       <c r="Z101" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA101" s="27" t="s">
-        <v>34</v>
+        <v>61060001</v>
+      </c>
+      <c r="AA101" s="27">
+        <v>0</v>
       </c>
       <c r="AB101" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC101" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC101" s="27" t="s">
+      <c r="AD101" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="102" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A102" s="27">
-        <v>61160001</v>
+        <v>61140001</v>
       </c>
       <c r="B102" s="27">
         <v>4</v>
       </c>
       <c r="C102" s="27">
-        <v>6116</v>
+        <v>6114</v>
       </c>
       <c r="D102" s="27">
         <v>1</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F102" s="27" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="G102" s="27" t="s">
         <v>34</v>
       </c>
       <c r="H102" s="27" t="s">
-        <v>275</v>
+        <v>215</v>
       </c>
       <c r="I102" s="27">
         <v>0</v>
@@ -10937,121 +11354,219 @@
         <v>0</v>
       </c>
       <c r="V102" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="W102" s="27">
-        <v>0</v>
+        <v>10000</v>
       </c>
       <c r="X102" s="27">
-        <v>10000</v>
+        <v>0</v>
       </c>
       <c r="Y102" s="27">
-        <v>61080001</v>
+        <v>10000</v>
       </c>
       <c r="Z102" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA102" s="27" t="s">
-        <v>34</v>
+        <v>61070001</v>
+      </c>
+      <c r="AA102" s="27">
+        <v>0</v>
       </c>
       <c r="AB102" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC102" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC102" s="27" t="s">
+      <c r="AD102" s="27" t="s">
         <v>62</v>
       </c>
     </row>
-    <row r="103" spans="1:29" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:30" x14ac:dyDescent="0.15">
       <c r="A103" s="27">
-        <v>61180001</v>
+        <v>61160001</v>
       </c>
       <c r="B103" s="27">
         <v>4</v>
       </c>
       <c r="C103" s="27">
+        <v>6116</v>
+      </c>
+      <c r="D103" s="27">
+        <v>1</v>
+      </c>
+      <c r="E103" s="12" t="s">
+        <v>216</v>
+      </c>
+      <c r="F103" s="27" t="s">
+        <v>276</v>
+      </c>
+      <c r="G103" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="H103" s="27" t="s">
+        <v>275</v>
+      </c>
+      <c r="I103" s="27">
+        <v>0</v>
+      </c>
+      <c r="J103" s="27">
+        <v>0</v>
+      </c>
+      <c r="K103" s="27">
+        <v>0</v>
+      </c>
+      <c r="L103" s="27">
+        <v>0</v>
+      </c>
+      <c r="M103" s="27">
+        <v>0</v>
+      </c>
+      <c r="N103" s="27">
+        <v>0</v>
+      </c>
+      <c r="O103" s="27">
+        <v>0</v>
+      </c>
+      <c r="P103" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q103" s="27">
+        <v>0</v>
+      </c>
+      <c r="R103" s="27">
+        <v>0</v>
+      </c>
+      <c r="S103" s="27">
+        <v>0</v>
+      </c>
+      <c r="T103" s="27">
+        <v>0</v>
+      </c>
+      <c r="U103" s="27">
+        <v>0</v>
+      </c>
+      <c r="V103" s="27">
+        <v>0</v>
+      </c>
+      <c r="W103" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X103" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y103" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z103" s="27">
+        <v>61080001</v>
+      </c>
+      <c r="AA103" s="27">
+        <v>0</v>
+      </c>
+      <c r="AB103" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC103" s="27" t="s">
+        <v>61</v>
+      </c>
+      <c r="AD103" s="27" t="s">
+        <v>62</v>
+      </c>
+    </row>
+    <row r="104" spans="1:30" x14ac:dyDescent="0.15">
+      <c r="A104" s="27">
+        <v>61180001</v>
+      </c>
+      <c r="B104" s="27">
+        <v>4</v>
+      </c>
+      <c r="C104" s="27">
         <v>6118</v>
       </c>
-      <c r="D103" s="27">
-        <v>1</v>
-      </c>
-      <c r="E103" s="12" t="s">
+      <c r="D104" s="27">
+        <v>1</v>
+      </c>
+      <c r="E104" s="12" t="s">
         <v>217</v>
       </c>
-      <c r="F103" s="27" t="s">
+      <c r="F104" s="27" t="s">
         <v>278</v>
       </c>
-      <c r="G103" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="H103" s="27" t="s">
+      <c r="G104" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="H104" s="27" t="s">
         <v>277</v>
       </c>
-      <c r="I103" s="27">
-        <v>0</v>
-      </c>
-      <c r="J103" s="27">
-        <v>0</v>
-      </c>
-      <c r="K103" s="27">
-        <v>0</v>
-      </c>
-      <c r="L103" s="27">
-        <v>0</v>
-      </c>
-      <c r="M103" s="27">
-        <v>0</v>
-      </c>
-      <c r="N103" s="27">
-        <v>0</v>
-      </c>
-      <c r="O103" s="27">
-        <v>0</v>
-      </c>
-      <c r="P103" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q103" s="27">
-        <v>0</v>
-      </c>
-      <c r="R103" s="27">
-        <v>0</v>
-      </c>
-      <c r="S103" s="27">
-        <v>0</v>
-      </c>
-      <c r="T103" s="27">
-        <v>0</v>
-      </c>
-      <c r="U103" s="27">
-        <v>0</v>
-      </c>
-      <c r="V103" s="27">
-        <v>10000</v>
-      </c>
-      <c r="W103" s="27">
-        <v>0</v>
-      </c>
-      <c r="X103" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Y103" s="27">
+      <c r="I104" s="27">
+        <v>0</v>
+      </c>
+      <c r="J104" s="27">
+        <v>0</v>
+      </c>
+      <c r="K104" s="27">
+        <v>0</v>
+      </c>
+      <c r="L104" s="27">
+        <v>0</v>
+      </c>
+      <c r="M104" s="27">
+        <v>0</v>
+      </c>
+      <c r="N104" s="27">
+        <v>0</v>
+      </c>
+      <c r="O104" s="27">
+        <v>0</v>
+      </c>
+      <c r="P104" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="27">
+        <v>0</v>
+      </c>
+      <c r="R104" s="27">
+        <v>0</v>
+      </c>
+      <c r="S104" s="27">
+        <v>0</v>
+      </c>
+      <c r="T104" s="27">
+        <v>0</v>
+      </c>
+      <c r="U104" s="27">
+        <v>0</v>
+      </c>
+      <c r="V104" s="27">
+        <v>0</v>
+      </c>
+      <c r="W104" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X104" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z104" s="27">
         <v>61090001</v>
       </c>
-      <c r="Z103" s="27">
-        <v>0</v>
-      </c>
-      <c r="AA103" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AB103" s="27" t="s">
+      <c r="AA104" s="27">
+        <v>0</v>
+      </c>
+      <c r="AB104" s="27" t="s">
+        <v>34</v>
+      </c>
+      <c r="AC104" s="27" t="s">
         <v>61</v>
       </c>
-      <c r="AC103" s="27" t="s">
+      <c r="AD104" s="27" t="s">
         <v>62</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AA77" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AB104" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A04FC212-D0B1-4530-9E46-1D26952C6008}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0797EAF7-B638-4AEB-9F2B-E48BABD15539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -1,22 +1,22 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28827"/>
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{0797EAF7-B638-4AEB-9F2B-E48BABD15539}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28465B04-19DD-41AD-875D-2B6DFCA8A82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AB$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$104</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -288,74 +288,12 @@
         </r>
       </text>
     </comment>
-    <comment ref="AC4" authorId="1" shapeId="0" xr:uid="{01D943CF-AECD-4005-A6CE-59046F14F27A}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1 死亡
-2 非死亡
-3 安全
-4 非安全
-5 无敌
-6 非无敌
-7 隐身
-8 非隐身
-9 定身
-10 非定身
-11 混乱
-12 非混乱
-13 在水面
-14 不在水面
-15 麻痹
-16 非麻痹
-17 眩晕
-18 非眩晕</t>
-        </r>
-      </text>
-    </comment>
-    <comment ref="AD4" authorId="1" shapeId="0" xr:uid="{FF5772BF-0DF9-41C0-B44E-0880B3623722}">
-      <text>
-        <r>
-          <rPr>
-            <b/>
-            <sz val="9"/>
-            <rFont val="宋体"/>
-            <family val="3"/>
-            <charset val="134"/>
-          </rPr>
-          <t>1 死亡
-2 非死亡
-3 安全
-4 非安全
-5 无敌
-6 非无敌
-7 隐身
-8 非隐身
-9 定身
-10 非定身
-11 混乱
-12 非混乱
-13 在水面
-14 不在水面
-15 麻痹
-16 非麻痹
-17 眩晕
-18 非眩晕</t>
-        </r>
-      </text>
-    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="775" uniqueCount="303">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="292">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -411,9 +349,6 @@
     <t>target_effect</t>
   </si>
   <si>
-    <t>target_effect_pro</t>
-  </si>
-  <si>
     <t>技能id</t>
   </si>
   <si>
@@ -456,9 +391,6 @@
     <t>释放后对目标效果</t>
   </si>
   <si>
-    <t>效果同组几率</t>
-  </si>
-  <si>
     <t>0:0</t>
   </si>
   <si>
@@ -545,32 +477,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>is_allow</t>
-  </si>
-  <si>
-    <t>is_target</t>
-  </si>
-  <si>
-    <t>允许释放状态</t>
-  </si>
-  <si>
-    <t>能被选中的目标状态</t>
-  </si>
-  <si>
-    <t>2,4,5,6,7,8,9,10,12,14,16,18</t>
-  </si>
-  <si>
-    <t>2,4,6,8,9,10,11,12,14,15,16,17,18</t>
-  </si>
-  <si>
-    <t>2,4,5,6,7,8,9,10,12,14,16,18</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
-    <t>2,4,6,8,9,10,11,12,14,15,16,17,18</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>level</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
@@ -617,9 +523,6 @@
   </si>
   <si>
     <t>LIST&lt;INT&gt;_S_C</t>
-  </si>
-  <si>
-    <t>MAP&lt;INT:INT&gt;_S_C</t>
   </si>
   <si>
     <t>属性id-击中回血</t>
@@ -2085,7 +1988,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AD104"/>
+  <dimension ref="A1:AA104"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -2110,110 +2013,98 @@
     <col min="25" max="25" width="19.25" style="5" bestFit="1" customWidth="1"/>
     <col min="26" max="26" width="14.25" style="5" bestFit="1" customWidth="1"/>
     <col min="27" max="27" width="15.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.875" style="5" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="24.125" style="5" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="28.25" style="5" bestFit="1" customWidth="1"/>
-    <col min="31" max="16384" width="9" style="5"/>
+    <col min="28" max="16384" width="9" style="5"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="2" spans="1:30" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="2" spans="1:27" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="B2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="C2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="D2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="E2" s="6" t="s">
         <v>2</v>
       </c>
       <c r="F2" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="G2" s="5" t="s">
-        <v>77</v>
+        <v>67</v>
       </c>
       <c r="H2" s="5" t="s">
-        <v>76</v>
+        <v>66</v>
       </c>
       <c r="I2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="J2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="K2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="L2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="M2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="N2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="O2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="P2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="Q2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="R2" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="S2" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="T2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="U2" s="33" t="s">
-        <v>300</v>
+        <v>289</v>
       </c>
       <c r="V2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="W2" s="5" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="X2" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="Y2" s="1" t="s">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="Z2" s="5" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
       <c r="AA2" s="5" t="s">
-        <v>78</v>
-      </c>
-      <c r="AB2" s="5" t="s">
-        <v>79</v>
-      </c>
-      <c r="AC2" s="1" t="s">
-        <v>78</v>
-      </c>
-      <c r="AD2" s="1" t="s">
-        <v>78</v>
+        <v>68</v>
       </c>
     </row>
-    <row r="3" spans="1:30" ht="13.5" x14ac:dyDescent="0.15">
+    <row r="3" spans="1:27" ht="13.5" x14ac:dyDescent="0.15">
       <c r="A3" s="5" t="s">
         <v>3</v>
       </c>
@@ -2224,7 +2115,7 @@
         <v>5</v>
       </c>
       <c r="D3" s="5" t="s">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="E3" s="6" t="s">
         <v>6</v>
@@ -2239,19 +2130,19 @@
         <v>9</v>
       </c>
       <c r="I3" s="5" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="J3" s="5" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="K3" s="5" t="s">
         <v>10</v>
       </c>
       <c r="L3" s="5" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="M3" s="5" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="N3" s="5" t="s">
         <v>11</v>
@@ -2260,34 +2151,34 @@
         <v>12</v>
       </c>
       <c r="P3" s="5" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="Q3" s="5" t="s">
         <v>13</v>
       </c>
       <c r="R3" s="1" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="S3" s="1" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="T3" s="5" t="s">
         <v>14</v>
       </c>
       <c r="U3" s="33" t="s">
-        <v>299</v>
+        <v>288</v>
       </c>
       <c r="V3" s="5" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="W3" s="5" t="s">
         <v>15</v>
       </c>
       <c r="X3" s="1" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y3" s="1" t="s">
         <v>42</v>
-      </c>
-      <c r="Y3" s="1" t="s">
-        <v>44</v>
       </c>
       <c r="Z3" s="5" t="s">
         <v>16</v>
@@ -2295,109 +2186,91 @@
       <c r="AA3" s="5" t="s">
         <v>17</v>
       </c>
-      <c r="AB3" s="5" t="s">
+    </row>
+    <row r="4" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
+      <c r="A4" s="5" t="s">
         <v>18</v>
       </c>
-      <c r="AC3" s="1" t="s">
-        <v>57</v>
-      </c>
-      <c r="AD3" s="1" t="s">
-        <v>58</v>
+      <c r="B4" s="5" t="s">
+        <v>19</v>
+      </c>
+      <c r="C4" s="5" t="s">
+        <v>20</v>
+      </c>
+      <c r="D4" s="5" t="s">
+        <v>56</v>
+      </c>
+      <c r="E4" s="6" t="s">
+        <v>21</v>
+      </c>
+      <c r="F4" s="5" t="s">
+        <v>21</v>
+      </c>
+      <c r="G4" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="H4" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="I4" s="5" t="s">
+        <v>49</v>
+      </c>
+      <c r="J4" s="5" t="s">
+        <v>39</v>
+      </c>
+      <c r="K4" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="L4" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="M4" s="5" t="s">
+        <v>46</v>
+      </c>
+      <c r="N4" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="O4" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="P4" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="Q4" s="5" t="s">
+        <v>63</v>
+      </c>
+      <c r="R4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="S4" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="T4" s="5" t="s">
+        <v>28</v>
+      </c>
+      <c r="U4" s="33" t="s">
+        <v>290</v>
+      </c>
+      <c r="V4" s="5" t="s">
+        <v>35</v>
+      </c>
+      <c r="W4" s="5" t="s">
+        <v>29</v>
+      </c>
+      <c r="X4" s="5" t="s">
+        <v>41</v>
+      </c>
+      <c r="Y4" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="Z4" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="AA4" s="5" t="s">
+        <v>31</v>
       </c>
     </row>
-    <row r="4" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
-      <c r="A4" s="5" t="s">
-        <v>19</v>
-      </c>
-      <c r="B4" s="5" t="s">
-        <v>20</v>
-      </c>
-      <c r="C4" s="5" t="s">
-        <v>21</v>
-      </c>
-      <c r="D4" s="5" t="s">
-        <v>66</v>
-      </c>
-      <c r="E4" s="6" t="s">
-        <v>22</v>
-      </c>
-      <c r="F4" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="G4" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="H4" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="I4" s="5" t="s">
-        <v>51</v>
-      </c>
-      <c r="J4" s="5" t="s">
-        <v>41</v>
-      </c>
-      <c r="K4" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="L4" s="5" t="s">
-        <v>49</v>
-      </c>
-      <c r="M4" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="N4" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="O4" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="P4" s="5" t="s">
-        <v>28</v>
-      </c>
-      <c r="Q4" s="5" t="s">
-        <v>73</v>
-      </c>
-      <c r="R4" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="S4" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="T4" s="5" t="s">
-        <v>29</v>
-      </c>
-      <c r="U4" s="33" t="s">
-        <v>301</v>
-      </c>
-      <c r="V4" s="5" t="s">
-        <v>37</v>
-      </c>
-      <c r="W4" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="X4" s="5" t="s">
-        <v>43</v>
-      </c>
-      <c r="Y4" s="5" t="s">
-        <v>45</v>
-      </c>
-      <c r="Z4" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="AA4" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="AB4" s="5" t="s">
-        <v>33</v>
-      </c>
-      <c r="AC4" s="5" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD4" s="5" t="s">
-        <v>60</v>
-      </c>
-    </row>
-    <row r="5" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A5" s="7">
         <v>10101</v>
       </c>
@@ -2411,13 +2284,13 @@
         <v>1</v>
       </c>
       <c r="E5" s="8" t="s">
-        <v>67</v>
+        <v>57</v>
       </c>
       <c r="F5" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G5" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H5" s="9"/>
       <c r="I5" s="9">
@@ -2454,7 +2327,7 @@
         <v>1</v>
       </c>
       <c r="T5" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U5" s="34">
         <v>0</v>
@@ -2477,17 +2350,8 @@
       <c r="AA5" s="10">
         <v>0</v>
       </c>
-      <c r="AB5" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC5" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD5" s="10" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="6" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A6" s="7">
         <v>10102</v>
       </c>
@@ -2501,13 +2365,13 @@
         <v>1</v>
       </c>
       <c r="E6" s="8" t="s">
-        <v>68</v>
+        <v>58</v>
       </c>
       <c r="F6" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G6" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H6" s="9"/>
       <c r="I6" s="9">
@@ -2544,7 +2408,7 @@
         <v>1</v>
       </c>
       <c r="T6" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U6" s="34">
         <v>0</v>
@@ -2567,17 +2431,8 @@
       <c r="AA6" s="10">
         <v>0</v>
       </c>
-      <c r="AB6" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC6" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD6" s="10" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="7" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A7" s="7">
         <v>10201</v>
       </c>
@@ -2591,13 +2446,13 @@
         <v>2</v>
       </c>
       <c r="E7" s="8" t="s">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="F7" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G7" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H7" s="9"/>
       <c r="I7" s="9">
@@ -2634,7 +2489,7 @@
         <v>1</v>
       </c>
       <c r="T7" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U7" s="34">
         <v>0</v>
@@ -2657,17 +2512,8 @@
       <c r="AA7" s="10">
         <v>0</v>
       </c>
-      <c r="AB7" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC7" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD7" s="10" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="8" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A8" s="7">
         <v>10202</v>
       </c>
@@ -2681,13 +2527,13 @@
         <v>2</v>
       </c>
       <c r="E8" s="8" t="s">
-        <v>71</v>
+        <v>61</v>
       </c>
       <c r="F8" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G8" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H8" s="9"/>
       <c r="I8" s="9">
@@ -2724,7 +2570,7 @@
         <v>1</v>
       </c>
       <c r="T8" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U8" s="34">
         <v>0</v>
@@ -2747,17 +2593,8 @@
       <c r="AA8" s="10">
         <v>0</v>
       </c>
-      <c r="AB8" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC8" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD8" s="10" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="9" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A9" s="7">
         <v>10301</v>
       </c>
@@ -2771,13 +2608,13 @@
         <v>3</v>
       </c>
       <c r="E9" s="8" t="s">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F9" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G9" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H9" s="9"/>
       <c r="I9" s="9">
@@ -2814,7 +2651,7 @@
         <v>1</v>
       </c>
       <c r="T9" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U9" s="34">
         <v>0</v>
@@ -2837,17 +2674,8 @@
       <c r="AA9" s="10">
         <v>0</v>
       </c>
-      <c r="AB9" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC9" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD9" s="10" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="10" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A10" s="7">
         <v>10302</v>
       </c>
@@ -2861,13 +2689,13 @@
         <v>3</v>
       </c>
       <c r="E10" s="8" t="s">
-        <v>72</v>
+        <v>62</v>
       </c>
       <c r="F10" s="7" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="G10" s="9" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H10" s="9"/>
       <c r="I10" s="9">
@@ -2904,7 +2732,7 @@
         <v>1</v>
       </c>
       <c r="T10" s="9">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10" s="34">
         <v>0</v>
@@ -2927,17 +2755,8 @@
       <c r="AA10" s="10">
         <v>0</v>
       </c>
-      <c r="AB10" s="10" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC10" s="10" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD10" s="10" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="11" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A11" s="2">
         <v>20001</v>
       </c>
@@ -2951,16 +2770,16 @@
         <v>1</v>
       </c>
       <c r="E11" s="11" t="s">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I11" s="2">
         <v>0</v>
@@ -3019,17 +2838,8 @@
       <c r="AA11" s="2">
         <v>0</v>
       </c>
-      <c r="AB11" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC11" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD11" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="12" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A12" s="2">
         <v>20010001</v>
       </c>
@@ -3043,16 +2853,16 @@
         <v>1</v>
       </c>
       <c r="E12" s="11" t="s">
-        <v>158</v>
+        <v>147</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I12" s="2">
         <v>0</v>
@@ -3111,17 +2921,8 @@
       <c r="AA12" s="2">
         <v>0</v>
       </c>
-      <c r="AB12" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC12" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD12" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="13" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A13" s="2">
         <v>20020001</v>
       </c>
@@ -3135,16 +2936,16 @@
         <v>1</v>
       </c>
       <c r="E13" s="11" t="s">
-        <v>159</v>
+        <v>148</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I13" s="2">
         <v>0</v>
@@ -3203,17 +3004,8 @@
       <c r="AA13" s="2">
         <v>0</v>
       </c>
-      <c r="AB13" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC13" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD13" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="14" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A14" s="2">
         <v>20030001</v>
       </c>
@@ -3227,16 +3019,16 @@
         <v>1</v>
       </c>
       <c r="E14" s="11" t="s">
-        <v>160</v>
+        <v>149</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H14" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I14" s="2">
         <v>0</v>
@@ -3295,17 +3087,8 @@
       <c r="AA14" s="2">
         <v>0</v>
       </c>
-      <c r="AB14" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC14" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD14" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="15" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A15" s="2">
         <v>20040001</v>
       </c>
@@ -3319,16 +3102,16 @@
         <v>1</v>
       </c>
       <c r="E15" s="11" t="s">
-        <v>161</v>
+        <v>150</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H15" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I15" s="2">
         <v>0</v>
@@ -3387,17 +3170,8 @@
       <c r="AA15" s="2">
         <v>0</v>
       </c>
-      <c r="AB15" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC15" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD15" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="16" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A16" s="2">
         <v>20050001</v>
       </c>
@@ -3411,16 +3185,16 @@
         <v>1</v>
       </c>
       <c r="E16" s="11" t="s">
-        <v>162</v>
+        <v>151</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H16" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I16" s="2">
         <v>2000</v>
@@ -3479,17 +3253,8 @@
       <c r="AA16" s="2">
         <v>0</v>
       </c>
-      <c r="AB16" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC16" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD16" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="17" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A17" s="2">
         <v>20060001</v>
       </c>
@@ -3503,16 +3268,16 @@
         <v>1</v>
       </c>
       <c r="E17" s="11" t="s">
+        <v>152</v>
+      </c>
+      <c r="F17" s="2" t="s">
         <v>163</v>
       </c>
-      <c r="F17" s="2" t="s">
-        <v>174</v>
-      </c>
       <c r="G17" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H17" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I17" s="2">
         <v>2000</v>
@@ -3571,17 +3336,8 @@
       <c r="AA17" s="2">
         <v>0</v>
       </c>
-      <c r="AB17" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC17" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD17" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="18" spans="1:30" ht="13.5" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:27" ht="13.5" x14ac:dyDescent="0.2">
       <c r="A18" s="2">
         <v>20070001</v>
       </c>
@@ -3595,16 +3351,16 @@
         <v>1</v>
       </c>
       <c r="E18" s="11" t="s">
-        <v>164</v>
+        <v>153</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H18" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I18" s="2">
         <v>2000</v>
@@ -3663,17 +3419,8 @@
       <c r="AA18" s="2">
         <v>0</v>
       </c>
-      <c r="AB18" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC18" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD18" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A19" s="2">
         <v>20080001</v>
       </c>
@@ -3687,16 +3434,16 @@
         <v>1</v>
       </c>
       <c r="E19" s="11" t="s">
-        <v>165</v>
+        <v>154</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H19" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I19" s="2">
         <v>2000</v>
@@ -3755,17 +3502,8 @@
       <c r="AA19" s="2">
         <v>0</v>
       </c>
-      <c r="AB19" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC19" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD19" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A20" s="2">
         <v>20090001</v>
       </c>
@@ -3779,16 +3517,16 @@
         <v>1</v>
       </c>
       <c r="E20" s="11" t="s">
-        <v>166</v>
+        <v>155</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H20" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I20" s="2">
         <v>2000</v>
@@ -3847,17 +3585,8 @@
       <c r="AA20" s="2">
         <v>0</v>
       </c>
-      <c r="AB20" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC20" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD20" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A21" s="2">
         <v>20100001</v>
       </c>
@@ -3871,16 +3600,16 @@
         <v>1</v>
       </c>
       <c r="E21" s="11" t="s">
-        <v>167</v>
+        <v>156</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H21" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I21" s="2">
         <v>2000</v>
@@ -3939,17 +3668,8 @@
       <c r="AA21" s="2">
         <v>0</v>
       </c>
-      <c r="AB21" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC21" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD21" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A22" s="2">
         <v>20110001</v>
       </c>
@@ -3963,16 +3683,16 @@
         <v>1</v>
       </c>
       <c r="E22" s="11" t="s">
-        <v>168</v>
+        <v>157</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H22" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I22" s="2">
         <v>2000</v>
@@ -4031,17 +3751,8 @@
       <c r="AA22" s="2">
         <v>0</v>
       </c>
-      <c r="AB22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC22" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD22" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A23" s="2">
         <v>20120001</v>
       </c>
@@ -4055,16 +3766,16 @@
         <v>1</v>
       </c>
       <c r="E23" s="11" t="s">
-        <v>169</v>
+        <v>158</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H23" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I23" s="2">
         <v>2000</v>
@@ -4123,17 +3834,8 @@
       <c r="AA23" s="2">
         <v>0</v>
       </c>
-      <c r="AB23" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC23" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD23" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A24" s="2">
         <v>20130001</v>
       </c>
@@ -4147,16 +3849,16 @@
         <v>1</v>
       </c>
       <c r="E24" s="11" t="s">
-        <v>170</v>
+        <v>159</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G24" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H24" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I24" s="2">
         <v>2000</v>
@@ -4215,17 +3917,8 @@
       <c r="AA24" s="2">
         <v>0</v>
       </c>
-      <c r="AB24" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC24" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD24" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A25" s="2">
         <v>20140001</v>
       </c>
@@ -4239,16 +3932,16 @@
         <v>1</v>
       </c>
       <c r="E25" s="11" t="s">
-        <v>171</v>
+        <v>160</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G25" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H25" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I25" s="2">
         <v>2000</v>
@@ -4307,17 +4000,8 @@
       <c r="AA25" s="2">
         <v>0</v>
       </c>
-      <c r="AB25" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC25" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD25" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A26" s="2">
         <v>20150001</v>
       </c>
@@ -4331,16 +4015,16 @@
         <v>1</v>
       </c>
       <c r="E26" s="11" t="s">
-        <v>172</v>
+        <v>161</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G26" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H26" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I26" s="2">
         <v>2000</v>
@@ -4399,17 +4083,8 @@
       <c r="AA26" s="2">
         <v>0</v>
       </c>
-      <c r="AB26" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC26" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD26" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A27" s="2">
         <v>20160001</v>
       </c>
@@ -4423,16 +4098,16 @@
         <v>1</v>
       </c>
       <c r="E27" s="11" t="s">
-        <v>173</v>
+        <v>162</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>174</v>
+        <v>163</v>
       </c>
       <c r="G27" s="2" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H27" s="2" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="I27" s="2">
         <v>2000</v>
@@ -4491,17 +4166,8 @@
       <c r="AA27" s="2">
         <v>0</v>
       </c>
-      <c r="AB27" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC27" s="2" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD27" s="2" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="28" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A28" s="23">
         <v>25010001</v>
       </c>
@@ -4515,16 +4181,16 @@
         <v>1</v>
       </c>
       <c r="E28" s="18" t="s">
-        <v>296</v>
+        <v>285</v>
       </c>
       <c r="F28" s="23" t="s">
-        <v>297</v>
+        <v>286</v>
       </c>
       <c r="G28" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>298</v>
+        <v>287</v>
       </c>
       <c r="I28" s="23">
         <v>0</v>
@@ -4560,7 +4226,7 @@
         <v>1</v>
       </c>
       <c r="T28" s="23">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U28" s="23">
         <v>0</v>
@@ -4583,17 +4249,8 @@
       <c r="AA28" s="23">
         <v>0</v>
       </c>
-      <c r="AB28" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC28" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD28" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A29" s="3">
         <v>30001</v>
       </c>
@@ -4607,16 +4264,16 @@
         <v>1</v>
       </c>
       <c r="E29" s="4" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="G29" s="3" t="s">
-        <v>176</v>
+        <v>165</v>
       </c>
       <c r="H29" s="3" t="s">
-        <v>177</v>
+        <v>166</v>
       </c>
       <c r="I29" s="3">
         <v>0</v>
@@ -4675,17 +4332,8 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A30" s="3">
         <v>4000001</v>
       </c>
@@ -4699,16 +4347,16 @@
         <v>1</v>
       </c>
       <c r="E30" s="4" t="s">
-        <v>80</v>
+        <v>69</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>117</v>
+        <v>106</v>
       </c>
       <c r="G30" s="3" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H30" s="3" t="s">
-        <v>87</v>
+        <v>76</v>
       </c>
       <c r="I30" s="3">
         <v>0</v>
@@ -4744,7 +4392,7 @@
         <v>0</v>
       </c>
       <c r="T30" s="3">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U30" s="3">
         <v>0</v>
@@ -4767,17 +4415,8 @@
       <c r="AA30" s="3">
         <v>0</v>
       </c>
-      <c r="AB30" s="3" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC30" s="3" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD30" s="3" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="31" spans="1:30" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:27" ht="10.5" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A31" s="21">
         <v>5000001</v>
       </c>
@@ -4791,16 +4430,16 @@
         <v>1</v>
       </c>
       <c r="E31" s="22" t="s">
-        <v>118</v>
+        <v>107</v>
       </c>
       <c r="F31" s="21" t="s">
-        <v>84</v>
+        <v>73</v>
       </c>
       <c r="G31" s="21" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H31" s="21" t="s">
-        <v>125</v>
+        <v>114</v>
       </c>
       <c r="I31" s="21">
         <v>8000</v>
@@ -4859,17 +4498,8 @@
       <c r="AA31" s="21">
         <v>55010001</v>
       </c>
-      <c r="AB31" s="21" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC31" s="21" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD31" s="21" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="32" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="32" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A32" s="17">
         <v>6000001</v>
       </c>
@@ -4883,13 +4513,13 @@
         <v>1</v>
       </c>
       <c r="E32" s="18" t="s">
-        <v>136</v>
+        <v>125</v>
       </c>
       <c r="F32" s="17" t="s">
-        <v>129</v>
+        <v>118</v>
       </c>
       <c r="G32" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H32" s="17"/>
       <c r="I32" s="17">
@@ -4926,7 +4556,7 @@
         <v>9</v>
       </c>
       <c r="T32" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U32" s="17">
         <v>2</v>
@@ -4949,17 +4579,8 @@
       <c r="AA32" s="17">
         <v>56010001</v>
       </c>
-      <c r="AB32" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC32" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD32" s="17" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="33" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="33" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A33" s="17">
         <v>6010001</v>
       </c>
@@ -4973,13 +4594,13 @@
         <v>1</v>
       </c>
       <c r="E33" s="18" t="s">
-        <v>141</v>
+        <v>130</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>130</v>
+        <v>119</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H33" s="17"/>
       <c r="I33" s="17">
@@ -5016,7 +4637,7 @@
         <v>9</v>
       </c>
       <c r="T33" s="17">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U33" s="17">
         <v>2</v>
@@ -5039,17 +4660,8 @@
       <c r="AA33" s="17">
         <v>56010001</v>
       </c>
-      <c r="AB33" s="17" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC33" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD33" s="17" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="34" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="34" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A34" s="19">
         <v>7000001</v>
       </c>
@@ -5063,13 +4675,13 @@
         <v>1</v>
       </c>
       <c r="E34" s="18" t="s">
-        <v>143</v>
+        <v>132</v>
       </c>
       <c r="F34" s="19" t="s">
-        <v>131</v>
+        <v>120</v>
       </c>
       <c r="G34" s="19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H34" s="19"/>
       <c r="I34" s="19">
@@ -5106,7 +4718,7 @@
         <v>1</v>
       </c>
       <c r="T34" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U34" s="19">
         <v>4</v>
@@ -5129,17 +4741,8 @@
       <c r="AA34" s="19">
         <v>57010001</v>
       </c>
-      <c r="AB34" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC34" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD34" s="19" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="35" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="35" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A35" s="19">
         <v>7010001</v>
       </c>
@@ -5153,13 +4756,13 @@
         <v>1</v>
       </c>
       <c r="E35" s="18" t="s">
-        <v>149</v>
+        <v>138</v>
       </c>
       <c r="F35" s="19" t="s">
-        <v>132</v>
+        <v>121</v>
       </c>
       <c r="G35" s="19" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H35" s="19"/>
       <c r="I35" s="19">
@@ -5196,7 +4799,7 @@
         <v>9</v>
       </c>
       <c r="T35" s="19">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U35" s="19">
         <v>4</v>
@@ -5219,17 +4822,8 @@
       <c r="AA35" s="19">
         <v>57010001</v>
       </c>
-      <c r="AB35" s="19" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC35" s="19" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD35" s="19" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="36" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="36" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A36" s="20">
         <v>8000001</v>
       </c>
@@ -5243,13 +4837,13 @@
         <v>1</v>
       </c>
       <c r="E36" s="18" t="s">
-        <v>151</v>
+        <v>140</v>
       </c>
       <c r="F36" s="20" t="s">
-        <v>133</v>
+        <v>122</v>
       </c>
       <c r="G36" s="20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H36" s="20"/>
       <c r="I36" s="20">
@@ -5286,7 +4880,7 @@
         <v>9</v>
       </c>
       <c r="T36" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U36" s="20">
         <v>3</v>
@@ -5309,17 +4903,8 @@
       <c r="AA36" s="20">
         <v>58010001</v>
       </c>
-      <c r="AB36" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC36" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD36" s="20" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="37" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="37" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A37" s="20">
         <v>8010001</v>
       </c>
@@ -5333,13 +4918,13 @@
         <v>1</v>
       </c>
       <c r="E37" s="18" t="s">
-        <v>154</v>
+        <v>143</v>
       </c>
       <c r="F37" s="20" t="s">
-        <v>134</v>
+        <v>123</v>
       </c>
       <c r="G37" s="20" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H37" s="20"/>
       <c r="I37" s="20">
@@ -5376,7 +4961,7 @@
         <v>9</v>
       </c>
       <c r="T37" s="20">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U37" s="20">
         <v>3</v>
@@ -5399,17 +4984,8 @@
       <c r="AA37" s="20">
         <v>58050001</v>
       </c>
-      <c r="AB37" s="20" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC37" s="20" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD37" s="20" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="38" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="38" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A38" s="28">
         <v>9000001</v>
       </c>
@@ -5423,13 +4999,13 @@
         <v>1</v>
       </c>
       <c r="E38" s="18" t="s">
-        <v>218</v>
+        <v>207</v>
       </c>
       <c r="F38" s="28" t="s">
-        <v>116</v>
+        <v>105</v>
       </c>
       <c r="G38" s="28" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H38" s="28"/>
       <c r="I38" s="28">
@@ -5466,10 +5042,10 @@
         <v>1</v>
       </c>
       <c r="T38" s="28">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U38" s="32" t="s">
-        <v>302</v>
+        <v>291</v>
       </c>
       <c r="V38" s="28">
         <v>150</v>
@@ -5489,17 +5065,8 @@
       <c r="AA38" s="28">
         <v>0</v>
       </c>
-      <c r="AB38" s="28" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC38" s="28">
-        <v>1</v>
-      </c>
-      <c r="AD38" s="28">
-        <v>1</v>
-      </c>
     </row>
-    <row r="39" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="39" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A39" s="30">
         <v>10010001</v>
       </c>
@@ -5513,13 +5080,13 @@
         <v>1</v>
       </c>
       <c r="E39" s="18" t="s">
-        <v>219</v>
+        <v>208</v>
       </c>
       <c r="F39" s="30" t="s">
-        <v>220</v>
+        <v>209</v>
       </c>
       <c r="G39" s="30" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H39" s="30"/>
       <c r="I39" s="30">
@@ -5556,7 +5123,7 @@
         <v>9</v>
       </c>
       <c r="T39" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U39" s="30">
         <v>0</v>
@@ -5579,17 +5146,8 @@
       <c r="AA39" s="30">
         <v>0</v>
       </c>
-      <c r="AB39" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC39" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD39" s="30" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="40" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="40" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A40" s="30">
         <v>10020001</v>
       </c>
@@ -5603,13 +5161,13 @@
         <v>1</v>
       </c>
       <c r="E40" s="18" t="s">
-        <v>221</v>
+        <v>210</v>
       </c>
       <c r="F40" s="30" t="s">
-        <v>222</v>
+        <v>211</v>
       </c>
       <c r="G40" s="30" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H40" s="30"/>
       <c r="I40" s="30">
@@ -5646,7 +5204,7 @@
         <v>9</v>
       </c>
       <c r="T40" s="30">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U40" s="30">
         <v>0</v>
@@ -5669,17 +5227,8 @@
       <c r="AA40" s="30">
         <v>0</v>
       </c>
-      <c r="AB40" s="30" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC40" s="30" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD40" s="30" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="41" spans="1:30" s="29" customFormat="1" x14ac:dyDescent="0.15">
+    <row r="41" spans="1:27" s="29" customFormat="1" x14ac:dyDescent="0.15">
       <c r="A41" s="31">
         <v>11010001</v>
       </c>
@@ -5693,13 +5242,13 @@
         <v>1</v>
       </c>
       <c r="E41" s="18" t="s">
-        <v>223</v>
+        <v>212</v>
       </c>
       <c r="F41" s="31" t="s">
-        <v>224</v>
+        <v>213</v>
       </c>
       <c r="G41" s="31" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H41" s="31"/>
       <c r="I41" s="31">
@@ -5736,7 +5285,7 @@
         <v>9</v>
       </c>
       <c r="T41" s="31">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U41" s="31">
         <v>0</v>
@@ -5759,17 +5308,8 @@
       <c r="AA41" s="31">
         <v>0</v>
       </c>
-      <c r="AB41" s="31" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC41" s="31" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD41" s="31" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="42" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A42" s="23">
         <v>54010001</v>
       </c>
@@ -5783,16 +5323,16 @@
         <v>1</v>
       </c>
       <c r="E42" s="18" t="s">
-        <v>101</v>
+        <v>90</v>
       </c>
       <c r="F42" s="23" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="G42" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H42" s="23" t="s">
-        <v>89</v>
+        <v>78</v>
       </c>
       <c r="I42" s="23">
         <v>0</v>
@@ -5851,17 +5391,8 @@
       <c r="AA42" s="23">
         <v>0</v>
       </c>
-      <c r="AB42" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC42" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD42" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="43" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A43" s="23">
         <v>54030001</v>
       </c>
@@ -5875,16 +5406,16 @@
         <v>1</v>
       </c>
       <c r="E43" s="18" t="s">
-        <v>102</v>
+        <v>91</v>
       </c>
       <c r="F43" s="23" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="G43" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H43" s="23" t="s">
-        <v>90</v>
+        <v>79</v>
       </c>
       <c r="I43" s="23">
         <v>0</v>
@@ -5943,17 +5474,8 @@
       <c r="AA43" s="23">
         <v>0</v>
       </c>
-      <c r="AB43" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC43" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD43" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="44" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A44" s="23">
         <v>54050001</v>
       </c>
@@ -5967,16 +5489,16 @@
         <v>1</v>
       </c>
       <c r="E44" s="18" t="s">
-        <v>103</v>
+        <v>92</v>
       </c>
       <c r="F44" s="23" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="G44" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H44" s="23" t="s">
-        <v>91</v>
+        <v>80</v>
       </c>
       <c r="I44" s="23">
         <v>0</v>
@@ -6035,17 +5557,8 @@
       <c r="AA44" s="23">
         <v>0</v>
       </c>
-      <c r="AB44" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC44" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD44" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="45" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A45" s="23">
         <v>54070001</v>
       </c>
@@ -6059,16 +5572,16 @@
         <v>1</v>
       </c>
       <c r="E45" s="18" t="s">
-        <v>104</v>
+        <v>93</v>
       </c>
       <c r="F45" s="23" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="G45" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H45" s="23" t="s">
-        <v>92</v>
+        <v>81</v>
       </c>
       <c r="I45" s="23">
         <v>0</v>
@@ -6127,17 +5640,8 @@
       <c r="AA45" s="23">
         <v>0</v>
       </c>
-      <c r="AB45" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC45" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD45" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="46" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A46" s="23">
         <v>54090001</v>
       </c>
@@ -6151,16 +5655,16 @@
         <v>1</v>
       </c>
       <c r="E46" s="18" t="s">
-        <v>105</v>
+        <v>94</v>
       </c>
       <c r="F46" s="23" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="G46" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H46" s="23" t="s">
-        <v>93</v>
+        <v>82</v>
       </c>
       <c r="I46" s="23">
         <v>0</v>
@@ -6219,17 +5723,8 @@
       <c r="AA46" s="23">
         <v>0</v>
       </c>
-      <c r="AB46" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC46" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD46" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="47" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A47" s="23">
         <v>54110001</v>
       </c>
@@ -6243,16 +5738,16 @@
         <v>1</v>
       </c>
       <c r="E47" s="18" t="s">
-        <v>106</v>
+        <v>95</v>
       </c>
       <c r="F47" s="23" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="G47" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H47" s="23" t="s">
-        <v>94</v>
+        <v>83</v>
       </c>
       <c r="I47" s="23">
         <v>0</v>
@@ -6311,17 +5806,8 @@
       <c r="AA47" s="23">
         <v>0</v>
       </c>
-      <c r="AB47" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC47" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD47" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="48" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A48" s="23">
         <v>54130001</v>
       </c>
@@ -6335,16 +5821,16 @@
         <v>1</v>
       </c>
       <c r="E48" s="18" t="s">
-        <v>107</v>
+        <v>96</v>
       </c>
       <c r="F48" s="23" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G48" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H48" s="23" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I48" s="23">
         <v>0</v>
@@ -6403,17 +5889,8 @@
       <c r="AA48" s="23">
         <v>0</v>
       </c>
-      <c r="AB48" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC48" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD48" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="49" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A49" s="23">
         <v>54150001</v>
       </c>
@@ -6427,16 +5904,16 @@
         <v>1</v>
       </c>
       <c r="E49" s="18" t="s">
-        <v>108</v>
+        <v>97</v>
       </c>
       <c r="F49" s="23" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="G49" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H49" s="23" t="s">
-        <v>96</v>
+        <v>85</v>
       </c>
       <c r="I49" s="23">
         <v>0</v>
@@ -6495,17 +5972,8 @@
       <c r="AA49" s="23">
         <v>0</v>
       </c>
-      <c r="AB49" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC49" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD49" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="50" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A50" s="23">
         <v>54170001</v>
       </c>
@@ -6519,16 +5987,16 @@
         <v>1</v>
       </c>
       <c r="E50" s="18" t="s">
-        <v>109</v>
+        <v>98</v>
       </c>
       <c r="F50" s="23" t="s">
-        <v>97</v>
+        <v>86</v>
       </c>
       <c r="G50" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H50" s="23" t="s">
-        <v>112</v>
+        <v>101</v>
       </c>
       <c r="I50" s="23">
         <v>0</v>
@@ -6587,17 +6055,8 @@
       <c r="AA50" s="23">
         <v>54090001</v>
       </c>
-      <c r="AB50" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC50" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD50" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="51" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A51" s="23">
         <v>54190001</v>
       </c>
@@ -6611,16 +6070,16 @@
         <v>1</v>
       </c>
       <c r="E51" s="18" t="s">
-        <v>110</v>
+        <v>99</v>
       </c>
       <c r="F51" s="23" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="G51" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H51" s="23" t="s">
-        <v>98</v>
+        <v>87</v>
       </c>
       <c r="I51" s="23">
         <v>0</v>
@@ -6679,17 +6138,8 @@
       <c r="AA51" s="23">
         <v>0</v>
       </c>
-      <c r="AB51" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC51" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD51" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="52" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A52" s="23">
         <v>54210001</v>
       </c>
@@ -6703,16 +6153,16 @@
         <v>1</v>
       </c>
       <c r="E52" s="18" t="s">
-        <v>111</v>
+        <v>100</v>
       </c>
       <c r="F52" s="23" t="s">
-        <v>99</v>
+        <v>88</v>
       </c>
       <c r="G52" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H52" s="23" t="s">
-        <v>113</v>
+        <v>102</v>
       </c>
       <c r="I52" s="23">
         <v>0</v>
@@ -6771,17 +6221,8 @@
       <c r="AA52" s="23">
         <v>54110001</v>
       </c>
-      <c r="AB52" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC52" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD52" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="53" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A53" s="23">
         <v>54230001</v>
       </c>
@@ -6795,16 +6236,16 @@
         <v>1</v>
       </c>
       <c r="E53" s="18" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F53" s="23" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="G53" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H53" s="23" t="s">
-        <v>114</v>
+        <v>103</v>
       </c>
       <c r="I53" s="23">
         <v>0</v>
@@ -6863,17 +6304,8 @@
       <c r="AA53" s="23">
         <v>0</v>
       </c>
-      <c r="AB53" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC53" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD53" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="54" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A54" s="23">
         <v>54250001</v>
       </c>
@@ -6887,16 +6319,16 @@
         <v>1</v>
       </c>
       <c r="E54" s="18" t="s">
-        <v>157</v>
+        <v>146</v>
       </c>
       <c r="F54" s="23" t="s">
-        <v>128</v>
+        <v>117</v>
       </c>
       <c r="G54" s="23" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H54" s="23" t="s">
-        <v>269</v>
+        <v>258</v>
       </c>
       <c r="I54" s="23">
         <v>0</v>
@@ -6955,17 +6387,8 @@
       <c r="AA54" s="23">
         <v>0</v>
       </c>
-      <c r="AB54" s="23" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC54" s="23" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD54" s="23" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A55" s="13">
         <v>55010001</v>
       </c>
@@ -6979,16 +6402,16 @@
         <v>1</v>
       </c>
       <c r="E55" s="4" t="s">
-        <v>81</v>
+        <v>70</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>279</v>
+        <v>268</v>
       </c>
       <c r="G55" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H55" s="13" t="s">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="I55" s="13">
         <v>0</v>
@@ -7047,17 +6470,8 @@
       <c r="AA55" s="13">
         <v>55010001</v>
       </c>
-      <c r="AB55" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC55" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD55" s="13" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A56" s="13">
         <v>55020001</v>
       </c>
@@ -7071,16 +6485,16 @@
         <v>1</v>
       </c>
       <c r="E56" s="4" t="s">
-        <v>121</v>
+        <v>110</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>280</v>
+        <v>269</v>
       </c>
       <c r="G56" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H56" s="13" t="s">
-        <v>122</v>
+        <v>111</v>
       </c>
       <c r="I56" s="13">
         <v>0</v>
@@ -7139,17 +6553,8 @@
       <c r="AA56" s="13">
         <v>55010001</v>
       </c>
-      <c r="AB56" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC56" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD56" s="13" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A57" s="13">
         <v>55030001</v>
       </c>
@@ -7163,16 +6568,16 @@
         <v>1</v>
       </c>
       <c r="E57" s="4" t="s">
-        <v>123</v>
+        <v>112</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>281</v>
+        <v>270</v>
       </c>
       <c r="G57" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H57" s="13" t="s">
-        <v>124</v>
+        <v>113</v>
       </c>
       <c r="I57" s="13">
         <v>0</v>
@@ -7231,17 +6636,8 @@
       <c r="AA57" s="13">
         <v>0</v>
       </c>
-      <c r="AB57" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC57" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD57" s="13" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A58" s="13">
         <v>55040001</v>
       </c>
@@ -7255,16 +6651,16 @@
         <v>1</v>
       </c>
       <c r="E58" s="4" t="s">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>282</v>
+        <v>271</v>
       </c>
       <c r="G58" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H58" s="13" t="s">
-        <v>83</v>
+        <v>72</v>
       </c>
       <c r="I58" s="13">
         <v>0</v>
@@ -7323,17 +6719,8 @@
       <c r="AA58" s="13">
         <v>0</v>
       </c>
-      <c r="AB58" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC58" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD58" s="13" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A59" s="13">
         <v>55050001</v>
       </c>
@@ -7347,16 +6734,16 @@
         <v>1</v>
       </c>
       <c r="E59" s="4" t="s">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>283</v>
+        <v>272</v>
       </c>
       <c r="G59" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H59" s="13" t="s">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="I59" s="13">
         <v>0</v>
@@ -7415,17 +6802,8 @@
       <c r="AA59" s="13">
         <v>55050001</v>
       </c>
-      <c r="AB59" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC59" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD59" s="13" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A60" s="13">
         <v>55060001</v>
       </c>
@@ -7439,16 +6817,16 @@
         <v>1</v>
       </c>
       <c r="E60" s="4" t="s">
-        <v>126</v>
+        <v>115</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>284</v>
+        <v>273</v>
       </c>
       <c r="G60" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H60" s="13" t="s">
-        <v>119</v>
+        <v>108</v>
       </c>
       <c r="I60" s="13">
         <v>0</v>
@@ -7507,17 +6885,8 @@
       <c r="AA60" s="13">
         <v>0</v>
       </c>
-      <c r="AB60" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC60" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD60" s="13" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:27" x14ac:dyDescent="0.2">
       <c r="A61" s="13">
         <v>55070001</v>
       </c>
@@ -7531,16 +6900,16 @@
         <v>1</v>
       </c>
       <c r="E61" s="4" t="s">
-        <v>127</v>
+        <v>116</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>285</v>
+        <v>274</v>
       </c>
       <c r="G61" s="13" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H61" s="13" t="s">
-        <v>120</v>
+        <v>109</v>
       </c>
       <c r="I61" s="13">
         <v>0</v>
@@ -7599,17 +6968,8 @@
       <c r="AA61" s="13">
         <v>0</v>
       </c>
-      <c r="AB61" s="13" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC61" s="13" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD61" s="13" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="62" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A62" s="14">
         <v>56010001</v>
       </c>
@@ -7623,16 +6983,16 @@
         <v>1</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>135</v>
+        <v>124</v>
       </c>
       <c r="F62" s="14" t="s">
-        <v>225</v>
+        <v>214</v>
       </c>
       <c r="G62" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H62" s="14" t="s">
-        <v>251</v>
+        <v>240</v>
       </c>
       <c r="I62" s="14">
         <v>0</v>
@@ -7691,17 +7051,8 @@
       <c r="AA62" s="14">
         <v>56010001</v>
       </c>
-      <c r="AB62" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC62" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD62" s="14" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="63" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A63" s="14">
         <v>56040001</v>
       </c>
@@ -7715,16 +7066,16 @@
         <v>1</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>137</v>
+        <v>126</v>
       </c>
       <c r="F63" s="14" t="s">
-        <v>226</v>
+        <v>215</v>
       </c>
       <c r="G63" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H63" s="14" t="s">
-        <v>252</v>
+        <v>241</v>
       </c>
       <c r="I63" s="14">
         <v>0</v>
@@ -7783,17 +7134,8 @@
       <c r="AA63" s="14">
         <v>0</v>
       </c>
-      <c r="AB63" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC63" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD63" s="14" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="64" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A64" s="14">
         <v>56060001</v>
       </c>
@@ -7807,16 +7149,16 @@
         <v>1</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>138</v>
+        <v>127</v>
       </c>
       <c r="F64" s="14" t="s">
-        <v>227</v>
+        <v>216</v>
       </c>
       <c r="G64" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H64" s="14" t="s">
-        <v>253</v>
+        <v>242</v>
       </c>
       <c r="I64" s="14">
         <v>0</v>
@@ -7875,17 +7217,8 @@
       <c r="AA64" s="14">
         <v>56030001</v>
       </c>
-      <c r="AB64" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC64" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD64" s="14" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="65" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A65" s="14">
         <v>56080001</v>
       </c>
@@ -7899,16 +7232,16 @@
         <v>1</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>139</v>
+        <v>128</v>
       </c>
       <c r="F65" s="14" t="s">
-        <v>228</v>
+        <v>217</v>
       </c>
       <c r="G65" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H65" s="14" t="s">
-        <v>254</v>
+        <v>243</v>
       </c>
       <c r="I65" s="14">
         <v>0</v>
@@ -7967,17 +7300,8 @@
       <c r="AA65" s="14">
         <v>0</v>
       </c>
-      <c r="AB65" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC65" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD65" s="14" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="66" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A66" s="14">
         <v>56100001</v>
       </c>
@@ -7991,16 +7315,16 @@
         <v>1</v>
       </c>
       <c r="E66" s="12" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>291</v>
+        <v>280</v>
       </c>
       <c r="G66" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>289</v>
+        <v>278</v>
       </c>
       <c r="I66" s="14">
         <v>0</v>
@@ -8059,17 +7383,8 @@
       <c r="AA66" s="14">
         <v>56050001</v>
       </c>
-      <c r="AB66" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC66" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD66" s="14" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="67" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A67" s="14">
         <v>56130001</v>
       </c>
@@ -8083,16 +7398,16 @@
         <v>1</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>140</v>
+        <v>129</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="G67" s="14" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H67" s="14" t="s">
-        <v>290</v>
+        <v>279</v>
       </c>
       <c r="I67" s="14">
         <v>0</v>
@@ -8151,17 +7466,8 @@
       <c r="AA67" s="14">
         <v>56060001</v>
       </c>
-      <c r="AB67" s="14" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC67" s="14" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD67" s="14" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="68" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A68" s="15">
         <v>57010001</v>
       </c>
@@ -8175,16 +7481,16 @@
         <v>1</v>
       </c>
       <c r="E68" s="12" t="s">
-        <v>142</v>
+        <v>131</v>
       </c>
       <c r="F68" s="15" t="s">
-        <v>229</v>
+        <v>218</v>
       </c>
       <c r="G68" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H68" s="15" t="s">
-        <v>255</v>
+        <v>244</v>
       </c>
       <c r="I68" s="15">
         <v>0</v>
@@ -8243,17 +7549,8 @@
       <c r="AA68" s="15">
         <v>57010001</v>
       </c>
-      <c r="AB68" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC68" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD68" s="15" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="69" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A69" s="15">
         <v>57040001</v>
       </c>
@@ -8267,16 +7564,16 @@
         <v>1</v>
       </c>
       <c r="E69" s="12" t="s">
-        <v>144</v>
+        <v>133</v>
       </c>
       <c r="F69" s="15" t="s">
-        <v>230</v>
+        <v>219</v>
       </c>
       <c r="G69" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H69" s="15" t="s">
-        <v>256</v>
+        <v>245</v>
       </c>
       <c r="I69" s="15">
         <v>0</v>
@@ -8335,17 +7632,8 @@
       <c r="AA69" s="15">
         <v>0</v>
       </c>
-      <c r="AB69" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC69" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD69" s="15" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="70" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A70" s="15">
         <v>57060001</v>
       </c>
@@ -8359,16 +7647,16 @@
         <v>1</v>
       </c>
       <c r="E70" s="12" t="s">
-        <v>145</v>
+        <v>134</v>
       </c>
       <c r="F70" s="15" t="s">
-        <v>231</v>
+        <v>220</v>
       </c>
       <c r="G70" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H70" s="15" t="s">
-        <v>257</v>
+        <v>246</v>
       </c>
       <c r="I70" s="15">
         <v>0</v>
@@ -8427,17 +7715,8 @@
       <c r="AA70" s="15">
         <v>0</v>
       </c>
-      <c r="AB70" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC70" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD70" s="15" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="71" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A71" s="15">
         <v>57080001</v>
       </c>
@@ -8451,16 +7730,16 @@
         <v>1</v>
       </c>
       <c r="E71" s="12" t="s">
-        <v>146</v>
+        <v>135</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>293</v>
+        <v>282</v>
       </c>
       <c r="G71" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>292</v>
+        <v>281</v>
       </c>
       <c r="I71" s="15">
         <v>0</v>
@@ -8519,17 +7798,8 @@
       <c r="AA71" s="15">
         <v>57040001</v>
       </c>
-      <c r="AB71" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC71" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD71" s="15" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="72" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A72" s="15">
         <v>57100001</v>
       </c>
@@ -8543,16 +7813,16 @@
         <v>1</v>
       </c>
       <c r="E72" s="12" t="s">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>287</v>
+        <v>276</v>
       </c>
       <c r="G72" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H72" s="15" t="s">
-        <v>258</v>
+        <v>247</v>
       </c>
       <c r="I72" s="15">
         <v>0</v>
@@ -8611,17 +7881,8 @@
       <c r="AA72" s="15">
         <v>0</v>
       </c>
-      <c r="AB72" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC72" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD72" s="15" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="73" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A73" s="15">
         <v>57120001</v>
       </c>
@@ -8635,16 +7896,16 @@
         <v>1</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>148</v>
+        <v>137</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>288</v>
+        <v>277</v>
       </c>
       <c r="G73" s="15" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H73" s="15" t="s">
-        <v>259</v>
+        <v>248</v>
       </c>
       <c r="I73" s="15">
         <v>0</v>
@@ -8703,17 +7964,8 @@
       <c r="AA73" s="15">
         <v>57060001</v>
       </c>
-      <c r="AB73" s="15" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC73" s="15" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD73" s="15" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="74" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A74" s="16">
         <v>58010001</v>
       </c>
@@ -8727,16 +7979,16 @@
         <v>1</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>150</v>
+        <v>139</v>
       </c>
       <c r="F74" s="16" t="s">
-        <v>232</v>
+        <v>221</v>
       </c>
       <c r="G74" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H74" s="16" t="s">
-        <v>260</v>
+        <v>249</v>
       </c>
       <c r="I74" s="16">
         <v>0</v>
@@ -8795,17 +8047,8 @@
       <c r="AA74" s="16">
         <v>58010001</v>
       </c>
-      <c r="AB74" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC74" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD74" s="16" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="75" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A75" s="16">
         <v>58040001</v>
       </c>
@@ -8819,16 +8062,16 @@
         <v>1</v>
       </c>
       <c r="E75" s="12" t="s">
-        <v>156</v>
+        <v>145</v>
       </c>
       <c r="F75" s="16" t="s">
-        <v>233</v>
+        <v>222</v>
       </c>
       <c r="G75" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H75" s="16" t="s">
-        <v>261</v>
+        <v>250</v>
       </c>
       <c r="I75" s="16">
         <v>0</v>
@@ -8887,17 +8130,8 @@
       <c r="AA75" s="16">
         <v>0</v>
       </c>
-      <c r="AB75" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC75" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD75" s="16" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="76" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A76" s="16">
         <v>58060001</v>
       </c>
@@ -8911,16 +8145,16 @@
         <v>1</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>152</v>
+        <v>141</v>
       </c>
       <c r="F76" s="16" t="s">
-        <v>234</v>
+        <v>223</v>
       </c>
       <c r="G76" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H76" s="16" t="s">
-        <v>262</v>
+        <v>251</v>
       </c>
       <c r="I76" s="16">
         <v>0</v>
@@ -8979,17 +8213,8 @@
       <c r="AA76" s="16">
         <v>0</v>
       </c>
-      <c r="AB76" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC76" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD76" s="16" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="77" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A77" s="16">
         <v>58080001</v>
       </c>
@@ -9003,16 +8228,16 @@
         <v>1</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>153</v>
+        <v>142</v>
       </c>
       <c r="F77" s="16" t="s">
-        <v>235</v>
+        <v>224</v>
       </c>
       <c r="G77" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H77" s="16" t="s">
-        <v>263</v>
+        <v>252</v>
       </c>
       <c r="I77" s="16">
         <v>0</v>
@@ -9071,17 +8296,8 @@
       <c r="AA77" s="16">
         <v>58040001</v>
       </c>
-      <c r="AB77" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC77" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD77" s="16" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="78" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A78" s="16">
         <v>58110001</v>
       </c>
@@ -9095,16 +8311,16 @@
         <v>1</v>
       </c>
       <c r="E78" s="12" t="s">
-        <v>155</v>
+        <v>144</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>286</v>
+        <v>275</v>
       </c>
       <c r="G78" s="16" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H78" s="16" t="s">
-        <v>264</v>
+        <v>253</v>
       </c>
       <c r="I78" s="16">
         <v>0</v>
@@ -9163,17 +8379,8 @@
       <c r="AA78" s="16">
         <v>58050001</v>
       </c>
-      <c r="AB78" s="16" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC78" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD78" s="16" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="79" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A79" s="24">
         <v>59010001</v>
       </c>
@@ -9187,16 +8394,16 @@
         <v>1</v>
       </c>
       <c r="E79" s="12" t="s">
-        <v>178</v>
+        <v>167</v>
       </c>
       <c r="F79" s="24" t="s">
-        <v>236</v>
+        <v>225</v>
       </c>
       <c r="G79" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H79" s="24" t="s">
-        <v>179</v>
+        <v>168</v>
       </c>
       <c r="I79" s="24">
         <v>0</v>
@@ -9255,17 +8462,8 @@
       <c r="AA79" s="24">
         <v>0</v>
       </c>
-      <c r="AB79" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC79" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD79" s="24" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="80" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A80" s="24">
         <v>59030001</v>
       </c>
@@ -9279,16 +8477,16 @@
         <v>1</v>
       </c>
       <c r="E80" s="12" t="s">
-        <v>180</v>
+        <v>169</v>
       </c>
       <c r="F80" s="24" t="s">
-        <v>237</v>
+        <v>226</v>
       </c>
       <c r="G80" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H80" s="24" t="s">
-        <v>115</v>
+        <v>104</v>
       </c>
       <c r="I80" s="24">
         <v>0</v>
@@ -9347,17 +8545,8 @@
       <c r="AA80" s="24">
         <v>0</v>
       </c>
-      <c r="AB80" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC80" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD80" s="24" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="81" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A81" s="24">
         <v>59050001</v>
       </c>
@@ -9371,16 +8560,16 @@
         <v>1</v>
       </c>
       <c r="E81" s="12" t="s">
-        <v>181</v>
+        <v>170</v>
       </c>
       <c r="F81" s="24" t="s">
-        <v>238</v>
+        <v>227</v>
       </c>
       <c r="G81" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H81" s="24" t="s">
-        <v>265</v>
+        <v>254</v>
       </c>
       <c r="I81" s="24">
         <v>0</v>
@@ -9439,17 +8628,8 @@
       <c r="AA81" s="24">
         <v>0</v>
       </c>
-      <c r="AB81" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC81" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD81" s="24" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="82" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A82" s="24">
         <v>59070001</v>
       </c>
@@ -9463,16 +8643,16 @@
         <v>1</v>
       </c>
       <c r="E82" s="12" t="s">
-        <v>182</v>
+        <v>171</v>
       </c>
       <c r="F82" s="24" t="s">
-        <v>239</v>
+        <v>228</v>
       </c>
       <c r="G82" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H82" s="24" t="s">
-        <v>183</v>
+        <v>172</v>
       </c>
       <c r="I82" s="24">
         <v>0</v>
@@ -9531,17 +8711,8 @@
       <c r="AA82" s="24">
         <v>0</v>
       </c>
-      <c r="AB82" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC82" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD82" s="24" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="83" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A83" s="24">
         <v>59090001</v>
       </c>
@@ -9555,16 +8726,16 @@
         <v>1</v>
       </c>
       <c r="E83" s="12" t="s">
-        <v>184</v>
+        <v>173</v>
       </c>
       <c r="F83" s="24" t="s">
-        <v>240</v>
+        <v>229</v>
       </c>
       <c r="G83" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H83" s="24" t="s">
-        <v>185</v>
+        <v>174</v>
       </c>
       <c r="I83" s="24">
         <v>0</v>
@@ -9623,17 +8794,8 @@
       <c r="AA83" s="24">
         <v>0</v>
       </c>
-      <c r="AB83" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC83" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD83" s="24" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="84" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A84" s="24">
         <v>59110001</v>
       </c>
@@ -9647,16 +8809,16 @@
         <v>1</v>
       </c>
       <c r="E84" s="12" t="s">
-        <v>186</v>
+        <v>175</v>
       </c>
       <c r="F84" s="24" t="s">
-        <v>241</v>
+        <v>230</v>
       </c>
       <c r="G84" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H84" s="24" t="s">
-        <v>187</v>
+        <v>176</v>
       </c>
       <c r="I84" s="24">
         <v>0</v>
@@ -9715,17 +8877,8 @@
       <c r="AA84" s="24">
         <v>0</v>
       </c>
-      <c r="AB84" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC84" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD84" s="24" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="85" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A85" s="24">
         <v>59130001</v>
       </c>
@@ -9739,16 +8892,16 @@
         <v>1</v>
       </c>
       <c r="E85" s="12" t="s">
-        <v>188</v>
+        <v>177</v>
       </c>
       <c r="F85" s="24" t="s">
-        <v>242</v>
+        <v>231</v>
       </c>
       <c r="G85" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H85" s="24" t="s">
-        <v>189</v>
+        <v>178</v>
       </c>
       <c r="I85" s="24">
         <v>0</v>
@@ -9807,17 +8960,8 @@
       <c r="AA85" s="24">
         <v>0</v>
       </c>
-      <c r="AB85" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC85" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD85" s="24" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="86" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A86" s="24">
         <v>59150001</v>
       </c>
@@ -9831,16 +8975,16 @@
         <v>1</v>
       </c>
       <c r="E86" s="12" t="s">
-        <v>190</v>
+        <v>179</v>
       </c>
       <c r="F86" s="24" t="s">
-        <v>243</v>
+        <v>232</v>
       </c>
       <c r="G86" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H86" s="24" t="s">
-        <v>191</v>
+        <v>180</v>
       </c>
       <c r="I86" s="24">
         <v>0</v>
@@ -9899,17 +9043,8 @@
       <c r="AA86" s="24">
         <v>0</v>
       </c>
-      <c r="AB86" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC86" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD86" s="24" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="87" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A87" s="24">
         <v>59180001</v>
       </c>
@@ -9923,16 +9058,16 @@
         <v>1</v>
       </c>
       <c r="E87" s="12" t="s">
-        <v>192</v>
+        <v>181</v>
       </c>
       <c r="F87" s="24" t="s">
-        <v>244</v>
+        <v>233</v>
       </c>
       <c r="G87" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H87" s="24" t="s">
-        <v>193</v>
+        <v>182</v>
       </c>
       <c r="I87" s="24">
         <v>0</v>
@@ -9991,17 +9126,8 @@
       <c r="AA87" s="24">
         <v>0</v>
       </c>
-      <c r="AB87" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC87" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD87" s="24" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="88" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A88" s="24">
         <v>59200001</v>
       </c>
@@ -10015,16 +9141,16 @@
         <v>1</v>
       </c>
       <c r="E88" s="12" t="s">
-        <v>194</v>
+        <v>183</v>
       </c>
       <c r="F88" s="24" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="G88" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H88" s="24" t="s">
-        <v>245</v>
+        <v>234</v>
       </c>
       <c r="I88" s="24">
         <v>0</v>
@@ -10083,17 +9209,8 @@
       <c r="AA88" s="24">
         <v>0</v>
       </c>
-      <c r="AB88" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC88" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD88" s="24" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="89" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A89" s="24">
         <v>59220001</v>
       </c>
@@ -10107,16 +9224,16 @@
         <v>1</v>
       </c>
       <c r="E89" s="12" t="s">
-        <v>195</v>
+        <v>184</v>
       </c>
       <c r="F89" s="24" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="G89" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H89" s="24" t="s">
-        <v>246</v>
+        <v>235</v>
       </c>
       <c r="I89" s="24">
         <v>0</v>
@@ -10175,17 +9292,8 @@
       <c r="AA89" s="24">
         <v>0</v>
       </c>
-      <c r="AB89" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC89" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD89" s="24" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="90" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A90" s="24">
         <v>59240001</v>
       </c>
@@ -10199,16 +9307,16 @@
         <v>1</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>295</v>
+        <v>284</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="G90" s="24" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>294</v>
+        <v>283</v>
       </c>
       <c r="I90" s="24">
         <v>0</v>
@@ -10267,17 +9375,8 @@
       <c r="AA90" s="24">
         <v>0</v>
       </c>
-      <c r="AB90" s="24" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC90" s="24" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD90" s="24" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="91" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A91" s="25">
         <v>60010001</v>
       </c>
@@ -10291,16 +9390,16 @@
         <v>1</v>
       </c>
       <c r="E91" s="12" t="s">
-        <v>196</v>
+        <v>185</v>
       </c>
       <c r="F91" s="25" t="s">
-        <v>247</v>
+        <v>236</v>
       </c>
       <c r="G91" s="25" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H91" s="25" t="s">
-        <v>197</v>
+        <v>186</v>
       </c>
       <c r="I91" s="25">
         <v>0</v>
@@ -10359,17 +9458,8 @@
       <c r="AA91" s="25">
         <v>0</v>
       </c>
-      <c r="AB91" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC91" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD91" s="25" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="92" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A92" s="25">
         <v>60030001</v>
       </c>
@@ -10383,16 +9473,16 @@
         <v>1</v>
       </c>
       <c r="E92" s="12" t="s">
-        <v>198</v>
+        <v>187</v>
       </c>
       <c r="F92" s="25" t="s">
-        <v>248</v>
+        <v>237</v>
       </c>
       <c r="G92" s="25" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H92" s="25" t="s">
-        <v>266</v>
+        <v>255</v>
       </c>
       <c r="I92" s="25">
         <v>0</v>
@@ -10451,17 +9541,8 @@
       <c r="AA92" s="25">
         <v>0</v>
       </c>
-      <c r="AB92" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC92" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD92" s="25" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="93" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A93" s="25">
         <v>60060001</v>
       </c>
@@ -10475,16 +9556,16 @@
         <v>1</v>
       </c>
       <c r="E93" s="12" t="s">
-        <v>199</v>
+        <v>188</v>
       </c>
       <c r="F93" s="25" t="s">
-        <v>249</v>
+        <v>238</v>
       </c>
       <c r="G93" s="25" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H93" s="25" t="s">
-        <v>200</v>
+        <v>189</v>
       </c>
       <c r="I93" s="25">
         <v>0</v>
@@ -10543,17 +9624,8 @@
       <c r="AA93" s="25">
         <v>0</v>
       </c>
-      <c r="AB93" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC93" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD93" s="25" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="94" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A94" s="25">
         <v>60090001</v>
       </c>
@@ -10567,16 +9639,16 @@
         <v>1</v>
       </c>
       <c r="E94" s="12" t="s">
-        <v>201</v>
+        <v>190</v>
       </c>
       <c r="F94" s="25" t="s">
-        <v>250</v>
+        <v>239</v>
       </c>
       <c r="G94" s="25" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H94" s="25" t="s">
-        <v>202</v>
+        <v>191</v>
       </c>
       <c r="I94" s="25">
         <v>0</v>
@@ -10635,17 +9707,8 @@
       <c r="AA94" s="25">
         <v>0</v>
       </c>
-      <c r="AB94" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC94" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD94" s="25" t="s">
-        <v>64</v>
-      </c>
     </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="95" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A95" s="25">
         <v>60110001</v>
       </c>
@@ -10659,16 +9722,16 @@
         <v>1</v>
       </c>
       <c r="E95" s="12" t="s">
-        <v>203</v>
+        <v>192</v>
       </c>
       <c r="F95" s="25" t="s">
-        <v>268</v>
+        <v>257</v>
       </c>
       <c r="G95" s="25" t="s">
-        <v>100</v>
+        <v>89</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>267</v>
+        <v>256</v>
       </c>
       <c r="I95" s="25">
         <v>0</v>
@@ -10725,19 +9788,10 @@
         <v>60070001</v>
       </c>
       <c r="AA95" s="26" t="s">
-        <v>204</v>
-      </c>
-      <c r="AB95" s="25" t="s">
-        <v>100</v>
-      </c>
-      <c r="AC95" s="25" t="s">
-        <v>63</v>
-      </c>
-      <c r="AD95" s="25" t="s">
-        <v>64</v>
+        <v>193</v>
       </c>
     </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="96" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A96" s="27">
         <v>61020001</v>
       </c>
@@ -10751,16 +9805,16 @@
         <v>1</v>
       </c>
       <c r="E96" s="12" t="s">
-        <v>205</v>
+        <v>194</v>
       </c>
       <c r="F96" s="27" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="G96" s="27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H96" s="27" t="s">
-        <v>206</v>
+        <v>195</v>
       </c>
       <c r="I96" s="27">
         <v>0</v>
@@ -10819,17 +9873,8 @@
       <c r="AA96" s="27">
         <v>0</v>
       </c>
-      <c r="AB96" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC96" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD96" s="27" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="97" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A97" s="27">
         <v>61040001</v>
       </c>
@@ -10843,16 +9888,16 @@
         <v>1</v>
       </c>
       <c r="E97" s="12" t="s">
-        <v>207</v>
+        <v>196</v>
       </c>
       <c r="F97" s="27" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="G97" s="27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H97" s="27" t="s">
-        <v>208</v>
+        <v>197</v>
       </c>
       <c r="I97" s="27">
         <v>0</v>
@@ -10911,17 +9956,8 @@
       <c r="AA97" s="27">
         <v>0</v>
       </c>
-      <c r="AB97" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC97" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD97" s="27" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="98" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="98" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A98" s="27">
         <v>61060001</v>
       </c>
@@ -10935,16 +9971,16 @@
         <v>1</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>209</v>
+        <v>198</v>
       </c>
       <c r="F98" s="27" t="s">
-        <v>270</v>
+        <v>259</v>
       </c>
       <c r="G98" s="27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H98" s="27" t="s">
-        <v>271</v>
+        <v>260</v>
       </c>
       <c r="I98" s="27">
         <v>0</v>
@@ -11003,17 +10039,8 @@
       <c r="AA98" s="27">
         <v>0</v>
       </c>
-      <c r="AB98" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC98" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD98" s="27" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="99" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="99" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A99" s="27">
         <v>61080001</v>
       </c>
@@ -11027,16 +10054,16 @@
         <v>1</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>210</v>
+        <v>199</v>
       </c>
       <c r="F99" s="27" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="G99" s="27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H99" s="27" t="s">
-        <v>95</v>
+        <v>84</v>
       </c>
       <c r="I99" s="27">
         <v>0</v>
@@ -11095,17 +10122,8 @@
       <c r="AA99" s="27">
         <v>0</v>
       </c>
-      <c r="AB99" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC99" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD99" s="27" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="100" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="100" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A100" s="27">
         <v>61100001</v>
       </c>
@@ -11119,16 +10137,16 @@
         <v>1</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>211</v>
+        <v>200</v>
       </c>
       <c r="F100" s="27" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="G100" s="27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H100" s="27" t="s">
-        <v>212</v>
+        <v>201</v>
       </c>
       <c r="I100" s="27">
         <v>0</v>
@@ -11187,17 +10205,8 @@
       <c r="AA100" s="27">
         <v>0</v>
       </c>
-      <c r="AB100" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC100" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD100" s="27" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="101" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="101" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A101" s="27">
         <v>61120001</v>
       </c>
@@ -11211,16 +10220,16 @@
         <v>1</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>213</v>
+        <v>202</v>
       </c>
       <c r="F101" s="27" t="s">
-        <v>272</v>
+        <v>261</v>
       </c>
       <c r="G101" s="27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H101" s="27" t="s">
-        <v>273</v>
+        <v>262</v>
       </c>
       <c r="I101" s="27">
         <v>0</v>
@@ -11279,17 +10288,8 @@
       <c r="AA101" s="27">
         <v>0</v>
       </c>
-      <c r="AB101" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC101" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD101" s="27" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="102" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="102" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A102" s="27">
         <v>61140001</v>
       </c>
@@ -11303,16 +10303,16 @@
         <v>1</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>214</v>
+        <v>203</v>
       </c>
       <c r="F102" s="27" t="s">
-        <v>274</v>
+        <v>263</v>
       </c>
       <c r="G102" s="27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H102" s="27" t="s">
-        <v>215</v>
+        <v>204</v>
       </c>
       <c r="I102" s="27">
         <v>0</v>
@@ -11371,17 +10371,8 @@
       <c r="AA102" s="27">
         <v>0</v>
       </c>
-      <c r="AB102" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC102" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD102" s="27" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="103" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="103" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A103" s="27">
         <v>61160001</v>
       </c>
@@ -11395,16 +10386,16 @@
         <v>1</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>216</v>
+        <v>205</v>
       </c>
       <c r="F103" s="27" t="s">
-        <v>276</v>
+        <v>265</v>
       </c>
       <c r="G103" s="27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H103" s="27" t="s">
-        <v>275</v>
+        <v>264</v>
       </c>
       <c r="I103" s="27">
         <v>0</v>
@@ -11463,17 +10454,8 @@
       <c r="AA103" s="27">
         <v>0</v>
       </c>
-      <c r="AB103" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC103" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD103" s="27" t="s">
-        <v>62</v>
-      </c>
     </row>
-    <row r="104" spans="1:30" x14ac:dyDescent="0.15">
+    <row r="104" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A104" s="27">
         <v>61180001</v>
       </c>
@@ -11487,16 +10469,16 @@
         <v>1</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>217</v>
+        <v>206</v>
       </c>
       <c r="F104" s="27" t="s">
-        <v>278</v>
+        <v>267</v>
       </c>
       <c r="G104" s="27" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="H104" s="27" t="s">
-        <v>277</v>
+        <v>266</v>
       </c>
       <c r="I104" s="27">
         <v>0</v>
@@ -11555,18 +10537,9 @@
       <c r="AA104" s="27">
         <v>0</v>
       </c>
-      <c r="AB104" s="27" t="s">
-        <v>34</v>
-      </c>
-      <c r="AC104" s="27" t="s">
-        <v>61</v>
-      </c>
-      <c r="AD104" s="27" t="s">
-        <v>62</v>
-      </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AB104" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AA104" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>

--- a/servers/maze_main_server_dev/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
+++ b/servers/maze_main_server_dev/conf.d/data/maze_skill_info_v8【迷宫-技能-技能信息】.xlsx
@@ -8,15 +8,15 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\派派世界2.0\02策划方案\06表格\4.0版本-迷宫独立表\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{28465B04-19DD-41AD-875D-2B6DFCA8A82E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5E9E04A4-209C-4931-A5C5-F020B6F92D66}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15225" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="maze_skill_info_v8" sheetId="1" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$104</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">maze_skill_info_v8!$A$4:$AA$106</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -293,7 +293,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="468" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="476" uniqueCount="296">
   <si>
     <t>paipaiworld_config</t>
   </si>
@@ -1174,10 +1174,6 @@
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
   <si>
-    <t>光环技能-自身效果：光环范围提高-范围内敌人受到伤害提高-范围内敌人造成伤害降低</t>
-    <phoneticPr fontId="5" type="noConversion"/>
-  </si>
-  <si>
     <t>获取护盾提高</t>
   </si>
   <si>
@@ -1302,6 +1298,26 @@
   </si>
   <si>
     <t>1,2,3,4,0</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-自身效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-敌人效果</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-自身效果：光环范围提高</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>光环技能-敌人效果：范围内敌人受到伤害提高-范围内敌人造成伤害降低</t>
+    <phoneticPr fontId="5" type="noConversion"/>
+  </si>
+  <si>
+    <t>正义光环</t>
     <phoneticPr fontId="5" type="noConversion"/>
   </si>
 </sst>
@@ -1988,7 +2004,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AA104"/>
+  <dimension ref="A1:AA106"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="11.25" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="15.625" style="5" bestFit="1" customWidth="1"/>
@@ -2083,7 +2099,7 @@
         <v>65</v>
       </c>
       <c r="U2" s="33" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
       <c r="V2" s="5" t="s">
         <v>65</v>
@@ -2166,7 +2182,7 @@
         <v>14</v>
       </c>
       <c r="U3" s="33" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
       <c r="V3" s="5" t="s">
         <v>34</v>
@@ -2249,7 +2265,7 @@
         <v>28</v>
       </c>
       <c r="U4" s="33" t="s">
-        <v>290</v>
+        <v>289</v>
       </c>
       <c r="V4" s="5" t="s">
         <v>35</v>
@@ -4172,7 +4188,7 @@
         <v>25010001</v>
       </c>
       <c r="B28" s="23">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="C28" s="23">
         <v>2501</v>
@@ -4181,16 +4197,16 @@
         <v>1</v>
       </c>
       <c r="E28" s="18" t="s">
+        <v>284</v>
+      </c>
+      <c r="F28" s="23" t="s">
         <v>285</v>
-      </c>
-      <c r="F28" s="23" t="s">
-        <v>286</v>
       </c>
       <c r="G28" s="23" t="s">
         <v>32</v>
       </c>
       <c r="H28" s="23" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
       <c r="I28" s="23">
         <v>0</v>
@@ -5045,7 +5061,7 @@
         <v>1</v>
       </c>
       <c r="U38" s="32" t="s">
-        <v>291</v>
+        <v>290</v>
       </c>
       <c r="V38" s="28">
         <v>150</v>
@@ -6328,7 +6344,7 @@
         <v>32</v>
       </c>
       <c r="H54" s="23" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
       <c r="I54" s="23">
         <v>0</v>
@@ -6405,7 +6421,7 @@
         <v>70</v>
       </c>
       <c r="F55" s="13" t="s">
-        <v>268</v>
+        <v>267</v>
       </c>
       <c r="G55" s="13" t="s">
         <v>32</v>
@@ -6488,7 +6504,7 @@
         <v>110</v>
       </c>
       <c r="F56" s="13" t="s">
-        <v>269</v>
+        <v>268</v>
       </c>
       <c r="G56" s="13" t="s">
         <v>32</v>
@@ -6571,7 +6587,7 @@
         <v>112</v>
       </c>
       <c r="F57" s="13" t="s">
-        <v>270</v>
+        <v>269</v>
       </c>
       <c r="G57" s="13" t="s">
         <v>32</v>
@@ -6654,7 +6670,7 @@
         <v>74</v>
       </c>
       <c r="F58" s="13" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="G58" s="13" t="s">
         <v>32</v>
@@ -6737,7 +6753,7 @@
         <v>75</v>
       </c>
       <c r="F59" s="13" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="G59" s="13" t="s">
         <v>32</v>
@@ -6820,7 +6836,7 @@
         <v>115</v>
       </c>
       <c r="F60" s="13" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="G60" s="13" t="s">
         <v>32</v>
@@ -6903,7 +6919,7 @@
         <v>116</v>
       </c>
       <c r="F61" s="13" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="G61" s="13" t="s">
         <v>32</v>
@@ -7318,13 +7334,13 @@
         <v>129</v>
       </c>
       <c r="F66" s="14" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
       <c r="G66" s="14" t="s">
         <v>32</v>
       </c>
       <c r="H66" s="14" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I66" s="14">
         <v>0</v>
@@ -7401,13 +7417,13 @@
         <v>129</v>
       </c>
       <c r="F67" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="G67" s="14" t="s">
         <v>32</v>
       </c>
       <c r="H67" s="14" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I67" s="14">
         <v>0</v>
@@ -7733,13 +7749,13 @@
         <v>135</v>
       </c>
       <c r="F71" s="15" t="s">
-        <v>282</v>
+        <v>281</v>
       </c>
       <c r="G71" s="15" t="s">
         <v>32</v>
       </c>
       <c r="H71" s="15" t="s">
-        <v>281</v>
+        <v>280</v>
       </c>
       <c r="I71" s="15">
         <v>0</v>
@@ -7816,7 +7832,7 @@
         <v>136</v>
       </c>
       <c r="F72" s="15" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="G72" s="15" t="s">
         <v>32</v>
@@ -7899,7 +7915,7 @@
         <v>137</v>
       </c>
       <c r="F73" s="15" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="G73" s="15" t="s">
         <v>32</v>
@@ -8314,7 +8330,7 @@
         <v>144</v>
       </c>
       <c r="F78" s="16" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="G78" s="16" t="s">
         <v>32</v>
@@ -9307,16 +9323,16 @@
         <v>1</v>
       </c>
       <c r="E90" s="12" t="s">
-        <v>284</v>
+        <v>283</v>
       </c>
       <c r="F90" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="G90" s="24" t="s">
         <v>32</v>
       </c>
       <c r="H90" s="24" t="s">
-        <v>283</v>
+        <v>282</v>
       </c>
       <c r="I90" s="24">
         <v>0</v>
@@ -9713,7 +9729,7 @@
         <v>60110001</v>
       </c>
       <c r="B95" s="25">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="C95" s="25">
         <v>6011</v>
@@ -9722,16 +9738,16 @@
         <v>1</v>
       </c>
       <c r="E95" s="12" t="s">
+        <v>295</v>
+      </c>
+      <c r="F95" s="25" t="s">
         <v>192</v>
-      </c>
-      <c r="F95" s="25" t="s">
-        <v>257</v>
       </c>
       <c r="G95" s="25" t="s">
         <v>89</v>
       </c>
       <c r="H95" s="25" t="s">
-        <v>256</v>
+        <v>192</v>
       </c>
       <c r="I95" s="25">
         <v>0</v>
@@ -9785,202 +9801,202 @@
         <v>10000</v>
       </c>
       <c r="Z95" s="25">
-        <v>60070001</v>
-      </c>
-      <c r="AA95" s="26" t="s">
-        <v>193</v>
+        <v>60080001</v>
+      </c>
+      <c r="AA95" s="26">
+        <v>0</v>
       </c>
     </row>
     <row r="96" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A96" s="27">
-        <v>61020001</v>
-      </c>
-      <c r="B96" s="27">
+      <c r="A96" s="25">
+        <v>60120001</v>
+      </c>
+      <c r="B96" s="25">
+        <v>5</v>
+      </c>
+      <c r="C96" s="25">
+        <v>6012</v>
+      </c>
+      <c r="D96" s="25">
+        <v>1</v>
+      </c>
+      <c r="E96" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="F96" s="25" t="s">
+        <v>293</v>
+      </c>
+      <c r="G96" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="H96" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="I96" s="25">
+        <v>0</v>
+      </c>
+      <c r="J96" s="25">
+        <v>0</v>
+      </c>
+      <c r="K96" s="25">
+        <v>0</v>
+      </c>
+      <c r="L96" s="25">
+        <v>0</v>
+      </c>
+      <c r="M96" s="25">
+        <v>0</v>
+      </c>
+      <c r="N96" s="25">
+        <v>0</v>
+      </c>
+      <c r="O96" s="25">
+        <v>0</v>
+      </c>
+      <c r="P96" s="25">
         <v>4</v>
       </c>
-      <c r="C96" s="27">
-        <v>6102</v>
-      </c>
-      <c r="D96" s="27">
-        <v>1</v>
-      </c>
-      <c r="E96" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="F96" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="G96" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="H96" s="27" t="s">
-        <v>195</v>
-      </c>
-      <c r="I96" s="27">
-        <v>0</v>
-      </c>
-      <c r="J96" s="27">
-        <v>0</v>
-      </c>
-      <c r="K96" s="27">
-        <v>0</v>
-      </c>
-      <c r="L96" s="27">
-        <v>0</v>
-      </c>
-      <c r="M96" s="27">
-        <v>0</v>
-      </c>
-      <c r="N96" s="27">
-        <v>0</v>
-      </c>
-      <c r="O96" s="27">
-        <v>0</v>
-      </c>
-      <c r="P96" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q96" s="27">
-        <v>0</v>
-      </c>
-      <c r="R96" s="27">
-        <v>0</v>
-      </c>
-      <c r="S96" s="27">
-        <v>0</v>
-      </c>
-      <c r="T96" s="27">
-        <v>0</v>
-      </c>
-      <c r="U96" s="27">
-        <v>0</v>
-      </c>
-      <c r="V96" s="27">
-        <v>0</v>
-      </c>
-      <c r="W96" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X96" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y96" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z96" s="27">
-        <v>61010001</v>
-      </c>
-      <c r="AA96" s="27">
+      <c r="Q96" s="25">
+        <v>1</v>
+      </c>
+      <c r="R96" s="25">
+        <v>10000</v>
+      </c>
+      <c r="S96" s="25">
+        <v>0</v>
+      </c>
+      <c r="T96" s="25">
+        <v>0</v>
+      </c>
+      <c r="U96" s="25">
+        <v>0</v>
+      </c>
+      <c r="V96" s="25">
+        <v>0</v>
+      </c>
+      <c r="W96" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X96" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y96" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z96" s="25">
+        <v>60070001</v>
+      </c>
+      <c r="AA96" s="26">
         <v>0</v>
       </c>
     </row>
     <row r="97" spans="1:27" x14ac:dyDescent="0.15">
-      <c r="A97" s="27">
-        <v>61040001</v>
-      </c>
-      <c r="B97" s="27">
+      <c r="A97" s="25">
+        <v>60130001</v>
+      </c>
+      <c r="B97" s="25">
+        <v>5</v>
+      </c>
+      <c r="C97" s="25">
+        <v>6013</v>
+      </c>
+      <c r="D97" s="25">
+        <v>1</v>
+      </c>
+      <c r="E97" s="12" t="s">
+        <v>292</v>
+      </c>
+      <c r="F97" s="25" t="s">
+        <v>294</v>
+      </c>
+      <c r="G97" s="25" t="s">
+        <v>89</v>
+      </c>
+      <c r="H97" s="25" t="s">
+        <v>256</v>
+      </c>
+      <c r="I97" s="25">
+        <v>0</v>
+      </c>
+      <c r="J97" s="25">
+        <v>0</v>
+      </c>
+      <c r="K97" s="25">
+        <v>0</v>
+      </c>
+      <c r="L97" s="25">
+        <v>0</v>
+      </c>
+      <c r="M97" s="25">
+        <v>0</v>
+      </c>
+      <c r="N97" s="25">
+        <v>0</v>
+      </c>
+      <c r="O97" s="25">
+        <v>0</v>
+      </c>
+      <c r="P97" s="25">
         <v>4</v>
       </c>
-      <c r="C97" s="27">
-        <v>6104</v>
-      </c>
-      <c r="D97" s="27">
-        <v>1</v>
-      </c>
-      <c r="E97" s="12" t="s">
-        <v>196</v>
-      </c>
-      <c r="F97" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="G97" s="27" t="s">
-        <v>32</v>
-      </c>
-      <c r="H97" s="27" t="s">
-        <v>197</v>
-      </c>
-      <c r="I97" s="27">
-        <v>0</v>
-      </c>
-      <c r="J97" s="27">
-        <v>0</v>
-      </c>
-      <c r="K97" s="27">
-        <v>0</v>
-      </c>
-      <c r="L97" s="27">
-        <v>0</v>
-      </c>
-      <c r="M97" s="27">
-        <v>0</v>
-      </c>
-      <c r="N97" s="27">
-        <v>0</v>
-      </c>
-      <c r="O97" s="27">
-        <v>0</v>
-      </c>
-      <c r="P97" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q97" s="27">
-        <v>0</v>
-      </c>
-      <c r="R97" s="27">
-        <v>0</v>
-      </c>
-      <c r="S97" s="27">
-        <v>0</v>
-      </c>
-      <c r="T97" s="27">
-        <v>0</v>
-      </c>
-      <c r="U97" s="27">
-        <v>0</v>
-      </c>
-      <c r="V97" s="27">
-        <v>0</v>
-      </c>
-      <c r="W97" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X97" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y97" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z97" s="27">
-        <v>61020001</v>
-      </c>
-      <c r="AA97" s="27">
-        <v>0</v>
+      <c r="Q97" s="25">
+        <v>2</v>
+      </c>
+      <c r="R97" s="25">
+        <v>10000</v>
+      </c>
+      <c r="S97" s="25">
+        <v>0</v>
+      </c>
+      <c r="T97" s="25">
+        <v>0</v>
+      </c>
+      <c r="U97" s="25">
+        <v>0</v>
+      </c>
+      <c r="V97" s="25">
+        <v>0</v>
+      </c>
+      <c r="W97" s="25">
+        <v>10000</v>
+      </c>
+      <c r="X97" s="25">
+        <v>0</v>
+      </c>
+      <c r="Y97" s="25">
+        <v>10000</v>
+      </c>
+      <c r="Z97" s="25">
+        <v>0</v>
+      </c>
+      <c r="AA97" s="26" t="s">
+        <v>193</v>
       </c>
     </row>
     <row r="98" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A98" s="27">
-        <v>61060001</v>
+        <v>61020001</v>
       </c>
       <c r="B98" s="27">
         <v>4</v>
       </c>
       <c r="C98" s="27">
-        <v>6106</v>
+        <v>6102</v>
       </c>
       <c r="D98" s="27">
         <v>1</v>
       </c>
       <c r="E98" s="12" t="s">
-        <v>198</v>
+        <v>194</v>
       </c>
       <c r="F98" s="27" t="s">
-        <v>259</v>
+        <v>195</v>
       </c>
       <c r="G98" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H98" s="27" t="s">
-        <v>260</v>
+        <v>195</v>
       </c>
       <c r="I98" s="27">
         <v>0</v>
@@ -10034,7 +10050,7 @@
         <v>10000</v>
       </c>
       <c r="Z98" s="27">
-        <v>61030001</v>
+        <v>61010001</v>
       </c>
       <c r="AA98" s="27">
         <v>0</v>
@@ -10042,28 +10058,28 @@
     </row>
     <row r="99" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A99" s="27">
-        <v>61080001</v>
+        <v>61040001</v>
       </c>
       <c r="B99" s="27">
         <v>4</v>
       </c>
       <c r="C99" s="27">
-        <v>6108</v>
+        <v>6104</v>
       </c>
       <c r="D99" s="27">
         <v>1</v>
       </c>
       <c r="E99" s="12" t="s">
-        <v>199</v>
+        <v>196</v>
       </c>
       <c r="F99" s="27" t="s">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="G99" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H99" s="27" t="s">
-        <v>84</v>
+        <v>197</v>
       </c>
       <c r="I99" s="27">
         <v>0</v>
@@ -10117,7 +10133,7 @@
         <v>10000</v>
       </c>
       <c r="Z99" s="27">
-        <v>61040001</v>
+        <v>61020001</v>
       </c>
       <c r="AA99" s="27">
         <v>0</v>
@@ -10125,28 +10141,28 @@
     </row>
     <row r="100" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A100" s="27">
-        <v>61100001</v>
+        <v>61060001</v>
       </c>
       <c r="B100" s="27">
         <v>4</v>
       </c>
       <c r="C100" s="27">
-        <v>6110</v>
+        <v>6106</v>
       </c>
       <c r="D100" s="27">
         <v>1</v>
       </c>
       <c r="E100" s="12" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="F100" s="27" t="s">
-        <v>201</v>
+        <v>258</v>
       </c>
       <c r="G100" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H100" s="27" t="s">
-        <v>201</v>
+        <v>259</v>
       </c>
       <c r="I100" s="27">
         <v>0</v>
@@ -10200,7 +10216,7 @@
         <v>10000</v>
       </c>
       <c r="Z100" s="27">
-        <v>61050001</v>
+        <v>61030001</v>
       </c>
       <c r="AA100" s="27">
         <v>0</v>
@@ -10208,28 +10224,28 @@
     </row>
     <row r="101" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A101" s="27">
-        <v>61120001</v>
+        <v>61080001</v>
       </c>
       <c r="B101" s="27">
         <v>4</v>
       </c>
       <c r="C101" s="27">
-        <v>6112</v>
+        <v>6108</v>
       </c>
       <c r="D101" s="27">
         <v>1</v>
       </c>
       <c r="E101" s="12" t="s">
-        <v>202</v>
+        <v>199</v>
       </c>
       <c r="F101" s="27" t="s">
-        <v>261</v>
+        <v>84</v>
       </c>
       <c r="G101" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H101" s="27" t="s">
-        <v>262</v>
+        <v>84</v>
       </c>
       <c r="I101" s="27">
         <v>0</v>
@@ -10283,7 +10299,7 @@
         <v>10000</v>
       </c>
       <c r="Z101" s="27">
-        <v>61060001</v>
+        <v>61040001</v>
       </c>
       <c r="AA101" s="27">
         <v>0</v>
@@ -10291,28 +10307,28 @@
     </row>
     <row r="102" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A102" s="27">
-        <v>61140001</v>
+        <v>61100001</v>
       </c>
       <c r="B102" s="27">
         <v>4</v>
       </c>
       <c r="C102" s="27">
-        <v>6114</v>
+        <v>6110</v>
       </c>
       <c r="D102" s="27">
         <v>1</v>
       </c>
       <c r="E102" s="12" t="s">
-        <v>203</v>
+        <v>200</v>
       </c>
       <c r="F102" s="27" t="s">
-        <v>263</v>
+        <v>201</v>
       </c>
       <c r="G102" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H102" s="27" t="s">
-        <v>204</v>
+        <v>201</v>
       </c>
       <c r="I102" s="27">
         <v>0</v>
@@ -10366,7 +10382,7 @@
         <v>10000</v>
       </c>
       <c r="Z102" s="27">
-        <v>61070001</v>
+        <v>61050001</v>
       </c>
       <c r="AA102" s="27">
         <v>0</v>
@@ -10374,28 +10390,28 @@
     </row>
     <row r="103" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A103" s="27">
-        <v>61160001</v>
+        <v>61120001</v>
       </c>
       <c r="B103" s="27">
         <v>4</v>
       </c>
       <c r="C103" s="27">
-        <v>6116</v>
+        <v>6112</v>
       </c>
       <c r="D103" s="27">
         <v>1</v>
       </c>
       <c r="E103" s="12" t="s">
-        <v>205</v>
+        <v>202</v>
       </c>
       <c r="F103" s="27" t="s">
-        <v>265</v>
+        <v>260</v>
       </c>
       <c r="G103" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H103" s="27" t="s">
-        <v>264</v>
+        <v>261</v>
       </c>
       <c r="I103" s="27">
         <v>0</v>
@@ -10449,7 +10465,7 @@
         <v>10000</v>
       </c>
       <c r="Z103" s="27">
-        <v>61080001</v>
+        <v>61060001</v>
       </c>
       <c r="AA103" s="27">
         <v>0</v>
@@ -10457,89 +10473,255 @@
     </row>
     <row r="104" spans="1:27" x14ac:dyDescent="0.15">
       <c r="A104" s="27">
-        <v>61180001</v>
+        <v>61140001</v>
       </c>
       <c r="B104" s="27">
         <v>4</v>
       </c>
       <c r="C104" s="27">
-        <v>6118</v>
+        <v>6114</v>
       </c>
       <c r="D104" s="27">
         <v>1</v>
       </c>
       <c r="E104" s="12" t="s">
-        <v>206</v>
+        <v>203</v>
       </c>
       <c r="F104" s="27" t="s">
-        <v>267</v>
+        <v>262</v>
       </c>
       <c r="G104" s="27" t="s">
         <v>32</v>
       </c>
       <c r="H104" s="27" t="s">
+        <v>204</v>
+      </c>
+      <c r="I104" s="27">
+        <v>0</v>
+      </c>
+      <c r="J104" s="27">
+        <v>0</v>
+      </c>
+      <c r="K104" s="27">
+        <v>0</v>
+      </c>
+      <c r="L104" s="27">
+        <v>0</v>
+      </c>
+      <c r="M104" s="27">
+        <v>0</v>
+      </c>
+      <c r="N104" s="27">
+        <v>0</v>
+      </c>
+      <c r="O104" s="27">
+        <v>0</v>
+      </c>
+      <c r="P104" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q104" s="27">
+        <v>0</v>
+      </c>
+      <c r="R104" s="27">
+        <v>0</v>
+      </c>
+      <c r="S104" s="27">
+        <v>0</v>
+      </c>
+      <c r="T104" s="27">
+        <v>0</v>
+      </c>
+      <c r="U104" s="27">
+        <v>0</v>
+      </c>
+      <c r="V104" s="27">
+        <v>0</v>
+      </c>
+      <c r="W104" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X104" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y104" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z104" s="27">
+        <v>61070001</v>
+      </c>
+      <c r="AA104" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="105" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A105" s="27">
+        <v>61160001</v>
+      </c>
+      <c r="B105" s="27">
+        <v>4</v>
+      </c>
+      <c r="C105" s="27">
+        <v>6116</v>
+      </c>
+      <c r="D105" s="27">
+        <v>1</v>
+      </c>
+      <c r="E105" s="12" t="s">
+        <v>205</v>
+      </c>
+      <c r="F105" s="27" t="s">
+        <v>264</v>
+      </c>
+      <c r="G105" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H105" s="27" t="s">
+        <v>263</v>
+      </c>
+      <c r="I105" s="27">
+        <v>0</v>
+      </c>
+      <c r="J105" s="27">
+        <v>0</v>
+      </c>
+      <c r="K105" s="27">
+        <v>0</v>
+      </c>
+      <c r="L105" s="27">
+        <v>0</v>
+      </c>
+      <c r="M105" s="27">
+        <v>0</v>
+      </c>
+      <c r="N105" s="27">
+        <v>0</v>
+      </c>
+      <c r="O105" s="27">
+        <v>0</v>
+      </c>
+      <c r="P105" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q105" s="27">
+        <v>0</v>
+      </c>
+      <c r="R105" s="27">
+        <v>0</v>
+      </c>
+      <c r="S105" s="27">
+        <v>0</v>
+      </c>
+      <c r="T105" s="27">
+        <v>0</v>
+      </c>
+      <c r="U105" s="27">
+        <v>0</v>
+      </c>
+      <c r="V105" s="27">
+        <v>0</v>
+      </c>
+      <c r="W105" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X105" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y105" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z105" s="27">
+        <v>61080001</v>
+      </c>
+      <c r="AA105" s="27">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="106" spans="1:27" x14ac:dyDescent="0.15">
+      <c r="A106" s="27">
+        <v>61180001</v>
+      </c>
+      <c r="B106" s="27">
+        <v>4</v>
+      </c>
+      <c r="C106" s="27">
+        <v>6118</v>
+      </c>
+      <c r="D106" s="27">
+        <v>1</v>
+      </c>
+      <c r="E106" s="12" t="s">
+        <v>206</v>
+      </c>
+      <c r="F106" s="27" t="s">
         <v>266</v>
       </c>
-      <c r="I104" s="27">
-        <v>0</v>
-      </c>
-      <c r="J104" s="27">
-        <v>0</v>
-      </c>
-      <c r="K104" s="27">
-        <v>0</v>
-      </c>
-      <c r="L104" s="27">
-        <v>0</v>
-      </c>
-      <c r="M104" s="27">
-        <v>0</v>
-      </c>
-      <c r="N104" s="27">
-        <v>0</v>
-      </c>
-      <c r="O104" s="27">
-        <v>0</v>
-      </c>
-      <c r="P104" s="27">
-        <v>0</v>
-      </c>
-      <c r="Q104" s="27">
-        <v>0</v>
-      </c>
-      <c r="R104" s="27">
-        <v>0</v>
-      </c>
-      <c r="S104" s="27">
-        <v>0</v>
-      </c>
-      <c r="T104" s="27">
-        <v>0</v>
-      </c>
-      <c r="U104" s="27">
-        <v>0</v>
-      </c>
-      <c r="V104" s="27">
-        <v>0</v>
-      </c>
-      <c r="W104" s="27">
-        <v>10000</v>
-      </c>
-      <c r="X104" s="27">
-        <v>0</v>
-      </c>
-      <c r="Y104" s="27">
-        <v>10000</v>
-      </c>
-      <c r="Z104" s="27">
+      <c r="G106" s="27" t="s">
+        <v>32</v>
+      </c>
+      <c r="H106" s="27" t="s">
+        <v>265</v>
+      </c>
+      <c r="I106" s="27">
+        <v>0</v>
+      </c>
+      <c r="J106" s="27">
+        <v>0</v>
+      </c>
+      <c r="K106" s="27">
+        <v>0</v>
+      </c>
+      <c r="L106" s="27">
+        <v>0</v>
+      </c>
+      <c r="M106" s="27">
+        <v>0</v>
+      </c>
+      <c r="N106" s="27">
+        <v>0</v>
+      </c>
+      <c r="O106" s="27">
+        <v>0</v>
+      </c>
+      <c r="P106" s="27">
+        <v>0</v>
+      </c>
+      <c r="Q106" s="27">
+        <v>0</v>
+      </c>
+      <c r="R106" s="27">
+        <v>0</v>
+      </c>
+      <c r="S106" s="27">
+        <v>0</v>
+      </c>
+      <c r="T106" s="27">
+        <v>0</v>
+      </c>
+      <c r="U106" s="27">
+        <v>0</v>
+      </c>
+      <c r="V106" s="27">
+        <v>0</v>
+      </c>
+      <c r="W106" s="27">
+        <v>10000</v>
+      </c>
+      <c r="X106" s="27">
+        <v>0</v>
+      </c>
+      <c r="Y106" s="27">
+        <v>10000</v>
+      </c>
+      <c r="Z106" s="27">
         <v>61090001</v>
       </c>
-      <c r="AA104" s="27">
+      <c r="AA106" s="27">
         <v>0</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A4:AA104" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
+  <autoFilter ref="A4:AA106" xr:uid="{00000000-0001-0000-0000-000000000000}"/>
   <phoneticPr fontId="5" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <legacyDrawing r:id="rId1"/>
